--- a/オーギヤ半田島図.xlsx
+++ b/オーギヤ半田島図.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13464"/>
+    <workbookView windowWidth="24660" windowHeight="11430"/>
   </bookViews>
   <sheets>
     <sheet name="島図" sheetId="1" r:id="rId1"/>
@@ -37,6 +37,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -44,9 +52,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -68,8 +90,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -91,31 +120,25 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="Arial"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -127,9 +150,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -137,7 +159,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -151,16 +173,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -169,20 +183,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -197,13 +197,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -221,25 +299,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -251,7 +353,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -263,25 +365,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -293,91 +377,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,21 +392,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -417,48 +402,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -480,6 +423,63 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -491,148 +491,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -907,36 +907,36 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:AG995"/>
-  <sheetFormatPr defaultColWidth="12.6296296296296" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.6285714285714" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="3.87962962962963" style="1" customWidth="1"/>
-    <col min="3" max="4" width="7.87962962962963" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.37962962962963" style="1" customWidth="1"/>
-    <col min="6" max="7" width="7.87962962962963" style="1" customWidth="1"/>
-    <col min="8" max="8" width="6.87962962962963" style="1" customWidth="1"/>
-    <col min="9" max="10" width="7.37962962962963" style="1" customWidth="1"/>
-    <col min="11" max="12" width="7.25" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7.37962962962963" style="1" customWidth="1"/>
-    <col min="14" max="15" width="7.87962962962963" style="1" customWidth="1"/>
-    <col min="16" max="16" width="7.12962962962963" style="1" customWidth="1"/>
-    <col min="17" max="20" width="7.5" style="1" customWidth="1"/>
-    <col min="21" max="21" width="7.12962962962963" style="1" customWidth="1"/>
-    <col min="22" max="22" width="7.87962962962963" style="1" customWidth="1"/>
-    <col min="23" max="23" width="6.87962962962963" style="1" customWidth="1"/>
-    <col min="24" max="24" width="7.12962962962963" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.75238095238095" style="1" customWidth="1"/>
+    <col min="2" max="2" width="3.87619047619048" style="1" customWidth="1"/>
+    <col min="3" max="4" width="7.87619047619048" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.38095238095238" style="1" customWidth="1"/>
+    <col min="6" max="7" width="7.87619047619048" style="1" customWidth="1"/>
+    <col min="8" max="8" width="6.87619047619048" style="1" customWidth="1"/>
+    <col min="9" max="10" width="7.38095238095238" style="1" customWidth="1"/>
+    <col min="11" max="12" width="7.24761904761905" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.38095238095238" style="1" customWidth="1"/>
+    <col min="14" max="15" width="7.87619047619048" style="1" customWidth="1"/>
+    <col min="16" max="16" width="7.13333333333333" style="1" customWidth="1"/>
+    <col min="17" max="20" width="7.5047619047619" style="1" customWidth="1"/>
+    <col min="21" max="21" width="7.13333333333333" style="1" customWidth="1"/>
+    <col min="22" max="22" width="7.87619047619048" style="1" customWidth="1"/>
+    <col min="23" max="23" width="6.87619047619048" style="1" customWidth="1"/>
+    <col min="24" max="24" width="7.13333333333333" style="1" customWidth="1"/>
     <col min="25" max="25" width="7" style="1" customWidth="1"/>
-    <col min="26" max="26" width="3.12962962962963" style="1" customWidth="1"/>
-    <col min="27" max="28" width="7.87962962962963" style="1" customWidth="1"/>
+    <col min="26" max="26" width="3.13333333333333" style="1" customWidth="1"/>
+    <col min="27" max="28" width="7.87619047619048" style="1" customWidth="1"/>
     <col min="29" max="29" width="2" style="1" customWidth="1"/>
-    <col min="30" max="30" width="7.87962962962963" style="1" customWidth="1"/>
-    <col min="31" max="31" width="7.12962962962963" style="1" customWidth="1"/>
-    <col min="32" max="32" width="2.37962962962963" style="1" customWidth="1"/>
-    <col min="33" max="33" width="7.12962962962963" style="1" customWidth="1"/>
-    <col min="34" max="16384" width="12.6296296296296" style="1"/>
+    <col min="30" max="30" width="7.87619047619048" style="1" customWidth="1"/>
+    <col min="31" max="31" width="7.13333333333333" style="1" customWidth="1"/>
+    <col min="32" max="32" width="2.38095238095238" style="1" customWidth="1"/>
+    <col min="33" max="33" width="7.13333333333333" style="1" customWidth="1"/>
+    <col min="34" max="16384" width="12.6285714285714" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:23">
+    <row r="2" ht="12.75" spans="3:23">
       <c r="C2" s="2">
         <v>1112</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="3" ht="13.2" spans="1:23">
+    <row r="3" ht="12.75" spans="1:23">
       <c r="A3" s="2">
         <v>1113</v>
       </c>
@@ -1027,7 +1027,7 @@
       <c r="V3" s="2"/>
       <c r="W3" s="2"/>
     </row>
-    <row r="4" ht="13.2" spans="1:23">
+    <row r="4" ht="12.75" spans="1:23">
       <c r="A4" s="2">
         <v>1114</v>
       </c>
@@ -1085,7 +1085,7 @@
       <c r="V4" s="2"/>
       <c r="W4" s="2"/>
     </row>
-    <row r="5" ht="13.2" spans="1:23">
+    <row r="5" ht="12.75" spans="1:23">
       <c r="A5" s="2">
         <v>1115</v>
       </c>
@@ -1139,7 +1139,7 @@
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
     </row>
-    <row r="6" ht="13.2" spans="1:23">
+    <row r="6" ht="12.75" spans="1:23">
       <c r="A6" s="2">
         <v>1116</v>
       </c>
@@ -1164,7 +1164,7 @@
       <c r="V6" s="2"/>
       <c r="W6" s="2"/>
     </row>
-    <row r="7" ht="13.2" spans="1:30">
+    <row r="7" ht="12.75" spans="1:30">
       <c r="A7" s="2">
         <v>1117</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="8" ht="13.2" spans="1:30">
+    <row r="8" ht="12.75" spans="1:30">
       <c r="A8" s="2">
         <v>1118</v>
       </c>
@@ -1280,7 +1280,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="9" ht="13.2" spans="1:30">
+    <row r="9" ht="12.75" spans="1:30">
       <c r="A9" s="2">
         <v>1119</v>
       </c>
@@ -1310,7 +1310,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="10" ht="13.2" spans="1:30">
+    <row r="10" ht="12.75" spans="1:30">
       <c r="A10" s="2">
         <v>1120</v>
       </c>
@@ -1362,7 +1362,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="11" ht="13.2" spans="1:30">
+    <row r="11" ht="12.75" spans="1:30">
       <c r="A11" s="2">
         <v>1121</v>
       </c>
@@ -1415,7 +1415,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="12" ht="13.2" spans="1:30">
+    <row r="12" ht="12.75" spans="1:30">
       <c r="A12" s="2">
         <v>1122</v>
       </c>
@@ -1456,7 +1456,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="13" ht="13.2" spans="1:30">
+    <row r="13" ht="12.75" spans="1:30">
       <c r="A13" s="2">
         <v>1123</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="14" ht="13.2" spans="1:30">
+    <row r="14" ht="12.75" spans="1:30">
       <c r="A14" s="2">
         <v>1124</v>
       </c>
@@ -1564,7 +1564,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="15" ht="13.2" spans="1:30">
+    <row r="15" ht="12.75" spans="1:30">
       <c r="A15" s="2">
         <v>1125</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="16" ht="13.2" spans="1:30">
+    <row r="16" ht="12.75" spans="1:30">
       <c r="A16" s="2">
         <v>1126</v>
       </c>
@@ -1654,7 +1654,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="17" ht="13.2" spans="1:30">
+    <row r="17" ht="12.75" spans="1:30">
       <c r="A17" s="2">
         <v>1127</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="18" ht="13.2" spans="1:30">
+    <row r="18" ht="12.75" spans="1:30">
       <c r="A18" s="2">
         <v>1128</v>
       </c>
@@ -1752,7 +1752,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="19" ht="13.2" spans="1:30">
+    <row r="19" ht="12.75" spans="1:30">
       <c r="A19" s="2">
         <v>1129</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="20" ht="13.2" spans="1:30">
+    <row r="20" ht="12.75" spans="1:30">
       <c r="A20" s="2">
         <v>1130</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="21" ht="13.2" spans="1:30">
+    <row r="21" ht="12.75" spans="1:30">
       <c r="A21" s="2">
         <v>1131</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="22" ht="13.2" spans="1:30">
+    <row r="22" ht="12.75" spans="1:30">
       <c r="A22" s="2">
         <v>1132</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="23" ht="13.2" spans="1:30">
+    <row r="23" ht="12.75" spans="1:30">
       <c r="A23" s="2">
         <v>1133</v>
       </c>
@@ -2036,7 +2036,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="24" ht="13.2" spans="1:30">
+    <row r="24" ht="12.75" spans="1:30">
       <c r="A24" s="2">
         <v>1134</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="25" ht="13.2" spans="1:30">
+    <row r="25" ht="12.75" spans="1:30">
       <c r="A25" s="2">
         <v>1135</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="26" ht="13.2" spans="1:30">
+    <row r="26" ht="12.75" spans="1:30">
       <c r="A26" s="2">
         <v>1136</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="27" ht="13.2" spans="3:26">
+    <row r="27" ht="12.75" spans="3:26">
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="H27" s="2"/>
@@ -2240,7 +2240,7 @@
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
     </row>
-    <row r="28" ht="13.2" spans="1:33">
+    <row r="28" ht="12.75" spans="1:33">
       <c r="A28" s="2">
         <v>767</v>
       </c>
@@ -2311,7 +2311,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="29" spans="1:33">
+    <row r="29" ht="12.75" spans="1:33">
       <c r="A29" s="2">
         <v>768</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="30" ht="13.2" spans="1:33">
+    <row r="30" ht="12.75" spans="1:33">
       <c r="A30" s="2">
         <v>769</v>
       </c>
@@ -2453,7 +2453,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="31" ht="13.2" spans="1:33">
+    <row r="31" ht="12.75" spans="1:33">
       <c r="A31" s="2">
         <v>770</v>
       </c>
@@ -2524,7 +2524,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="32" ht="13.2" spans="1:33">
+    <row r="32" ht="12.75" spans="1:33">
       <c r="A32" s="2">
         <v>771</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="33" ht="13.2" spans="1:33">
+    <row r="33" ht="12.75" spans="1:33">
       <c r="A33" s="2">
         <v>772</v>
       </c>
@@ -2646,7 +2646,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="34" ht="13.2" spans="1:33">
+    <row r="34" ht="12.75" spans="1:33">
       <c r="A34" s="2">
         <v>773</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="35" ht="13.2" spans="1:33">
+    <row r="35" ht="12.75" spans="1:33">
       <c r="A35" s="2">
         <v>774</v>
       </c>
@@ -2755,7 +2755,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="36" ht="13.2" spans="1:33">
+    <row r="36" ht="12.75" spans="1:33">
       <c r="A36" s="2">
         <v>775</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="37" ht="13.2" spans="1:33">
+    <row r="37" ht="12.75" spans="1:33">
       <c r="A37" s="2">
         <v>776</v>
       </c>
@@ -2859,7 +2859,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="38" ht="13.2" spans="1:33">
+    <row r="38" ht="12.75" spans="1:33">
       <c r="A38" s="2">
         <v>777</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="39" ht="13.2" spans="1:33">
+    <row r="39" spans="1:33">
       <c r="A39" s="2">
         <v>778</v>
       </c>
@@ -2923,9 +2923,7 @@
       <c r="D39" s="2">
         <v>901</v>
       </c>
-      <c r="V39" s="2">
-        <v>886</v>
-      </c>
+      <c r="V39" s="2"/>
       <c r="W39" s="2"/>
       <c r="X39" s="2">
         <v>863</v>
@@ -2950,7 +2948,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="40" ht="13.2" spans="1:33">
+    <row r="40" ht="12.75" spans="1:33">
       <c r="A40" s="2">
         <v>779</v>
       </c>
@@ -2993,9 +2991,7 @@
       </c>
       <c r="R40" s="2"/>
       <c r="S40" s="2"/>
-      <c r="V40" s="2">
-        <v>887</v>
-      </c>
+      <c r="V40" s="2"/>
       <c r="W40" s="2"/>
       <c r="X40" s="2">
         <v>862</v>
@@ -3020,7 +3016,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="41" ht="13.2" spans="1:33">
+    <row r="41" ht="12.75" spans="1:33">
       <c r="A41" s="2">
         <v>780</v>
       </c>
@@ -3090,7 +3086,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="42" ht="13.2" spans="1:33">
+    <row r="42" ht="12.75" spans="1:33">
       <c r="A42" s="2">
         <v>781</v>
       </c>
@@ -3125,7 +3121,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="43" ht="13.2" spans="1:33">
+    <row r="43" ht="12.75" spans="1:33">
       <c r="A43" s="2">
         <v>782</v>
       </c>
@@ -3191,7 +3187,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="44" ht="13.2" spans="1:33">
+    <row r="44" ht="12.75" spans="1:33">
       <c r="A44" s="2">
         <v>783</v>
       </c>
@@ -3257,7 +3253,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="45" ht="13.2" spans="1:33">
+    <row r="45" ht="12.75" spans="1:33">
       <c r="A45" s="2">
         <v>784</v>
       </c>
@@ -3278,7 +3274,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="46" ht="13.2" spans="1:33">
+    <row r="46" ht="12.75" spans="1:33">
       <c r="A46" s="2">
         <v>785</v>
       </c>
@@ -3344,7 +3340,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="47" ht="13.2" spans="1:33">
+    <row r="47" ht="12.75" spans="1:33">
       <c r="A47" s="2">
         <v>786</v>
       </c>
@@ -3367,7 +3363,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="48" ht="13.2" spans="1:26">
+    <row r="48" ht="12.75" spans="1:26">
       <c r="A48" s="2">
         <v>787</v>
       </c>
@@ -3379,7 +3375,7 @@
       <c r="Y48" s="2"/>
       <c r="Z48" s="2"/>
     </row>
-    <row r="49" ht="13.2" spans="1:23">
+    <row r="49" ht="12.75" spans="1:23">
       <c r="A49" s="2">
         <v>788</v>
       </c>
@@ -3405,7 +3401,7 @@
       <c r="V49" s="2"/>
       <c r="W49" s="2"/>
     </row>
-    <row r="50" ht="13.2" spans="1:23">
+    <row r="50" ht="12.75" spans="1:23">
       <c r="A50" s="2">
         <v>789</v>
       </c>
@@ -3431,7 +3427,7 @@
       <c r="V50" s="2"/>
       <c r="W50" s="2"/>
     </row>
-    <row r="51" ht="13.2" spans="1:23">
+    <row r="51" ht="12.75" spans="1:23">
       <c r="A51" s="2">
         <v>794</v>
       </c>
@@ -3457,10 +3453,10 @@
       <c r="V51" s="2"/>
       <c r="W51" s="2"/>
     </row>
-    <row r="52" ht="13.2" spans="22:22">
+    <row r="52" ht="12.75" spans="22:22">
       <c r="V52" s="2"/>
     </row>
-    <row r="53" ht="13.2" spans="3:23">
+    <row r="53" ht="12.75" spans="3:23">
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
@@ -3483,7 +3479,7 @@
       <c r="V53" s="2"/>
       <c r="W53" s="2"/>
     </row>
-    <row r="54" ht="13.2" spans="3:23">
+    <row r="54" ht="12.75" spans="3:23">
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
@@ -3506,7 +3502,7 @@
       <c r="V54" s="2"/>
       <c r="W54" s="2"/>
     </row>
-    <row r="55" ht="13.2" spans="3:23">
+    <row r="55" ht="12.75" spans="3:23">
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
@@ -3529,7 +3525,7 @@
       <c r="V55" s="2"/>
       <c r="W55" s="2"/>
     </row>
-    <row r="56" ht="13.2" spans="3:23">
+    <row r="56" ht="12.75" spans="3:23">
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
@@ -3552,7 +3548,7 @@
       <c r="V56" s="2"/>
       <c r="W56" s="2"/>
     </row>
-    <row r="57" ht="13.2" spans="3:23">
+    <row r="57" ht="12.75" spans="3:23">
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
@@ -3575,7 +3571,7 @@
       <c r="V57" s="2"/>
       <c r="W57" s="2"/>
     </row>
-    <row r="58" ht="13.2" spans="3:23">
+    <row r="58" ht="12.75" spans="3:23">
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -3598,7 +3594,7 @@
       <c r="V58" s="2"/>
       <c r="W58" s="2"/>
     </row>
-    <row r="59" ht="13.2" spans="3:23">
+    <row r="59" ht="12.75" spans="3:23">
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
@@ -3621,7 +3617,7 @@
       <c r="V59" s="2"/>
       <c r="W59" s="2"/>
     </row>
-    <row r="60" ht="13.2" spans="3:23">
+    <row r="60" ht="12.75" spans="3:23">
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
@@ -3644,7 +3640,7 @@
       <c r="V60" s="2"/>
       <c r="W60" s="2"/>
     </row>
-    <row r="61" ht="13.2" spans="3:23">
+    <row r="61" ht="12.75" spans="3:23">
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
@@ -3667,7 +3663,7 @@
       <c r="V61" s="2"/>
       <c r="W61" s="2"/>
     </row>
-    <row r="62" ht="13.2" spans="3:23">
+    <row r="62" ht="12.75" spans="3:23">
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
@@ -3690,7 +3686,7 @@
       <c r="V62" s="2"/>
       <c r="W62" s="2"/>
     </row>
-    <row r="63" ht="13.2" spans="3:23">
+    <row r="63" ht="12.75" spans="3:23">
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
@@ -3713,7 +3709,7 @@
       <c r="V63" s="2"/>
       <c r="W63" s="2"/>
     </row>
-    <row r="64" ht="13.2" spans="3:23">
+    <row r="64" ht="12.75" spans="3:23">
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
@@ -3736,7 +3732,7 @@
       <c r="V64" s="2"/>
       <c r="W64" s="2"/>
     </row>
-    <row r="65" ht="13.2" spans="3:23">
+    <row r="65" ht="12.75" spans="3:23">
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
@@ -3759,7 +3755,7 @@
       <c r="V65" s="2"/>
       <c r="W65" s="2"/>
     </row>
-    <row r="66" ht="13.2" spans="3:23">
+    <row r="66" ht="12.75" spans="3:23">
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
@@ -3782,7 +3778,7 @@
       <c r="V66" s="2"/>
       <c r="W66" s="2"/>
     </row>
-    <row r="67" ht="13.2" spans="3:23">
+    <row r="67" ht="12.75" spans="3:23">
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
@@ -3805,7 +3801,7 @@
       <c r="V67" s="2"/>
       <c r="W67" s="2"/>
     </row>
-    <row r="68" ht="13.2" spans="3:23">
+    <row r="68" ht="12.75" spans="3:23">
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
@@ -3828,7 +3824,7 @@
       <c r="V68" s="2"/>
       <c r="W68" s="2"/>
     </row>
-    <row r="69" ht="13.2" spans="3:23">
+    <row r="69" ht="12.75" spans="3:23">
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
@@ -3851,7 +3847,7 @@
       <c r="V69" s="2"/>
       <c r="W69" s="2"/>
     </row>
-    <row r="70" ht="13.2" spans="3:23">
+    <row r="70" ht="12.75" spans="3:23">
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
@@ -3874,7 +3870,7 @@
       <c r="V70" s="2"/>
       <c r="W70" s="2"/>
     </row>
-    <row r="71" ht="13.2" spans="3:23">
+    <row r="71" ht="12.75" spans="3:23">
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
@@ -3897,7 +3893,7 @@
       <c r="V71" s="2"/>
       <c r="W71" s="2"/>
     </row>
-    <row r="72" ht="13.2" spans="3:23">
+    <row r="72" ht="12.75" spans="3:23">
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
@@ -3920,7 +3916,7 @@
       <c r="V72" s="2"/>
       <c r="W72" s="2"/>
     </row>
-    <row r="73" ht="13.2" spans="3:23">
+    <row r="73" ht="12.75" spans="3:23">
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
@@ -3943,7 +3939,7 @@
       <c r="V73" s="2"/>
       <c r="W73" s="2"/>
     </row>
-    <row r="74" ht="13.2" spans="3:23">
+    <row r="74" ht="12.75" spans="3:23">
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
@@ -3966,7 +3962,7 @@
       <c r="V74" s="2"/>
       <c r="W74" s="2"/>
     </row>
-    <row r="75" ht="13.2" spans="3:23">
+    <row r="75" ht="12.75" spans="3:23">
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
@@ -3989,7 +3985,7 @@
       <c r="V75" s="2"/>
       <c r="W75" s="2"/>
     </row>
-    <row r="76" ht="13.2" spans="3:23">
+    <row r="76" ht="12.75" spans="3:23">
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
@@ -4012,7 +4008,7 @@
       <c r="V76" s="2"/>
       <c r="W76" s="2"/>
     </row>
-    <row r="77" ht="13.2" spans="3:23">
+    <row r="77" ht="12.75" spans="3:23">
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
@@ -4035,7 +4031,7 @@
       <c r="V77" s="2"/>
       <c r="W77" s="2"/>
     </row>
-    <row r="78" ht="13.2" spans="3:23">
+    <row r="78" ht="12.75" spans="3:23">
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
@@ -4058,7 +4054,7 @@
       <c r="V78" s="2"/>
       <c r="W78" s="2"/>
     </row>
-    <row r="79" ht="13.2" spans="3:23">
+    <row r="79" ht="12.75" spans="3:23">
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
@@ -4081,7 +4077,7 @@
       <c r="V79" s="2"/>
       <c r="W79" s="2"/>
     </row>
-    <row r="80" ht="13.2" spans="3:23">
+    <row r="80" ht="12.75" spans="3:23">
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
@@ -4104,7 +4100,7 @@
       <c r="V80" s="2"/>
       <c r="W80" s="2"/>
     </row>
-    <row r="81" ht="13.2" spans="3:23">
+    <row r="81" ht="12.75" spans="3:23">
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
@@ -4127,7 +4123,7 @@
       <c r="V81" s="2"/>
       <c r="W81" s="2"/>
     </row>
-    <row r="82" ht="13.2" spans="3:23">
+    <row r="82" ht="12.75" spans="3:23">
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
@@ -4150,7 +4146,7 @@
       <c r="V82" s="2"/>
       <c r="W82" s="2"/>
     </row>
-    <row r="83" ht="13.2" spans="3:23">
+    <row r="83" ht="12.75" spans="3:23">
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
       <c r="E83" s="2"/>
@@ -4173,7 +4169,7 @@
       <c r="V83" s="2"/>
       <c r="W83" s="2"/>
     </row>
-    <row r="84" ht="13.2" spans="3:23">
+    <row r="84" ht="12.75" spans="3:23">
       <c r="C84" s="2"/>
       <c r="D84" s="2"/>
       <c r="E84" s="2"/>
@@ -4196,7 +4192,7 @@
       <c r="V84" s="2"/>
       <c r="W84" s="2"/>
     </row>
-    <row r="85" ht="13.2" spans="3:23">
+    <row r="85" ht="12.75" spans="3:23">
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
       <c r="E85" s="2"/>
@@ -4219,7 +4215,7 @@
       <c r="V85" s="2"/>
       <c r="W85" s="2"/>
     </row>
-    <row r="86" ht="13.2" spans="3:23">
+    <row r="86" ht="12.75" spans="3:23">
       <c r="C86" s="2"/>
       <c r="D86" s="2"/>
       <c r="E86" s="2"/>
@@ -4242,7 +4238,7 @@
       <c r="V86" s="2"/>
       <c r="W86" s="2"/>
     </row>
-    <row r="87" ht="13.2" spans="3:23">
+    <row r="87" ht="12.75" spans="3:23">
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
       <c r="E87" s="2"/>
@@ -4265,7 +4261,7 @@
       <c r="V87" s="2"/>
       <c r="W87" s="2"/>
     </row>
-    <row r="88" ht="13.2" spans="3:23">
+    <row r="88" ht="12.75" spans="3:23">
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
       <c r="E88" s="2"/>
@@ -4288,7 +4284,7 @@
       <c r="V88" s="2"/>
       <c r="W88" s="2"/>
     </row>
-    <row r="89" ht="13.2" spans="3:23">
+    <row r="89" ht="12.75" spans="3:23">
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
       <c r="E89" s="2"/>
@@ -4311,7 +4307,7 @@
       <c r="V89" s="2"/>
       <c r="W89" s="2"/>
     </row>
-    <row r="90" ht="13.2" spans="3:23">
+    <row r="90" ht="12.75" spans="3:23">
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
@@ -4334,7 +4330,7 @@
       <c r="V90" s="2"/>
       <c r="W90" s="2"/>
     </row>
-    <row r="91" ht="13.2" spans="3:23">
+    <row r="91" ht="12.75" spans="3:23">
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
@@ -4357,7 +4353,7 @@
       <c r="V91" s="2"/>
       <c r="W91" s="2"/>
     </row>
-    <row r="92" ht="13.2" spans="3:23">
+    <row r="92" ht="12.75" spans="3:23">
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
@@ -4380,7 +4376,7 @@
       <c r="V92" s="2"/>
       <c r="W92" s="2"/>
     </row>
-    <row r="93" ht="13.2" spans="3:23">
+    <row r="93" ht="12.75" spans="3:23">
       <c r="C93" s="2"/>
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
@@ -4403,7 +4399,7 @@
       <c r="V93" s="2"/>
       <c r="W93" s="2"/>
     </row>
-    <row r="94" ht="13.2" spans="3:23">
+    <row r="94" ht="12.75" spans="3:23">
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
       <c r="E94" s="2"/>
@@ -4426,7 +4422,7 @@
       <c r="V94" s="2"/>
       <c r="W94" s="2"/>
     </row>
-    <row r="95" ht="13.2" spans="3:23">
+    <row r="95" ht="12.75" spans="3:23">
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
       <c r="E95" s="2"/>
@@ -4449,7 +4445,7 @@
       <c r="V95" s="2"/>
       <c r="W95" s="2"/>
     </row>
-    <row r="96" ht="13.2" spans="3:23">
+    <row r="96" ht="12.75" spans="3:23">
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
       <c r="E96" s="2"/>
@@ -4472,7 +4468,7 @@
       <c r="V96" s="2"/>
       <c r="W96" s="2"/>
     </row>
-    <row r="97" ht="13.2" spans="3:23">
+    <row r="97" ht="12.75" spans="3:23">
       <c r="C97" s="2"/>
       <c r="D97" s="2"/>
       <c r="E97" s="2"/>
@@ -4495,7 +4491,7 @@
       <c r="V97" s="2"/>
       <c r="W97" s="2"/>
     </row>
-    <row r="98" ht="13.2" spans="3:23">
+    <row r="98" ht="12.75" spans="3:23">
       <c r="C98" s="2"/>
       <c r="D98" s="2"/>
       <c r="E98" s="2"/>
@@ -4518,7 +4514,7 @@
       <c r="V98" s="2"/>
       <c r="W98" s="2"/>
     </row>
-    <row r="99" ht="13.2" spans="3:23">
+    <row r="99" ht="12.75" spans="3:23">
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
@@ -4541,7 +4537,7 @@
       <c r="V99" s="2"/>
       <c r="W99" s="2"/>
     </row>
-    <row r="100" ht="13.2" spans="3:23">
+    <row r="100" ht="12.75" spans="3:23">
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
       <c r="E100" s="2"/>
@@ -4564,7 +4560,7 @@
       <c r="V100" s="2"/>
       <c r="W100" s="2"/>
     </row>
-    <row r="101" ht="13.2" spans="3:23">
+    <row r="101" ht="12.75" spans="3:23">
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
       <c r="E101" s="2"/>
@@ -4587,7 +4583,7 @@
       <c r="V101" s="2"/>
       <c r="W101" s="2"/>
     </row>
-    <row r="102" ht="13.2" spans="3:23">
+    <row r="102" ht="12.75" spans="3:23">
       <c r="C102" s="2"/>
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
@@ -4610,7 +4606,7 @@
       <c r="V102" s="2"/>
       <c r="W102" s="2"/>
     </row>
-    <row r="103" ht="13.2" spans="3:23">
+    <row r="103" ht="12.75" spans="3:23">
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
@@ -4633,7 +4629,7 @@
       <c r="V103" s="2"/>
       <c r="W103" s="2"/>
     </row>
-    <row r="104" ht="13.2" spans="3:23">
+    <row r="104" ht="12.75" spans="3:23">
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
       <c r="E104" s="2"/>
@@ -4656,7 +4652,7 @@
       <c r="V104" s="2"/>
       <c r="W104" s="2"/>
     </row>
-    <row r="105" ht="13.2" spans="3:23">
+    <row r="105" ht="12.75" spans="3:23">
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
       <c r="E105" s="2"/>
@@ -4679,7 +4675,7 @@
       <c r="V105" s="2"/>
       <c r="W105" s="2"/>
     </row>
-    <row r="106" ht="13.2" spans="3:23">
+    <row r="106" ht="12.75" spans="3:23">
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
       <c r="E106" s="2"/>
@@ -4702,7 +4698,7 @@
       <c r="V106" s="2"/>
       <c r="W106" s="2"/>
     </row>
-    <row r="107" ht="13.2" spans="3:23">
+    <row r="107" ht="12.75" spans="3:23">
       <c r="C107" s="2"/>
       <c r="D107" s="2"/>
       <c r="E107" s="2"/>
@@ -4725,7 +4721,7 @@
       <c r="V107" s="2"/>
       <c r="W107" s="2"/>
     </row>
-    <row r="108" ht="13.2" spans="3:23">
+    <row r="108" ht="12.75" spans="3:23">
       <c r="C108" s="2"/>
       <c r="D108" s="2"/>
       <c r="E108" s="2"/>
@@ -4748,7 +4744,7 @@
       <c r="V108" s="2"/>
       <c r="W108" s="2"/>
     </row>
-    <row r="109" ht="13.2" spans="3:23">
+    <row r="109" ht="12.75" spans="3:23">
       <c r="C109" s="2"/>
       <c r="D109" s="2"/>
       <c r="E109" s="2"/>
@@ -4771,7 +4767,7 @@
       <c r="V109" s="2"/>
       <c r="W109" s="2"/>
     </row>
-    <row r="110" ht="13.2" spans="3:23">
+    <row r="110" ht="12.75" spans="3:23">
       <c r="C110" s="2"/>
       <c r="D110" s="2"/>
       <c r="E110" s="2"/>
@@ -4794,7 +4790,7 @@
       <c r="V110" s="2"/>
       <c r="W110" s="2"/>
     </row>
-    <row r="111" ht="13.2" spans="3:23">
+    <row r="111" ht="12.75" spans="3:23">
       <c r="C111" s="2"/>
       <c r="D111" s="2"/>
       <c r="E111" s="2"/>
@@ -4817,7 +4813,7 @@
       <c r="V111" s="2"/>
       <c r="W111" s="2"/>
     </row>
-    <row r="112" ht="13.2" spans="3:23">
+    <row r="112" ht="12.75" spans="3:23">
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
       <c r="E112" s="2"/>
@@ -4840,7 +4836,7 @@
       <c r="V112" s="2"/>
       <c r="W112" s="2"/>
     </row>
-    <row r="113" ht="13.2" spans="3:23">
+    <row r="113" ht="12.75" spans="3:23">
       <c r="C113" s="2"/>
       <c r="D113" s="2"/>
       <c r="E113" s="2"/>
@@ -4863,7 +4859,7 @@
       <c r="V113" s="2"/>
       <c r="W113" s="2"/>
     </row>
-    <row r="114" ht="13.2" spans="3:23">
+    <row r="114" ht="12.75" spans="3:23">
       <c r="C114" s="2"/>
       <c r="D114" s="2"/>
       <c r="E114" s="2"/>
@@ -4886,7 +4882,7 @@
       <c r="V114" s="2"/>
       <c r="W114" s="2"/>
     </row>
-    <row r="115" ht="13.2" spans="3:23">
+    <row r="115" ht="12.75" spans="3:23">
       <c r="C115" s="2"/>
       <c r="D115" s="2"/>
       <c r="E115" s="2"/>
@@ -4909,7 +4905,7 @@
       <c r="V115" s="2"/>
       <c r="W115" s="2"/>
     </row>
-    <row r="116" ht="13.2" spans="3:23">
+    <row r="116" ht="12.75" spans="3:23">
       <c r="C116" s="2"/>
       <c r="D116" s="2"/>
       <c r="E116" s="2"/>
@@ -4932,7 +4928,7 @@
       <c r="V116" s="2"/>
       <c r="W116" s="2"/>
     </row>
-    <row r="117" ht="13.2" spans="3:23">
+    <row r="117" ht="12.75" spans="3:23">
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
       <c r="E117" s="2"/>
@@ -4955,7 +4951,7 @@
       <c r="V117" s="2"/>
       <c r="W117" s="2"/>
     </row>
-    <row r="118" ht="13.2" spans="3:23">
+    <row r="118" ht="12.75" spans="3:23">
       <c r="C118" s="2"/>
       <c r="D118" s="2"/>
       <c r="E118" s="2"/>
@@ -4978,7 +4974,7 @@
       <c r="V118" s="2"/>
       <c r="W118" s="2"/>
     </row>
-    <row r="119" ht="13.2" spans="3:23">
+    <row r="119" ht="12.75" spans="3:23">
       <c r="C119" s="2"/>
       <c r="D119" s="2"/>
       <c r="E119" s="2"/>
@@ -5001,7 +4997,7 @@
       <c r="V119" s="2"/>
       <c r="W119" s="2"/>
     </row>
-    <row r="120" ht="13.2" spans="3:23">
+    <row r="120" ht="12.75" spans="3:23">
       <c r="C120" s="2"/>
       <c r="D120" s="2"/>
       <c r="E120" s="2"/>
@@ -5024,7 +5020,7 @@
       <c r="V120" s="2"/>
       <c r="W120" s="2"/>
     </row>
-    <row r="121" ht="13.2" spans="3:23">
+    <row r="121" ht="12.75" spans="3:23">
       <c r="C121" s="2"/>
       <c r="D121" s="2"/>
       <c r="E121" s="2"/>
@@ -5047,7 +5043,7 @@
       <c r="V121" s="2"/>
       <c r="W121" s="2"/>
     </row>
-    <row r="122" ht="13.2" spans="3:23">
+    <row r="122" ht="12.75" spans="3:23">
       <c r="C122" s="2"/>
       <c r="D122" s="2"/>
       <c r="E122" s="2"/>
@@ -5070,7 +5066,7 @@
       <c r="V122" s="2"/>
       <c r="W122" s="2"/>
     </row>
-    <row r="123" ht="13.2" spans="3:23">
+    <row r="123" ht="12.75" spans="3:23">
       <c r="C123" s="2"/>
       <c r="D123" s="2"/>
       <c r="E123" s="2"/>
@@ -5093,7 +5089,7 @@
       <c r="V123" s="2"/>
       <c r="W123" s="2"/>
     </row>
-    <row r="124" ht="13.2" spans="3:23">
+    <row r="124" ht="12.75" spans="3:23">
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
       <c r="E124" s="2"/>
@@ -5116,7 +5112,7 @@
       <c r="V124" s="2"/>
       <c r="W124" s="2"/>
     </row>
-    <row r="125" ht="13.2" spans="3:23">
+    <row r="125" ht="12.75" spans="3:23">
       <c r="C125" s="2"/>
       <c r="D125" s="2"/>
       <c r="E125" s="2"/>
@@ -5139,7 +5135,7 @@
       <c r="V125" s="2"/>
       <c r="W125" s="2"/>
     </row>
-    <row r="126" ht="13.2" spans="3:23">
+    <row r="126" ht="12.75" spans="3:23">
       <c r="C126" s="2"/>
       <c r="D126" s="2"/>
       <c r="E126" s="2"/>
@@ -5162,7 +5158,7 @@
       <c r="V126" s="2"/>
       <c r="W126" s="2"/>
     </row>
-    <row r="127" ht="13.2" spans="3:23">
+    <row r="127" ht="12.75" spans="3:23">
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
       <c r="E127" s="2"/>
@@ -5185,7 +5181,7 @@
       <c r="V127" s="2"/>
       <c r="W127" s="2"/>
     </row>
-    <row r="128" ht="13.2" spans="3:23">
+    <row r="128" ht="12.75" spans="3:23">
       <c r="C128" s="2"/>
       <c r="D128" s="2"/>
       <c r="E128" s="2"/>
@@ -5208,7 +5204,7 @@
       <c r="V128" s="2"/>
       <c r="W128" s="2"/>
     </row>
-    <row r="129" ht="13.2" spans="3:23">
+    <row r="129" ht="12.75" spans="3:23">
       <c r="C129" s="2"/>
       <c r="D129" s="2"/>
       <c r="E129" s="2"/>
@@ -5231,7 +5227,7 @@
       <c r="V129" s="2"/>
       <c r="W129" s="2"/>
     </row>
-    <row r="130" ht="13.2" spans="3:23">
+    <row r="130" ht="12.75" spans="3:23">
       <c r="C130" s="2"/>
       <c r="D130" s="2"/>
       <c r="E130" s="2"/>
@@ -5254,7 +5250,7 @@
       <c r="V130" s="2"/>
       <c r="W130" s="2"/>
     </row>
-    <row r="131" ht="13.2" spans="3:23">
+    <row r="131" ht="12.75" spans="3:23">
       <c r="C131" s="2"/>
       <c r="D131" s="2"/>
       <c r="E131" s="2"/>
@@ -5277,7 +5273,7 @@
       <c r="V131" s="2"/>
       <c r="W131" s="2"/>
     </row>
-    <row r="132" ht="13.2" spans="3:23">
+    <row r="132" ht="12.75" spans="3:23">
       <c r="C132" s="2"/>
       <c r="D132" s="2"/>
       <c r="E132" s="2"/>
@@ -5300,7 +5296,7 @@
       <c r="V132" s="2"/>
       <c r="W132" s="2"/>
     </row>
-    <row r="133" ht="13.2" spans="3:23">
+    <row r="133" ht="12.75" spans="3:23">
       <c r="C133" s="2"/>
       <c r="D133" s="2"/>
       <c r="E133" s="2"/>
@@ -5323,7 +5319,7 @@
       <c r="V133" s="2"/>
       <c r="W133" s="2"/>
     </row>
-    <row r="134" ht="13.2" spans="3:23">
+    <row r="134" ht="12.75" spans="3:23">
       <c r="C134" s="2"/>
       <c r="D134" s="2"/>
       <c r="E134" s="2"/>
@@ -5346,7 +5342,7 @@
       <c r="V134" s="2"/>
       <c r="W134" s="2"/>
     </row>
-    <row r="135" ht="13.2" spans="3:23">
+    <row r="135" ht="12.75" spans="3:23">
       <c r="C135" s="2"/>
       <c r="D135" s="2"/>
       <c r="E135" s="2"/>
@@ -5369,7 +5365,7 @@
       <c r="V135" s="2"/>
       <c r="W135" s="2"/>
     </row>
-    <row r="136" ht="13.2" spans="3:23">
+    <row r="136" ht="12.75" spans="3:23">
       <c r="C136" s="2"/>
       <c r="D136" s="2"/>
       <c r="E136" s="2"/>
@@ -5392,7 +5388,7 @@
       <c r="V136" s="2"/>
       <c r="W136" s="2"/>
     </row>
-    <row r="137" ht="13.2" spans="3:23">
+    <row r="137" ht="12.75" spans="3:23">
       <c r="C137" s="2"/>
       <c r="D137" s="2"/>
       <c r="E137" s="2"/>
@@ -5415,7 +5411,7 @@
       <c r="V137" s="2"/>
       <c r="W137" s="2"/>
     </row>
-    <row r="138" ht="13.2" spans="3:23">
+    <row r="138" ht="12.75" spans="3:23">
       <c r="C138" s="2"/>
       <c r="D138" s="2"/>
       <c r="E138" s="2"/>
@@ -5438,7 +5434,7 @@
       <c r="V138" s="2"/>
       <c r="W138" s="2"/>
     </row>
-    <row r="139" ht="13.2" spans="3:23">
+    <row r="139" ht="12.75" spans="3:23">
       <c r="C139" s="2"/>
       <c r="D139" s="2"/>
       <c r="E139" s="2"/>
@@ -5461,7 +5457,7 @@
       <c r="V139" s="2"/>
       <c r="W139" s="2"/>
     </row>
-    <row r="140" ht="13.2" spans="3:23">
+    <row r="140" ht="12.75" spans="3:23">
       <c r="C140" s="2"/>
       <c r="D140" s="2"/>
       <c r="E140" s="2"/>
@@ -5484,7 +5480,7 @@
       <c r="V140" s="2"/>
       <c r="W140" s="2"/>
     </row>
-    <row r="141" ht="13.2" spans="3:23">
+    <row r="141" ht="12.75" spans="3:23">
       <c r="C141" s="2"/>
       <c r="D141" s="2"/>
       <c r="E141" s="2"/>
@@ -5507,7 +5503,7 @@
       <c r="V141" s="2"/>
       <c r="W141" s="2"/>
     </row>
-    <row r="142" ht="13.2" spans="3:23">
+    <row r="142" ht="12.75" spans="3:23">
       <c r="C142" s="2"/>
       <c r="D142" s="2"/>
       <c r="E142" s="2"/>
@@ -5530,7 +5526,7 @@
       <c r="V142" s="2"/>
       <c r="W142" s="2"/>
     </row>
-    <row r="143" ht="13.2" spans="3:23">
+    <row r="143" ht="12.75" spans="3:23">
       <c r="C143" s="2"/>
       <c r="D143" s="2"/>
       <c r="E143" s="2"/>
@@ -5553,7 +5549,7 @@
       <c r="V143" s="2"/>
       <c r="W143" s="2"/>
     </row>
-    <row r="144" ht="13.2" spans="3:23">
+    <row r="144" ht="12.75" spans="3:23">
       <c r="C144" s="2"/>
       <c r="D144" s="2"/>
       <c r="E144" s="2"/>
@@ -5576,7 +5572,7 @@
       <c r="V144" s="2"/>
       <c r="W144" s="2"/>
     </row>
-    <row r="145" ht="13.2" spans="3:23">
+    <row r="145" ht="12.75" spans="3:23">
       <c r="C145" s="2"/>
       <c r="D145" s="2"/>
       <c r="E145" s="2"/>
@@ -5599,7 +5595,7 @@
       <c r="V145" s="2"/>
       <c r="W145" s="2"/>
     </row>
-    <row r="146" ht="13.2" spans="3:23">
+    <row r="146" ht="12.75" spans="3:23">
       <c r="C146" s="2"/>
       <c r="D146" s="2"/>
       <c r="E146" s="2"/>
@@ -5622,7 +5618,7 @@
       <c r="V146" s="2"/>
       <c r="W146" s="2"/>
     </row>
-    <row r="147" ht="13.2" spans="3:23">
+    <row r="147" ht="12.75" spans="3:23">
       <c r="C147" s="2"/>
       <c r="D147" s="2"/>
       <c r="E147" s="2"/>
@@ -5645,7 +5641,7 @@
       <c r="V147" s="2"/>
       <c r="W147" s="2"/>
     </row>
-    <row r="148" ht="13.2" spans="3:23">
+    <row r="148" ht="12.75" spans="3:23">
       <c r="C148" s="2"/>
       <c r="D148" s="2"/>
       <c r="E148" s="2"/>
@@ -5668,7 +5664,7 @@
       <c r="V148" s="2"/>
       <c r="W148" s="2"/>
     </row>
-    <row r="149" ht="13.2" spans="3:23">
+    <row r="149" ht="12.75" spans="3:23">
       <c r="C149" s="2"/>
       <c r="D149" s="2"/>
       <c r="E149" s="2"/>
@@ -5691,7 +5687,7 @@
       <c r="V149" s="2"/>
       <c r="W149" s="2"/>
     </row>
-    <row r="150" ht="13.2" spans="3:23">
+    <row r="150" ht="12.75" spans="3:23">
       <c r="C150" s="2"/>
       <c r="D150" s="2"/>
       <c r="E150" s="2"/>
@@ -5714,7 +5710,7 @@
       <c r="V150" s="2"/>
       <c r="W150" s="2"/>
     </row>
-    <row r="151" ht="13.2" spans="3:23">
+    <row r="151" ht="12.75" spans="3:23">
       <c r="C151" s="2"/>
       <c r="D151" s="2"/>
       <c r="E151" s="2"/>
@@ -5737,7 +5733,7 @@
       <c r="V151" s="2"/>
       <c r="W151" s="2"/>
     </row>
-    <row r="152" ht="13.2" spans="3:23">
+    <row r="152" ht="12.75" spans="3:23">
       <c r="C152" s="2"/>
       <c r="D152" s="2"/>
       <c r="E152" s="2"/>
@@ -5760,7 +5756,7 @@
       <c r="V152" s="2"/>
       <c r="W152" s="2"/>
     </row>
-    <row r="153" ht="13.2" spans="3:23">
+    <row r="153" ht="12.75" spans="3:23">
       <c r="C153" s="2"/>
       <c r="D153" s="2"/>
       <c r="E153" s="2"/>
@@ -5783,7 +5779,7 @@
       <c r="V153" s="2"/>
       <c r="W153" s="2"/>
     </row>
-    <row r="154" ht="13.2" spans="3:23">
+    <row r="154" ht="12.75" spans="3:23">
       <c r="C154" s="2"/>
       <c r="D154" s="2"/>
       <c r="E154" s="2"/>
@@ -5806,7 +5802,7 @@
       <c r="V154" s="2"/>
       <c r="W154" s="2"/>
     </row>
-    <row r="155" ht="13.2" spans="3:23">
+    <row r="155" ht="12.75" spans="3:23">
       <c r="C155" s="2"/>
       <c r="D155" s="2"/>
       <c r="E155" s="2"/>
@@ -5829,7 +5825,7 @@
       <c r="V155" s="2"/>
       <c r="W155" s="2"/>
     </row>
-    <row r="156" ht="13.2" spans="3:23">
+    <row r="156" ht="12.75" spans="3:23">
       <c r="C156" s="2"/>
       <c r="D156" s="2"/>
       <c r="E156" s="2"/>
@@ -5852,7 +5848,7 @@
       <c r="V156" s="2"/>
       <c r="W156" s="2"/>
     </row>
-    <row r="157" ht="13.2" spans="3:23">
+    <row r="157" ht="12.75" spans="3:23">
       <c r="C157" s="2"/>
       <c r="D157" s="2"/>
       <c r="E157" s="2"/>
@@ -5875,7 +5871,7 @@
       <c r="V157" s="2"/>
       <c r="W157" s="2"/>
     </row>
-    <row r="158" ht="13.2" spans="3:23">
+    <row r="158" ht="12.75" spans="3:23">
       <c r="C158" s="2"/>
       <c r="D158" s="2"/>
       <c r="E158" s="2"/>
@@ -5898,7 +5894,7 @@
       <c r="V158" s="2"/>
       <c r="W158" s="2"/>
     </row>
-    <row r="159" ht="13.2" spans="3:23">
+    <row r="159" ht="12.75" spans="3:23">
       <c r="C159" s="2"/>
       <c r="D159" s="2"/>
       <c r="E159" s="2"/>
@@ -5921,7 +5917,7 @@
       <c r="V159" s="2"/>
       <c r="W159" s="2"/>
     </row>
-    <row r="160" ht="13.2" spans="3:23">
+    <row r="160" ht="12.75" spans="3:23">
       <c r="C160" s="2"/>
       <c r="D160" s="2"/>
       <c r="E160" s="2"/>
@@ -5944,7 +5940,7 @@
       <c r="V160" s="2"/>
       <c r="W160" s="2"/>
     </row>
-    <row r="161" ht="13.2" spans="3:23">
+    <row r="161" ht="12.75" spans="3:23">
       <c r="C161" s="2"/>
       <c r="D161" s="2"/>
       <c r="E161" s="2"/>
@@ -5967,7 +5963,7 @@
       <c r="V161" s="2"/>
       <c r="W161" s="2"/>
     </row>
-    <row r="162" ht="13.2" spans="3:23">
+    <row r="162" ht="12.75" spans="3:23">
       <c r="C162" s="2"/>
       <c r="D162" s="2"/>
       <c r="E162" s="2"/>
@@ -5990,7 +5986,7 @@
       <c r="V162" s="2"/>
       <c r="W162" s="2"/>
     </row>
-    <row r="163" ht="13.2" spans="3:23">
+    <row r="163" ht="12.75" spans="3:23">
       <c r="C163" s="2"/>
       <c r="D163" s="2"/>
       <c r="E163" s="2"/>
@@ -6013,7 +6009,7 @@
       <c r="V163" s="2"/>
       <c r="W163" s="2"/>
     </row>
-    <row r="164" ht="13.2" spans="3:23">
+    <row r="164" ht="12.75" spans="3:23">
       <c r="C164" s="2"/>
       <c r="D164" s="2"/>
       <c r="E164" s="2"/>
@@ -6036,7 +6032,7 @@
       <c r="V164" s="2"/>
       <c r="W164" s="2"/>
     </row>
-    <row r="165" ht="13.2" spans="3:23">
+    <row r="165" ht="12.75" spans="3:23">
       <c r="C165" s="2"/>
       <c r="D165" s="2"/>
       <c r="E165" s="2"/>
@@ -6059,7 +6055,7 @@
       <c r="V165" s="2"/>
       <c r="W165" s="2"/>
     </row>
-    <row r="166" ht="13.2" spans="3:23">
+    <row r="166" ht="12.75" spans="3:23">
       <c r="C166" s="2"/>
       <c r="D166" s="2"/>
       <c r="E166" s="2"/>
@@ -6082,7 +6078,7 @@
       <c r="V166" s="2"/>
       <c r="W166" s="2"/>
     </row>
-    <row r="167" ht="13.2" spans="3:23">
+    <row r="167" ht="12.75" spans="3:23">
       <c r="C167" s="2"/>
       <c r="D167" s="2"/>
       <c r="E167" s="2"/>
@@ -6105,7 +6101,7 @@
       <c r="V167" s="2"/>
       <c r="W167" s="2"/>
     </row>
-    <row r="168" ht="13.2" spans="3:23">
+    <row r="168" ht="12.75" spans="3:23">
       <c r="C168" s="2"/>
       <c r="D168" s="2"/>
       <c r="E168" s="2"/>
@@ -6128,7 +6124,7 @@
       <c r="V168" s="2"/>
       <c r="W168" s="2"/>
     </row>
-    <row r="169" ht="13.2" spans="3:23">
+    <row r="169" ht="12.75" spans="3:23">
       <c r="C169" s="2"/>
       <c r="D169" s="2"/>
       <c r="E169" s="2"/>
@@ -6151,7 +6147,7 @@
       <c r="V169" s="2"/>
       <c r="W169" s="2"/>
     </row>
-    <row r="170" ht="13.2" spans="3:23">
+    <row r="170" ht="12.75" spans="3:23">
       <c r="C170" s="2"/>
       <c r="D170" s="2"/>
       <c r="E170" s="2"/>
@@ -6174,7 +6170,7 @@
       <c r="V170" s="2"/>
       <c r="W170" s="2"/>
     </row>
-    <row r="171" ht="13.2" spans="3:23">
+    <row r="171" ht="12.75" spans="3:23">
       <c r="C171" s="2"/>
       <c r="D171" s="2"/>
       <c r="E171" s="2"/>
@@ -6197,7 +6193,7 @@
       <c r="V171" s="2"/>
       <c r="W171" s="2"/>
     </row>
-    <row r="172" ht="13.2" spans="3:23">
+    <row r="172" ht="12.75" spans="3:23">
       <c r="C172" s="2"/>
       <c r="D172" s="2"/>
       <c r="E172" s="2"/>
@@ -6220,7 +6216,7 @@
       <c r="V172" s="2"/>
       <c r="W172" s="2"/>
     </row>
-    <row r="173" ht="13.2" spans="3:23">
+    <row r="173" ht="12.75" spans="3:23">
       <c r="C173" s="2"/>
       <c r="D173" s="2"/>
       <c r="E173" s="2"/>
@@ -6243,7 +6239,7 @@
       <c r="V173" s="2"/>
       <c r="W173" s="2"/>
     </row>
-    <row r="174" ht="13.2" spans="3:23">
+    <row r="174" ht="12.75" spans="3:23">
       <c r="C174" s="2"/>
       <c r="D174" s="2"/>
       <c r="E174" s="2"/>
@@ -6266,7 +6262,7 @@
       <c r="V174" s="2"/>
       <c r="W174" s="2"/>
     </row>
-    <row r="175" ht="13.2" spans="3:23">
+    <row r="175" ht="12.75" spans="3:23">
       <c r="C175" s="2"/>
       <c r="D175" s="2"/>
       <c r="E175" s="2"/>
@@ -6289,7 +6285,7 @@
       <c r="V175" s="2"/>
       <c r="W175" s="2"/>
     </row>
-    <row r="176" ht="13.2" spans="3:23">
+    <row r="176" ht="12.75" spans="3:23">
       <c r="C176" s="2"/>
       <c r="D176" s="2"/>
       <c r="E176" s="2"/>
@@ -6312,7 +6308,7 @@
       <c r="V176" s="2"/>
       <c r="W176" s="2"/>
     </row>
-    <row r="177" ht="13.2" spans="3:23">
+    <row r="177" ht="12.75" spans="3:23">
       <c r="C177" s="2"/>
       <c r="D177" s="2"/>
       <c r="E177" s="2"/>
@@ -6335,7 +6331,7 @@
       <c r="V177" s="2"/>
       <c r="W177" s="2"/>
     </row>
-    <row r="178" ht="13.2" spans="3:23">
+    <row r="178" ht="12.75" spans="3:23">
       <c r="C178" s="2"/>
       <c r="D178" s="2"/>
       <c r="E178" s="2"/>
@@ -6358,7 +6354,7 @@
       <c r="V178" s="2"/>
       <c r="W178" s="2"/>
     </row>
-    <row r="179" ht="13.2" spans="3:23">
+    <row r="179" ht="12.75" spans="3:23">
       <c r="C179" s="2"/>
       <c r="D179" s="2"/>
       <c r="E179" s="2"/>
@@ -6381,7 +6377,7 @@
       <c r="V179" s="2"/>
       <c r="W179" s="2"/>
     </row>
-    <row r="180" ht="13.2" spans="3:23">
+    <row r="180" ht="12.75" spans="3:23">
       <c r="C180" s="2"/>
       <c r="D180" s="2"/>
       <c r="E180" s="2"/>
@@ -6404,7 +6400,7 @@
       <c r="V180" s="2"/>
       <c r="W180" s="2"/>
     </row>
-    <row r="181" ht="13.2" spans="3:23">
+    <row r="181" ht="12.75" spans="3:23">
       <c r="C181" s="2"/>
       <c r="D181" s="2"/>
       <c r="E181" s="2"/>
@@ -6427,7 +6423,7 @@
       <c r="V181" s="2"/>
       <c r="W181" s="2"/>
     </row>
-    <row r="182" ht="13.2" spans="3:23">
+    <row r="182" ht="12.75" spans="3:23">
       <c r="C182" s="2"/>
       <c r="D182" s="2"/>
       <c r="E182" s="2"/>
@@ -6450,7 +6446,7 @@
       <c r="V182" s="2"/>
       <c r="W182" s="2"/>
     </row>
-    <row r="183" ht="13.2" spans="3:23">
+    <row r="183" ht="12.75" spans="3:23">
       <c r="C183" s="2"/>
       <c r="D183" s="2"/>
       <c r="E183" s="2"/>
@@ -6473,7 +6469,7 @@
       <c r="V183" s="2"/>
       <c r="W183" s="2"/>
     </row>
-    <row r="184" ht="13.2" spans="3:23">
+    <row r="184" ht="12.75" spans="3:23">
       <c r="C184" s="2"/>
       <c r="D184" s="2"/>
       <c r="E184" s="2"/>
@@ -6496,7 +6492,7 @@
       <c r="V184" s="2"/>
       <c r="W184" s="2"/>
     </row>
-    <row r="185" ht="13.2" spans="3:23">
+    <row r="185" ht="12.75" spans="3:23">
       <c r="C185" s="2"/>
       <c r="D185" s="2"/>
       <c r="E185" s="2"/>
@@ -6519,7 +6515,7 @@
       <c r="V185" s="2"/>
       <c r="W185" s="2"/>
     </row>
-    <row r="186" ht="13.2" spans="3:23">
+    <row r="186" ht="12.75" spans="3:23">
       <c r="C186" s="2"/>
       <c r="D186" s="2"/>
       <c r="E186" s="2"/>
@@ -6542,7 +6538,7 @@
       <c r="V186" s="2"/>
       <c r="W186" s="2"/>
     </row>
-    <row r="187" ht="13.2" spans="3:23">
+    <row r="187" ht="12.75" spans="3:23">
       <c r="C187" s="2"/>
       <c r="D187" s="2"/>
       <c r="E187" s="2"/>
@@ -6565,7 +6561,7 @@
       <c r="V187" s="2"/>
       <c r="W187" s="2"/>
     </row>
-    <row r="188" ht="13.2" spans="3:23">
+    <row r="188" ht="12.75" spans="3:23">
       <c r="C188" s="2"/>
       <c r="D188" s="2"/>
       <c r="E188" s="2"/>
@@ -6588,7 +6584,7 @@
       <c r="V188" s="2"/>
       <c r="W188" s="2"/>
     </row>
-    <row r="189" ht="13.2" spans="3:23">
+    <row r="189" ht="12.75" spans="3:23">
       <c r="C189" s="2"/>
       <c r="D189" s="2"/>
       <c r="E189" s="2"/>
@@ -6611,7 +6607,7 @@
       <c r="V189" s="2"/>
       <c r="W189" s="2"/>
     </row>
-    <row r="190" ht="13.2" spans="3:23">
+    <row r="190" ht="12.75" spans="3:23">
       <c r="C190" s="2"/>
       <c r="D190" s="2"/>
       <c r="E190" s="2"/>
@@ -6634,7 +6630,7 @@
       <c r="V190" s="2"/>
       <c r="W190" s="2"/>
     </row>
-    <row r="191" ht="13.2" spans="3:23">
+    <row r="191" ht="12.75" spans="3:23">
       <c r="C191" s="2"/>
       <c r="D191" s="2"/>
       <c r="E191" s="2"/>
@@ -6657,7 +6653,7 @@
       <c r="V191" s="2"/>
       <c r="W191" s="2"/>
     </row>
-    <row r="192" ht="13.2" spans="3:23">
+    <row r="192" ht="12.75" spans="3:23">
       <c r="C192" s="2"/>
       <c r="D192" s="2"/>
       <c r="E192" s="2"/>
@@ -6680,7 +6676,7 @@
       <c r="V192" s="2"/>
       <c r="W192" s="2"/>
     </row>
-    <row r="193" ht="13.2" spans="3:23">
+    <row r="193" ht="12.75" spans="3:23">
       <c r="C193" s="2"/>
       <c r="D193" s="2"/>
       <c r="E193" s="2"/>
@@ -6703,7 +6699,7 @@
       <c r="V193" s="2"/>
       <c r="W193" s="2"/>
     </row>
-    <row r="194" ht="13.2" spans="3:23">
+    <row r="194" ht="12.75" spans="3:23">
       <c r="C194" s="2"/>
       <c r="D194" s="2"/>
       <c r="E194" s="2"/>
@@ -6726,7 +6722,7 @@
       <c r="V194" s="2"/>
       <c r="W194" s="2"/>
     </row>
-    <row r="195" ht="13.2" spans="3:23">
+    <row r="195" ht="12.75" spans="3:23">
       <c r="C195" s="2"/>
       <c r="D195" s="2"/>
       <c r="E195" s="2"/>
@@ -6749,7 +6745,7 @@
       <c r="V195" s="2"/>
       <c r="W195" s="2"/>
     </row>
-    <row r="196" ht="13.2" spans="3:23">
+    <row r="196" ht="12.75" spans="3:23">
       <c r="C196" s="2"/>
       <c r="D196" s="2"/>
       <c r="E196" s="2"/>
@@ -6772,7 +6768,7 @@
       <c r="V196" s="2"/>
       <c r="W196" s="2"/>
     </row>
-    <row r="197" ht="13.2" spans="3:23">
+    <row r="197" ht="12.75" spans="3:23">
       <c r="C197" s="2"/>
       <c r="D197" s="2"/>
       <c r="E197" s="2"/>
@@ -6795,7 +6791,7 @@
       <c r="V197" s="2"/>
       <c r="W197" s="2"/>
     </row>
-    <row r="198" ht="13.2" spans="3:23">
+    <row r="198" ht="12.75" spans="3:23">
       <c r="C198" s="2"/>
       <c r="D198" s="2"/>
       <c r="E198" s="2"/>
@@ -6818,7 +6814,7 @@
       <c r="V198" s="2"/>
       <c r="W198" s="2"/>
     </row>
-    <row r="199" ht="13.2" spans="3:23">
+    <row r="199" ht="12.75" spans="3:23">
       <c r="C199" s="2"/>
       <c r="D199" s="2"/>
       <c r="E199" s="2"/>
@@ -6841,7 +6837,7 @@
       <c r="V199" s="2"/>
       <c r="W199" s="2"/>
     </row>
-    <row r="200" ht="13.2" spans="3:23">
+    <row r="200" ht="12.75" spans="3:23">
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
       <c r="E200" s="2"/>
@@ -6864,7 +6860,7 @@
       <c r="V200" s="2"/>
       <c r="W200" s="2"/>
     </row>
-    <row r="201" ht="13.2" spans="3:23">
+    <row r="201" ht="12.75" spans="3:23">
       <c r="C201" s="2"/>
       <c r="D201" s="2"/>
       <c r="E201" s="2"/>
@@ -6887,7 +6883,7 @@
       <c r="V201" s="2"/>
       <c r="W201" s="2"/>
     </row>
-    <row r="202" ht="13.2" spans="3:23">
+    <row r="202" ht="12.75" spans="3:23">
       <c r="C202" s="2"/>
       <c r="D202" s="2"/>
       <c r="E202" s="2"/>
@@ -6910,7 +6906,7 @@
       <c r="V202" s="2"/>
       <c r="W202" s="2"/>
     </row>
-    <row r="203" ht="13.2" spans="3:23">
+    <row r="203" ht="12.75" spans="3:23">
       <c r="C203" s="2"/>
       <c r="D203" s="2"/>
       <c r="E203" s="2"/>
@@ -6933,7 +6929,7 @@
       <c r="V203" s="2"/>
       <c r="W203" s="2"/>
     </row>
-    <row r="204" ht="13.2" spans="3:23">
+    <row r="204" ht="12.75" spans="3:23">
       <c r="C204" s="2"/>
       <c r="D204" s="2"/>
       <c r="E204" s="2"/>
@@ -6956,7 +6952,7 @@
       <c r="V204" s="2"/>
       <c r="W204" s="2"/>
     </row>
-    <row r="205" ht="13.2" spans="3:23">
+    <row r="205" ht="12.75" spans="3:23">
       <c r="C205" s="2"/>
       <c r="D205" s="2"/>
       <c r="E205" s="2"/>
@@ -6979,7 +6975,7 @@
       <c r="V205" s="2"/>
       <c r="W205" s="2"/>
     </row>
-    <row r="206" ht="13.2" spans="3:23">
+    <row r="206" ht="12.75" spans="3:23">
       <c r="C206" s="2"/>
       <c r="D206" s="2"/>
       <c r="E206" s="2"/>
@@ -7002,7 +6998,7 @@
       <c r="V206" s="2"/>
       <c r="W206" s="2"/>
     </row>
-    <row r="207" ht="13.2" spans="3:23">
+    <row r="207" ht="12.75" spans="3:23">
       <c r="C207" s="2"/>
       <c r="D207" s="2"/>
       <c r="E207" s="2"/>
@@ -7025,7 +7021,7 @@
       <c r="V207" s="2"/>
       <c r="W207" s="2"/>
     </row>
-    <row r="208" ht="13.2" spans="3:23">
+    <row r="208" ht="12.75" spans="3:23">
       <c r="C208" s="2"/>
       <c r="D208" s="2"/>
       <c r="E208" s="2"/>
@@ -7048,7 +7044,7 @@
       <c r="V208" s="2"/>
       <c r="W208" s="2"/>
     </row>
-    <row r="209" ht="13.2" spans="3:23">
+    <row r="209" ht="12.75" spans="3:23">
       <c r="C209" s="2"/>
       <c r="D209" s="2"/>
       <c r="E209" s="2"/>
@@ -7071,7 +7067,7 @@
       <c r="V209" s="2"/>
       <c r="W209" s="2"/>
     </row>
-    <row r="210" ht="13.2" spans="3:23">
+    <row r="210" ht="12.75" spans="3:23">
       <c r="C210" s="2"/>
       <c r="D210" s="2"/>
       <c r="E210" s="2"/>
@@ -7094,7 +7090,7 @@
       <c r="V210" s="2"/>
       <c r="W210" s="2"/>
     </row>
-    <row r="211" ht="13.2" spans="3:23">
+    <row r="211" ht="12.75" spans="3:23">
       <c r="C211" s="2"/>
       <c r="D211" s="2"/>
       <c r="E211" s="2"/>
@@ -7117,7 +7113,7 @@
       <c r="V211" s="2"/>
       <c r="W211" s="2"/>
     </row>
-    <row r="212" ht="13.2" spans="3:23">
+    <row r="212" ht="12.75" spans="3:23">
       <c r="C212" s="2"/>
       <c r="D212" s="2"/>
       <c r="E212" s="2"/>
@@ -7140,7 +7136,7 @@
       <c r="V212" s="2"/>
       <c r="W212" s="2"/>
     </row>
-    <row r="213" ht="13.2" spans="3:23">
+    <row r="213" ht="12.75" spans="3:23">
       <c r="C213" s="2"/>
       <c r="D213" s="2"/>
       <c r="E213" s="2"/>
@@ -7163,7 +7159,7 @@
       <c r="V213" s="2"/>
       <c r="W213" s="2"/>
     </row>
-    <row r="214" ht="13.2" spans="3:23">
+    <row r="214" ht="12.75" spans="3:23">
       <c r="C214" s="2"/>
       <c r="D214" s="2"/>
       <c r="E214" s="2"/>
@@ -7186,7 +7182,7 @@
       <c r="V214" s="2"/>
       <c r="W214" s="2"/>
     </row>
-    <row r="215" ht="13.2" spans="3:23">
+    <row r="215" ht="12.75" spans="3:23">
       <c r="C215" s="2"/>
       <c r="D215" s="2"/>
       <c r="E215" s="2"/>
@@ -7209,7 +7205,7 @@
       <c r="V215" s="2"/>
       <c r="W215" s="2"/>
     </row>
-    <row r="216" ht="13.2" spans="3:23">
+    <row r="216" ht="12.75" spans="3:23">
       <c r="C216" s="2"/>
       <c r="D216" s="2"/>
       <c r="E216" s="2"/>
@@ -7232,7 +7228,7 @@
       <c r="V216" s="2"/>
       <c r="W216" s="2"/>
     </row>
-    <row r="217" ht="13.2" spans="3:23">
+    <row r="217" ht="12.75" spans="3:23">
       <c r="C217" s="2"/>
       <c r="D217" s="2"/>
       <c r="E217" s="2"/>
@@ -7255,7 +7251,7 @@
       <c r="V217" s="2"/>
       <c r="W217" s="2"/>
     </row>
-    <row r="218" ht="13.2" spans="3:23">
+    <row r="218" ht="12.75" spans="3:23">
       <c r="C218" s="2"/>
       <c r="D218" s="2"/>
       <c r="E218" s="2"/>
@@ -7278,7 +7274,7 @@
       <c r="V218" s="2"/>
       <c r="W218" s="2"/>
     </row>
-    <row r="219" ht="13.2" spans="3:23">
+    <row r="219" ht="12.75" spans="3:23">
       <c r="C219" s="2"/>
       <c r="D219" s="2"/>
       <c r="E219" s="2"/>
@@ -7301,7 +7297,7 @@
       <c r="V219" s="2"/>
       <c r="W219" s="2"/>
     </row>
-    <row r="220" ht="13.2" spans="3:23">
+    <row r="220" ht="12.75" spans="3:23">
       <c r="C220" s="2"/>
       <c r="D220" s="2"/>
       <c r="E220" s="2"/>
@@ -7324,7 +7320,7 @@
       <c r="V220" s="2"/>
       <c r="W220" s="2"/>
     </row>
-    <row r="221" ht="13.2" spans="3:23">
+    <row r="221" ht="12.75" spans="3:23">
       <c r="C221" s="2"/>
       <c r="D221" s="2"/>
       <c r="E221" s="2"/>
@@ -7347,7 +7343,7 @@
       <c r="V221" s="2"/>
       <c r="W221" s="2"/>
     </row>
-    <row r="222" ht="13.2" spans="3:23">
+    <row r="222" ht="12.75" spans="3:23">
       <c r="C222" s="2"/>
       <c r="D222" s="2"/>
       <c r="E222" s="2"/>
@@ -7370,7 +7366,7 @@
       <c r="V222" s="2"/>
       <c r="W222" s="2"/>
     </row>
-    <row r="223" ht="13.2" spans="3:23">
+    <row r="223" ht="12.75" spans="3:23">
       <c r="C223" s="2"/>
       <c r="D223" s="2"/>
       <c r="E223" s="2"/>
@@ -7393,7 +7389,7 @@
       <c r="V223" s="2"/>
       <c r="W223" s="2"/>
     </row>
-    <row r="224" ht="13.2" spans="3:23">
+    <row r="224" ht="12.75" spans="3:23">
       <c r="C224" s="2"/>
       <c r="D224" s="2"/>
       <c r="E224" s="2"/>
@@ -7416,7 +7412,7 @@
       <c r="V224" s="2"/>
       <c r="W224" s="2"/>
     </row>
-    <row r="225" ht="13.2" spans="3:23">
+    <row r="225" ht="12.75" spans="3:23">
       <c r="C225" s="2"/>
       <c r="D225" s="2"/>
       <c r="E225" s="2"/>
@@ -7439,7 +7435,7 @@
       <c r="V225" s="2"/>
       <c r="W225" s="2"/>
     </row>
-    <row r="226" ht="13.2" spans="3:23">
+    <row r="226" ht="12.75" spans="3:23">
       <c r="C226" s="2"/>
       <c r="D226" s="2"/>
       <c r="E226" s="2"/>
@@ -7462,7 +7458,7 @@
       <c r="V226" s="2"/>
       <c r="W226" s="2"/>
     </row>
-    <row r="227" ht="13.2" spans="3:23">
+    <row r="227" ht="12.75" spans="3:23">
       <c r="C227" s="2"/>
       <c r="D227" s="2"/>
       <c r="E227" s="2"/>
@@ -7485,7 +7481,7 @@
       <c r="V227" s="2"/>
       <c r="W227" s="2"/>
     </row>
-    <row r="228" ht="13.2" spans="3:23">
+    <row r="228" ht="12.75" spans="3:23">
       <c r="C228" s="2"/>
       <c r="D228" s="2"/>
       <c r="E228" s="2"/>
@@ -7508,7 +7504,7 @@
       <c r="V228" s="2"/>
       <c r="W228" s="2"/>
     </row>
-    <row r="229" ht="13.2" spans="3:23">
+    <row r="229" ht="12.75" spans="3:23">
       <c r="C229" s="2"/>
       <c r="D229" s="2"/>
       <c r="E229" s="2"/>
@@ -7531,7 +7527,7 @@
       <c r="V229" s="2"/>
       <c r="W229" s="2"/>
     </row>
-    <row r="230" ht="13.2" spans="3:23">
+    <row r="230" ht="12.75" spans="3:23">
       <c r="C230" s="2"/>
       <c r="D230" s="2"/>
       <c r="E230" s="2"/>
@@ -7554,7 +7550,7 @@
       <c r="V230" s="2"/>
       <c r="W230" s="2"/>
     </row>
-    <row r="231" ht="13.2" spans="3:23">
+    <row r="231" ht="12.75" spans="3:23">
       <c r="C231" s="2"/>
       <c r="D231" s="2"/>
       <c r="E231" s="2"/>
@@ -7577,7 +7573,7 @@
       <c r="V231" s="2"/>
       <c r="W231" s="2"/>
     </row>
-    <row r="232" ht="13.2" spans="3:23">
+    <row r="232" ht="12.75" spans="3:23">
       <c r="C232" s="2"/>
       <c r="D232" s="2"/>
       <c r="E232" s="2"/>
@@ -7600,7 +7596,7 @@
       <c r="V232" s="2"/>
       <c r="W232" s="2"/>
     </row>
-    <row r="233" ht="13.2" spans="3:23">
+    <row r="233" ht="12.75" spans="3:23">
       <c r="C233" s="2"/>
       <c r="D233" s="2"/>
       <c r="E233" s="2"/>
@@ -7623,7 +7619,7 @@
       <c r="V233" s="2"/>
       <c r="W233" s="2"/>
     </row>
-    <row r="234" ht="13.2" spans="3:23">
+    <row r="234" ht="12.75" spans="3:23">
       <c r="C234" s="2"/>
       <c r="D234" s="2"/>
       <c r="E234" s="2"/>
@@ -7646,7 +7642,7 @@
       <c r="V234" s="2"/>
       <c r="W234" s="2"/>
     </row>
-    <row r="235" ht="13.2" spans="3:23">
+    <row r="235" ht="12.75" spans="3:23">
       <c r="C235" s="2"/>
       <c r="D235" s="2"/>
       <c r="E235" s="2"/>
@@ -7669,7 +7665,7 @@
       <c r="V235" s="2"/>
       <c r="W235" s="2"/>
     </row>
-    <row r="236" ht="13.2" spans="3:23">
+    <row r="236" ht="12.75" spans="3:23">
       <c r="C236" s="2"/>
       <c r="D236" s="2"/>
       <c r="E236" s="2"/>
@@ -7692,7 +7688,7 @@
       <c r="V236" s="2"/>
       <c r="W236" s="2"/>
     </row>
-    <row r="237" ht="13.2" spans="3:23">
+    <row r="237" ht="12.75" spans="3:23">
       <c r="C237" s="2"/>
       <c r="D237" s="2"/>
       <c r="E237" s="2"/>
@@ -7715,7 +7711,7 @@
       <c r="V237" s="2"/>
       <c r="W237" s="2"/>
     </row>
-    <row r="238" ht="13.2" spans="3:23">
+    <row r="238" ht="12.75" spans="3:23">
       <c r="C238" s="2"/>
       <c r="D238" s="2"/>
       <c r="E238" s="2"/>
@@ -7738,7 +7734,7 @@
       <c r="V238" s="2"/>
       <c r="W238" s="2"/>
     </row>
-    <row r="239" ht="13.2" spans="3:23">
+    <row r="239" ht="12.75" spans="3:23">
       <c r="C239" s="2"/>
       <c r="D239" s="2"/>
       <c r="E239" s="2"/>
@@ -7761,7 +7757,7 @@
       <c r="V239" s="2"/>
       <c r="W239" s="2"/>
     </row>
-    <row r="240" ht="13.2" spans="3:23">
+    <row r="240" ht="12.75" spans="3:23">
       <c r="C240" s="2"/>
       <c r="D240" s="2"/>
       <c r="E240" s="2"/>
@@ -7784,7 +7780,7 @@
       <c r="V240" s="2"/>
       <c r="W240" s="2"/>
     </row>
-    <row r="241" ht="13.2" spans="3:23">
+    <row r="241" ht="12.75" spans="3:23">
       <c r="C241" s="2"/>
       <c r="D241" s="2"/>
       <c r="E241" s="2"/>
@@ -7807,7 +7803,7 @@
       <c r="V241" s="2"/>
       <c r="W241" s="2"/>
     </row>
-    <row r="242" ht="13.2" spans="3:23">
+    <row r="242" ht="12.75" spans="3:23">
       <c r="C242" s="2"/>
       <c r="D242" s="2"/>
       <c r="E242" s="2"/>
@@ -7830,7 +7826,7 @@
       <c r="V242" s="2"/>
       <c r="W242" s="2"/>
     </row>
-    <row r="243" ht="13.2" spans="3:23">
+    <row r="243" ht="12.75" spans="3:23">
       <c r="C243" s="2"/>
       <c r="D243" s="2"/>
       <c r="E243" s="2"/>
@@ -7853,7 +7849,7 @@
       <c r="V243" s="2"/>
       <c r="W243" s="2"/>
     </row>
-    <row r="244" ht="13.2" spans="3:23">
+    <row r="244" ht="12.75" spans="3:23">
       <c r="C244" s="2"/>
       <c r="D244" s="2"/>
       <c r="E244" s="2"/>
@@ -7876,7 +7872,7 @@
       <c r="V244" s="2"/>
       <c r="W244" s="2"/>
     </row>
-    <row r="245" ht="13.2" spans="3:23">
+    <row r="245" ht="12.75" spans="3:23">
       <c r="C245" s="2"/>
       <c r="D245" s="2"/>
       <c r="E245" s="2"/>
@@ -7899,7 +7895,7 @@
       <c r="V245" s="2"/>
       <c r="W245" s="2"/>
     </row>
-    <row r="246" ht="13.2" spans="3:23">
+    <row r="246" ht="12.75" spans="3:23">
       <c r="C246" s="2"/>
       <c r="D246" s="2"/>
       <c r="E246" s="2"/>
@@ -7922,7 +7918,7 @@
       <c r="V246" s="2"/>
       <c r="W246" s="2"/>
     </row>
-    <row r="247" ht="13.2" spans="3:23">
+    <row r="247" ht="12.75" spans="3:23">
       <c r="C247" s="2"/>
       <c r="D247" s="2"/>
       <c r="E247" s="2"/>
@@ -7945,7 +7941,7 @@
       <c r="V247" s="2"/>
       <c r="W247" s="2"/>
     </row>
-    <row r="248" ht="13.2" spans="3:23">
+    <row r="248" ht="12.75" spans="3:23">
       <c r="C248" s="2"/>
       <c r="D248" s="2"/>
       <c r="E248" s="2"/>
@@ -7968,7 +7964,7 @@
       <c r="V248" s="2"/>
       <c r="W248" s="2"/>
     </row>
-    <row r="249" ht="13.2" spans="3:23">
+    <row r="249" ht="12.75" spans="3:23">
       <c r="C249" s="2"/>
       <c r="D249" s="2"/>
       <c r="E249" s="2"/>
@@ -7991,7 +7987,7 @@
       <c r="V249" s="2"/>
       <c r="W249" s="2"/>
     </row>
-    <row r="250" ht="13.2" spans="3:23">
+    <row r="250" ht="12.75" spans="3:23">
       <c r="C250" s="2"/>
       <c r="D250" s="2"/>
       <c r="E250" s="2"/>
@@ -8014,7 +8010,7 @@
       <c r="V250" s="2"/>
       <c r="W250" s="2"/>
     </row>
-    <row r="251" ht="13.2" spans="3:23">
+    <row r="251" ht="12.75" spans="3:23">
       <c r="C251" s="2"/>
       <c r="D251" s="2"/>
       <c r="E251" s="2"/>
@@ -8037,7 +8033,7 @@
       <c r="V251" s="2"/>
       <c r="W251" s="2"/>
     </row>
-    <row r="252" ht="13.2" spans="3:23">
+    <row r="252" ht="12.75" spans="3:23">
       <c r="C252" s="2"/>
       <c r="D252" s="2"/>
       <c r="E252" s="2"/>
@@ -8060,7 +8056,7 @@
       <c r="V252" s="2"/>
       <c r="W252" s="2"/>
     </row>
-    <row r="253" ht="13.2" spans="3:23">
+    <row r="253" ht="12.75" spans="3:23">
       <c r="C253" s="2"/>
       <c r="D253" s="2"/>
       <c r="E253" s="2"/>
@@ -8083,7 +8079,7 @@
       <c r="V253" s="2"/>
       <c r="W253" s="2"/>
     </row>
-    <row r="254" ht="13.2" spans="3:23">
+    <row r="254" ht="12.75" spans="3:23">
       <c r="C254" s="2"/>
       <c r="D254" s="2"/>
       <c r="E254" s="2"/>
@@ -8106,7 +8102,7 @@
       <c r="V254" s="2"/>
       <c r="W254" s="2"/>
     </row>
-    <row r="255" ht="13.2" spans="3:23">
+    <row r="255" ht="12.75" spans="3:23">
       <c r="C255" s="2"/>
       <c r="D255" s="2"/>
       <c r="E255" s="2"/>
@@ -8129,7 +8125,7 @@
       <c r="V255" s="2"/>
       <c r="W255" s="2"/>
     </row>
-    <row r="256" ht="13.2" spans="3:23">
+    <row r="256" ht="12.75" spans="3:23">
       <c r="C256" s="2"/>
       <c r="D256" s="2"/>
       <c r="E256" s="2"/>
@@ -8152,7 +8148,7 @@
       <c r="V256" s="2"/>
       <c r="W256" s="2"/>
     </row>
-    <row r="257" ht="13.2" spans="3:23">
+    <row r="257" ht="12.75" spans="3:23">
       <c r="C257" s="2"/>
       <c r="D257" s="2"/>
       <c r="E257" s="2"/>
@@ -8175,7 +8171,7 @@
       <c r="V257" s="2"/>
       <c r="W257" s="2"/>
     </row>
-    <row r="258" ht="13.2" spans="3:23">
+    <row r="258" ht="12.75" spans="3:23">
       <c r="C258" s="2"/>
       <c r="D258" s="2"/>
       <c r="E258" s="2"/>
@@ -8198,7 +8194,7 @@
       <c r="V258" s="2"/>
       <c r="W258" s="2"/>
     </row>
-    <row r="259" ht="13.2" spans="3:23">
+    <row r="259" ht="12.75" spans="3:23">
       <c r="C259" s="2"/>
       <c r="D259" s="2"/>
       <c r="E259" s="2"/>
@@ -8221,7 +8217,7 @@
       <c r="V259" s="2"/>
       <c r="W259" s="2"/>
     </row>
-    <row r="260" ht="13.2" spans="3:23">
+    <row r="260" ht="12.75" spans="3:23">
       <c r="C260" s="2"/>
       <c r="D260" s="2"/>
       <c r="E260" s="2"/>
@@ -8244,7 +8240,7 @@
       <c r="V260" s="2"/>
       <c r="W260" s="2"/>
     </row>
-    <row r="261" ht="13.2" spans="3:23">
+    <row r="261" ht="12.75" spans="3:23">
       <c r="C261" s="2"/>
       <c r="D261" s="2"/>
       <c r="E261" s="2"/>
@@ -8267,7 +8263,7 @@
       <c r="V261" s="2"/>
       <c r="W261" s="2"/>
     </row>
-    <row r="262" ht="13.2" spans="3:23">
+    <row r="262" ht="12.75" spans="3:23">
       <c r="C262" s="2"/>
       <c r="D262" s="2"/>
       <c r="E262" s="2"/>
@@ -8290,7 +8286,7 @@
       <c r="V262" s="2"/>
       <c r="W262" s="2"/>
     </row>
-    <row r="263" ht="13.2" spans="3:23">
+    <row r="263" ht="12.75" spans="3:23">
       <c r="C263" s="2"/>
       <c r="D263" s="2"/>
       <c r="E263" s="2"/>
@@ -8313,7 +8309,7 @@
       <c r="V263" s="2"/>
       <c r="W263" s="2"/>
     </row>
-    <row r="264" ht="13.2" spans="3:23">
+    <row r="264" ht="12.75" spans="3:23">
       <c r="C264" s="2"/>
       <c r="D264" s="2"/>
       <c r="E264" s="2"/>
@@ -8336,7 +8332,7 @@
       <c r="V264" s="2"/>
       <c r="W264" s="2"/>
     </row>
-    <row r="265" ht="13.2" spans="3:23">
+    <row r="265" ht="12.75" spans="3:23">
       <c r="C265" s="2"/>
       <c r="D265" s="2"/>
       <c r="E265" s="2"/>
@@ -8359,7 +8355,7 @@
       <c r="V265" s="2"/>
       <c r="W265" s="2"/>
     </row>
-    <row r="266" ht="13.2" spans="3:23">
+    <row r="266" ht="12.75" spans="3:23">
       <c r="C266" s="2"/>
       <c r="D266" s="2"/>
       <c r="E266" s="2"/>
@@ -8382,7 +8378,7 @@
       <c r="V266" s="2"/>
       <c r="W266" s="2"/>
     </row>
-    <row r="267" ht="13.2" spans="3:23">
+    <row r="267" ht="12.75" spans="3:23">
       <c r="C267" s="2"/>
       <c r="D267" s="2"/>
       <c r="E267" s="2"/>
@@ -8405,7 +8401,7 @@
       <c r="V267" s="2"/>
       <c r="W267" s="2"/>
     </row>
-    <row r="268" ht="13.2" spans="3:23">
+    <row r="268" ht="12.75" spans="3:23">
       <c r="C268" s="2"/>
       <c r="D268" s="2"/>
       <c r="E268" s="2"/>
@@ -8428,7 +8424,7 @@
       <c r="V268" s="2"/>
       <c r="W268" s="2"/>
     </row>
-    <row r="269" ht="13.2" spans="3:23">
+    <row r="269" ht="12.75" spans="3:23">
       <c r="C269" s="2"/>
       <c r="D269" s="2"/>
       <c r="E269" s="2"/>
@@ -8451,7 +8447,7 @@
       <c r="V269" s="2"/>
       <c r="W269" s="2"/>
     </row>
-    <row r="270" ht="13.2" spans="3:23">
+    <row r="270" ht="12.75" spans="3:23">
       <c r="C270" s="2"/>
       <c r="D270" s="2"/>
       <c r="E270" s="2"/>
@@ -8474,7 +8470,7 @@
       <c r="V270" s="2"/>
       <c r="W270" s="2"/>
     </row>
-    <row r="271" ht="13.2" spans="3:23">
+    <row r="271" ht="12.75" spans="3:23">
       <c r="C271" s="2"/>
       <c r="D271" s="2"/>
       <c r="E271" s="2"/>
@@ -8497,7 +8493,7 @@
       <c r="V271" s="2"/>
       <c r="W271" s="2"/>
     </row>
-    <row r="272" ht="13.2" spans="3:23">
+    <row r="272" ht="12.75" spans="3:23">
       <c r="C272" s="2"/>
       <c r="D272" s="2"/>
       <c r="E272" s="2"/>
@@ -8520,7 +8516,7 @@
       <c r="V272" s="2"/>
       <c r="W272" s="2"/>
     </row>
-    <row r="273" ht="13.2" spans="3:23">
+    <row r="273" ht="12.75" spans="3:23">
       <c r="C273" s="2"/>
       <c r="D273" s="2"/>
       <c r="E273" s="2"/>
@@ -8543,7 +8539,7 @@
       <c r="V273" s="2"/>
       <c r="W273" s="2"/>
     </row>
-    <row r="274" ht="13.2" spans="3:23">
+    <row r="274" ht="12.75" spans="3:23">
       <c r="C274" s="2"/>
       <c r="D274" s="2"/>
       <c r="E274" s="2"/>
@@ -8566,7 +8562,7 @@
       <c r="V274" s="2"/>
       <c r="W274" s="2"/>
     </row>
-    <row r="275" ht="13.2" spans="3:23">
+    <row r="275" ht="12.75" spans="3:23">
       <c r="C275" s="2"/>
       <c r="D275" s="2"/>
       <c r="E275" s="2"/>
@@ -8589,7 +8585,7 @@
       <c r="V275" s="2"/>
       <c r="W275" s="2"/>
     </row>
-    <row r="276" ht="13.2" spans="3:23">
+    <row r="276" ht="12.75" spans="3:23">
       <c r="C276" s="2"/>
       <c r="D276" s="2"/>
       <c r="E276" s="2"/>
@@ -8612,7 +8608,7 @@
       <c r="V276" s="2"/>
       <c r="W276" s="2"/>
     </row>
-    <row r="277" ht="13.2" spans="3:23">
+    <row r="277" ht="12.75" spans="3:23">
       <c r="C277" s="2"/>
       <c r="D277" s="2"/>
       <c r="E277" s="2"/>
@@ -8635,7 +8631,7 @@
       <c r="V277" s="2"/>
       <c r="W277" s="2"/>
     </row>
-    <row r="278" ht="13.2" spans="3:23">
+    <row r="278" ht="12.75" spans="3:23">
       <c r="C278" s="2"/>
       <c r="D278" s="2"/>
       <c r="E278" s="2"/>
@@ -8658,7 +8654,7 @@
       <c r="V278" s="2"/>
       <c r="W278" s="2"/>
     </row>
-    <row r="279" ht="13.2" spans="3:23">
+    <row r="279" ht="12.75" spans="3:23">
       <c r="C279" s="2"/>
       <c r="D279" s="2"/>
       <c r="E279" s="2"/>
@@ -8681,7 +8677,7 @@
       <c r="V279" s="2"/>
       <c r="W279" s="2"/>
     </row>
-    <row r="280" ht="13.2" spans="3:23">
+    <row r="280" ht="12.75" spans="3:23">
       <c r="C280" s="2"/>
       <c r="D280" s="2"/>
       <c r="E280" s="2"/>
@@ -8704,7 +8700,7 @@
       <c r="V280" s="2"/>
       <c r="W280" s="2"/>
     </row>
-    <row r="281" ht="13.2" spans="3:23">
+    <row r="281" ht="12.75" spans="3:23">
       <c r="C281" s="2"/>
       <c r="D281" s="2"/>
       <c r="E281" s="2"/>
@@ -8727,7 +8723,7 @@
       <c r="V281" s="2"/>
       <c r="W281" s="2"/>
     </row>
-    <row r="282" ht="13.2" spans="3:23">
+    <row r="282" ht="12.75" spans="3:23">
       <c r="C282" s="2"/>
       <c r="D282" s="2"/>
       <c r="E282" s="2"/>
@@ -8750,7 +8746,7 @@
       <c r="V282" s="2"/>
       <c r="W282" s="2"/>
     </row>
-    <row r="283" ht="13.2" spans="3:23">
+    <row r="283" ht="12.75" spans="3:23">
       <c r="C283" s="2"/>
       <c r="D283" s="2"/>
       <c r="E283" s="2"/>
@@ -8773,7 +8769,7 @@
       <c r="V283" s="2"/>
       <c r="W283" s="2"/>
     </row>
-    <row r="284" ht="13.2" spans="3:23">
+    <row r="284" ht="12.75" spans="3:23">
       <c r="C284" s="2"/>
       <c r="D284" s="2"/>
       <c r="E284" s="2"/>
@@ -8796,7 +8792,7 @@
       <c r="V284" s="2"/>
       <c r="W284" s="2"/>
     </row>
-    <row r="285" ht="13.2" spans="3:23">
+    <row r="285" ht="12.75" spans="3:23">
       <c r="C285" s="2"/>
       <c r="D285" s="2"/>
       <c r="E285" s="2"/>
@@ -8819,7 +8815,7 @@
       <c r="V285" s="2"/>
       <c r="W285" s="2"/>
     </row>
-    <row r="286" ht="13.2" spans="3:23">
+    <row r="286" ht="12.75" spans="3:23">
       <c r="C286" s="2"/>
       <c r="D286" s="2"/>
       <c r="E286" s="2"/>
@@ -8842,7 +8838,7 @@
       <c r="V286" s="2"/>
       <c r="W286" s="2"/>
     </row>
-    <row r="287" ht="13.2" spans="3:23">
+    <row r="287" ht="12.75" spans="3:23">
       <c r="C287" s="2"/>
       <c r="D287" s="2"/>
       <c r="E287" s="2"/>
@@ -8865,7 +8861,7 @@
       <c r="V287" s="2"/>
       <c r="W287" s="2"/>
     </row>
-    <row r="288" ht="13.2" spans="3:23">
+    <row r="288" ht="12.75" spans="3:23">
       <c r="C288" s="2"/>
       <c r="D288" s="2"/>
       <c r="E288" s="2"/>
@@ -8888,7 +8884,7 @@
       <c r="V288" s="2"/>
       <c r="W288" s="2"/>
     </row>
-    <row r="289" ht="13.2" spans="3:23">
+    <row r="289" ht="12.75" spans="3:23">
       <c r="C289" s="2"/>
       <c r="D289" s="2"/>
       <c r="E289" s="2"/>
@@ -8911,7 +8907,7 @@
       <c r="V289" s="2"/>
       <c r="W289" s="2"/>
     </row>
-    <row r="290" ht="13.2" spans="3:23">
+    <row r="290" ht="12.75" spans="3:23">
       <c r="C290" s="2"/>
       <c r="D290" s="2"/>
       <c r="E290" s="2"/>
@@ -8934,7 +8930,7 @@
       <c r="V290" s="2"/>
       <c r="W290" s="2"/>
     </row>
-    <row r="291" ht="13.2" spans="3:23">
+    <row r="291" ht="12.75" spans="3:23">
       <c r="C291" s="2"/>
       <c r="D291" s="2"/>
       <c r="E291" s="2"/>
@@ -8957,7 +8953,7 @@
       <c r="V291" s="2"/>
       <c r="W291" s="2"/>
     </row>
-    <row r="292" ht="13.2" spans="3:23">
+    <row r="292" ht="12.75" spans="3:23">
       <c r="C292" s="2"/>
       <c r="D292" s="2"/>
       <c r="E292" s="2"/>
@@ -8980,7 +8976,7 @@
       <c r="V292" s="2"/>
       <c r="W292" s="2"/>
     </row>
-    <row r="293" ht="13.2" spans="3:23">
+    <row r="293" ht="12.75" spans="3:23">
       <c r="C293" s="2"/>
       <c r="D293" s="2"/>
       <c r="E293" s="2"/>
@@ -9003,7 +8999,7 @@
       <c r="V293" s="2"/>
       <c r="W293" s="2"/>
     </row>
-    <row r="294" ht="13.2" spans="3:23">
+    <row r="294" ht="12.75" spans="3:23">
       <c r="C294" s="2"/>
       <c r="D294" s="2"/>
       <c r="E294" s="2"/>
@@ -9026,7 +9022,7 @@
       <c r="V294" s="2"/>
       <c r="W294" s="2"/>
     </row>
-    <row r="295" ht="13.2" spans="3:23">
+    <row r="295" ht="12.75" spans="3:23">
       <c r="C295" s="2"/>
       <c r="D295" s="2"/>
       <c r="E295" s="2"/>
@@ -9049,7 +9045,7 @@
       <c r="V295" s="2"/>
       <c r="W295" s="2"/>
     </row>
-    <row r="296" ht="13.2" spans="3:23">
+    <row r="296" ht="12.75" spans="3:23">
       <c r="C296" s="2"/>
       <c r="D296" s="2"/>
       <c r="E296" s="2"/>
@@ -9072,7 +9068,7 @@
       <c r="V296" s="2"/>
       <c r="W296" s="2"/>
     </row>
-    <row r="297" ht="13.2" spans="3:23">
+    <row r="297" ht="12.75" spans="3:23">
       <c r="C297" s="2"/>
       <c r="D297" s="2"/>
       <c r="E297" s="2"/>
@@ -9095,7 +9091,7 @@
       <c r="V297" s="2"/>
       <c r="W297" s="2"/>
     </row>
-    <row r="298" ht="13.2" spans="3:23">
+    <row r="298" ht="12.75" spans="3:23">
       <c r="C298" s="2"/>
       <c r="D298" s="2"/>
       <c r="E298" s="2"/>
@@ -9118,7 +9114,7 @@
       <c r="V298" s="2"/>
       <c r="W298" s="2"/>
     </row>
-    <row r="299" ht="13.2" spans="3:23">
+    <row r="299" ht="12.75" spans="3:23">
       <c r="C299" s="2"/>
       <c r="D299" s="2"/>
       <c r="E299" s="2"/>
@@ -9141,7 +9137,7 @@
       <c r="V299" s="2"/>
       <c r="W299" s="2"/>
     </row>
-    <row r="300" ht="13.2" spans="3:23">
+    <row r="300" ht="12.75" spans="3:23">
       <c r="C300" s="2"/>
       <c r="D300" s="2"/>
       <c r="E300" s="2"/>
@@ -9164,7 +9160,7 @@
       <c r="V300" s="2"/>
       <c r="W300" s="2"/>
     </row>
-    <row r="301" ht="13.2" spans="3:23">
+    <row r="301" ht="12.75" spans="3:23">
       <c r="C301" s="2"/>
       <c r="D301" s="2"/>
       <c r="E301" s="2"/>
@@ -9187,7 +9183,7 @@
       <c r="V301" s="2"/>
       <c r="W301" s="2"/>
     </row>
-    <row r="302" ht="13.2" spans="3:23">
+    <row r="302" ht="12.75" spans="3:23">
       <c r="C302" s="2"/>
       <c r="D302" s="2"/>
       <c r="E302" s="2"/>
@@ -9210,7 +9206,7 @@
       <c r="V302" s="2"/>
       <c r="W302" s="2"/>
     </row>
-    <row r="303" ht="13.2" spans="3:23">
+    <row r="303" ht="12.75" spans="3:23">
       <c r="C303" s="2"/>
       <c r="D303" s="2"/>
       <c r="E303" s="2"/>
@@ -9233,7 +9229,7 @@
       <c r="V303" s="2"/>
       <c r="W303" s="2"/>
     </row>
-    <row r="304" ht="13.2" spans="3:23">
+    <row r="304" ht="12.75" spans="3:23">
       <c r="C304" s="2"/>
       <c r="D304" s="2"/>
       <c r="E304" s="2"/>
@@ -9256,7 +9252,7 @@
       <c r="V304" s="2"/>
       <c r="W304" s="2"/>
     </row>
-    <row r="305" ht="13.2" spans="3:23">
+    <row r="305" ht="12.75" spans="3:23">
       <c r="C305" s="2"/>
       <c r="D305" s="2"/>
       <c r="E305" s="2"/>
@@ -9279,7 +9275,7 @@
       <c r="V305" s="2"/>
       <c r="W305" s="2"/>
     </row>
-    <row r="306" ht="13.2" spans="3:23">
+    <row r="306" ht="12.75" spans="3:23">
       <c r="C306" s="2"/>
       <c r="D306" s="2"/>
       <c r="E306" s="2"/>
@@ -9302,7 +9298,7 @@
       <c r="V306" s="2"/>
       <c r="W306" s="2"/>
     </row>
-    <row r="307" ht="13.2" spans="3:23">
+    <row r="307" ht="12.75" spans="3:23">
       <c r="C307" s="2"/>
       <c r="D307" s="2"/>
       <c r="E307" s="2"/>
@@ -9325,7 +9321,7 @@
       <c r="V307" s="2"/>
       <c r="W307" s="2"/>
     </row>
-    <row r="308" ht="13.2" spans="3:23">
+    <row r="308" ht="12.75" spans="3:23">
       <c r="C308" s="2"/>
       <c r="D308" s="2"/>
       <c r="E308" s="2"/>
@@ -9348,7 +9344,7 @@
       <c r="V308" s="2"/>
       <c r="W308" s="2"/>
     </row>
-    <row r="309" ht="13.2" spans="3:23">
+    <row r="309" ht="12.75" spans="3:23">
       <c r="C309" s="2"/>
       <c r="D309" s="2"/>
       <c r="E309" s="2"/>
@@ -9371,7 +9367,7 @@
       <c r="V309" s="2"/>
       <c r="W309" s="2"/>
     </row>
-    <row r="310" ht="13.2" spans="3:23">
+    <row r="310" ht="12.75" spans="3:23">
       <c r="C310" s="2"/>
       <c r="D310" s="2"/>
       <c r="E310" s="2"/>
@@ -9394,7 +9390,7 @@
       <c r="V310" s="2"/>
       <c r="W310" s="2"/>
     </row>
-    <row r="311" ht="13.2" spans="3:23">
+    <row r="311" ht="12.75" spans="3:23">
       <c r="C311" s="2"/>
       <c r="D311" s="2"/>
       <c r="E311" s="2"/>
@@ -9417,7 +9413,7 @@
       <c r="V311" s="2"/>
       <c r="W311" s="2"/>
     </row>
-    <row r="312" ht="13.2" spans="3:23">
+    <row r="312" ht="12.75" spans="3:23">
       <c r="C312" s="2"/>
       <c r="D312" s="2"/>
       <c r="E312" s="2"/>
@@ -9440,7 +9436,7 @@
       <c r="V312" s="2"/>
       <c r="W312" s="2"/>
     </row>
-    <row r="313" ht="13.2" spans="3:23">
+    <row r="313" ht="12.75" spans="3:23">
       <c r="C313" s="2"/>
       <c r="D313" s="2"/>
       <c r="E313" s="2"/>
@@ -9463,7 +9459,7 @@
       <c r="V313" s="2"/>
       <c r="W313" s="2"/>
     </row>
-    <row r="314" ht="13.2" spans="3:23">
+    <row r="314" ht="12.75" spans="3:23">
       <c r="C314" s="2"/>
       <c r="D314" s="2"/>
       <c r="E314" s="2"/>
@@ -9486,7 +9482,7 @@
       <c r="V314" s="2"/>
       <c r="W314" s="2"/>
     </row>
-    <row r="315" ht="13.2" spans="3:23">
+    <row r="315" ht="12.75" spans="3:23">
       <c r="C315" s="2"/>
       <c r="D315" s="2"/>
       <c r="E315" s="2"/>
@@ -9509,7 +9505,7 @@
       <c r="V315" s="2"/>
       <c r="W315" s="2"/>
     </row>
-    <row r="316" ht="13.2" spans="3:23">
+    <row r="316" ht="12.75" spans="3:23">
       <c r="C316" s="2"/>
       <c r="D316" s="2"/>
       <c r="E316" s="2"/>
@@ -9532,7 +9528,7 @@
       <c r="V316" s="2"/>
       <c r="W316" s="2"/>
     </row>
-    <row r="317" ht="13.2" spans="3:23">
+    <row r="317" ht="12.75" spans="3:23">
       <c r="C317" s="2"/>
       <c r="D317" s="2"/>
       <c r="E317" s="2"/>
@@ -9555,7 +9551,7 @@
       <c r="V317" s="2"/>
       <c r="W317" s="2"/>
     </row>
-    <row r="318" ht="13.2" spans="3:23">
+    <row r="318" ht="12.75" spans="3:23">
       <c r="C318" s="2"/>
       <c r="D318" s="2"/>
       <c r="E318" s="2"/>
@@ -9578,7 +9574,7 @@
       <c r="V318" s="2"/>
       <c r="W318" s="2"/>
     </row>
-    <row r="319" ht="13.2" spans="3:23">
+    <row r="319" ht="12.75" spans="3:23">
       <c r="C319" s="2"/>
       <c r="D319" s="2"/>
       <c r="E319" s="2"/>
@@ -9601,7 +9597,7 @@
       <c r="V319" s="2"/>
       <c r="W319" s="2"/>
     </row>
-    <row r="320" ht="13.2" spans="3:23">
+    <row r="320" ht="12.75" spans="3:23">
       <c r="C320" s="2"/>
       <c r="D320" s="2"/>
       <c r="E320" s="2"/>
@@ -9624,7 +9620,7 @@
       <c r="V320" s="2"/>
       <c r="W320" s="2"/>
     </row>
-    <row r="321" ht="13.2" spans="3:23">
+    <row r="321" ht="12.75" spans="3:23">
       <c r="C321" s="2"/>
       <c r="D321" s="2"/>
       <c r="E321" s="2"/>
@@ -9647,7 +9643,7 @@
       <c r="V321" s="2"/>
       <c r="W321" s="2"/>
     </row>
-    <row r="322" ht="13.2" spans="3:23">
+    <row r="322" ht="12.75" spans="3:23">
       <c r="C322" s="2"/>
       <c r="D322" s="2"/>
       <c r="E322" s="2"/>
@@ -9670,7 +9666,7 @@
       <c r="V322" s="2"/>
       <c r="W322" s="2"/>
     </row>
-    <row r="323" ht="13.2" spans="3:23">
+    <row r="323" ht="12.75" spans="3:23">
       <c r="C323" s="2"/>
       <c r="D323" s="2"/>
       <c r="E323" s="2"/>
@@ -9693,7 +9689,7 @@
       <c r="V323" s="2"/>
       <c r="W323" s="2"/>
     </row>
-    <row r="324" ht="13.2" spans="3:23">
+    <row r="324" ht="12.75" spans="3:23">
       <c r="C324" s="2"/>
       <c r="D324" s="2"/>
       <c r="E324" s="2"/>
@@ -9716,7 +9712,7 @@
       <c r="V324" s="2"/>
       <c r="W324" s="2"/>
     </row>
-    <row r="325" ht="13.2" spans="3:23">
+    <row r="325" ht="12.75" spans="3:23">
       <c r="C325" s="2"/>
       <c r="D325" s="2"/>
       <c r="E325" s="2"/>
@@ -9739,7 +9735,7 @@
       <c r="V325" s="2"/>
       <c r="W325" s="2"/>
     </row>
-    <row r="326" ht="13.2" spans="3:23">
+    <row r="326" ht="12.75" spans="3:23">
       <c r="C326" s="2"/>
       <c r="D326" s="2"/>
       <c r="E326" s="2"/>
@@ -9762,7 +9758,7 @@
       <c r="V326" s="2"/>
       <c r="W326" s="2"/>
     </row>
-    <row r="327" ht="13.2" spans="3:23">
+    <row r="327" ht="12.75" spans="3:23">
       <c r="C327" s="2"/>
       <c r="D327" s="2"/>
       <c r="E327" s="2"/>
@@ -9785,7 +9781,7 @@
       <c r="V327" s="2"/>
       <c r="W327" s="2"/>
     </row>
-    <row r="328" ht="13.2" spans="3:23">
+    <row r="328" ht="12.75" spans="3:23">
       <c r="C328" s="2"/>
       <c r="D328" s="2"/>
       <c r="E328" s="2"/>
@@ -9808,7 +9804,7 @@
       <c r="V328" s="2"/>
       <c r="W328" s="2"/>
     </row>
-    <row r="329" ht="13.2" spans="3:23">
+    <row r="329" ht="12.75" spans="3:23">
       <c r="C329" s="2"/>
       <c r="D329" s="2"/>
       <c r="E329" s="2"/>
@@ -9831,7 +9827,7 @@
       <c r="V329" s="2"/>
       <c r="W329" s="2"/>
     </row>
-    <row r="330" ht="13.2" spans="3:23">
+    <row r="330" ht="12.75" spans="3:23">
       <c r="C330" s="2"/>
       <c r="D330" s="2"/>
       <c r="E330" s="2"/>
@@ -9854,7 +9850,7 @@
       <c r="V330" s="2"/>
       <c r="W330" s="2"/>
     </row>
-    <row r="331" ht="13.2" spans="3:23">
+    <row r="331" ht="12.75" spans="3:23">
       <c r="C331" s="2"/>
       <c r="D331" s="2"/>
       <c r="E331" s="2"/>
@@ -9877,7 +9873,7 @@
       <c r="V331" s="2"/>
       <c r="W331" s="2"/>
     </row>
-    <row r="332" ht="13.2" spans="3:23">
+    <row r="332" ht="12.75" spans="3:23">
       <c r="C332" s="2"/>
       <c r="D332" s="2"/>
       <c r="E332" s="2"/>
@@ -9900,7 +9896,7 @@
       <c r="V332" s="2"/>
       <c r="W332" s="2"/>
     </row>
-    <row r="333" ht="13.2" spans="3:23">
+    <row r="333" ht="12.75" spans="3:23">
       <c r="C333" s="2"/>
       <c r="D333" s="2"/>
       <c r="E333" s="2"/>
@@ -9923,7 +9919,7 @@
       <c r="V333" s="2"/>
       <c r="W333" s="2"/>
     </row>
-    <row r="334" ht="13.2" spans="3:23">
+    <row r="334" ht="12.75" spans="3:23">
       <c r="C334" s="2"/>
       <c r="D334" s="2"/>
       <c r="E334" s="2"/>
@@ -9946,7 +9942,7 @@
       <c r="V334" s="2"/>
       <c r="W334" s="2"/>
     </row>
-    <row r="335" ht="13.2" spans="3:23">
+    <row r="335" ht="12.75" spans="3:23">
       <c r="C335" s="2"/>
       <c r="D335" s="2"/>
       <c r="E335" s="2"/>
@@ -9969,7 +9965,7 @@
       <c r="V335" s="2"/>
       <c r="W335" s="2"/>
     </row>
-    <row r="336" ht="13.2" spans="3:23">
+    <row r="336" ht="12.75" spans="3:23">
       <c r="C336" s="2"/>
       <c r="D336" s="2"/>
       <c r="E336" s="2"/>
@@ -9992,7 +9988,7 @@
       <c r="V336" s="2"/>
       <c r="W336" s="2"/>
     </row>
-    <row r="337" ht="13.2" spans="3:23">
+    <row r="337" ht="12.75" spans="3:23">
       <c r="C337" s="2"/>
       <c r="D337" s="2"/>
       <c r="E337" s="2"/>
@@ -10015,7 +10011,7 @@
       <c r="V337" s="2"/>
       <c r="W337" s="2"/>
     </row>
-    <row r="338" ht="13.2" spans="3:23">
+    <row r="338" ht="12.75" spans="3:23">
       <c r="C338" s="2"/>
       <c r="D338" s="2"/>
       <c r="E338" s="2"/>
@@ -10038,7 +10034,7 @@
       <c r="V338" s="2"/>
       <c r="W338" s="2"/>
     </row>
-    <row r="339" ht="13.2" spans="3:23">
+    <row r="339" ht="12.75" spans="3:23">
       <c r="C339" s="2"/>
       <c r="D339" s="2"/>
       <c r="E339" s="2"/>
@@ -10061,7 +10057,7 @@
       <c r="V339" s="2"/>
       <c r="W339" s="2"/>
     </row>
-    <row r="340" ht="13.2" spans="3:23">
+    <row r="340" ht="12.75" spans="3:23">
       <c r="C340" s="2"/>
       <c r="D340" s="2"/>
       <c r="E340" s="2"/>
@@ -10084,7 +10080,7 @@
       <c r="V340" s="2"/>
       <c r="W340" s="2"/>
     </row>
-    <row r="341" ht="13.2" spans="3:23">
+    <row r="341" ht="12.75" spans="3:23">
       <c r="C341" s="2"/>
       <c r="D341" s="2"/>
       <c r="E341" s="2"/>
@@ -10107,7 +10103,7 @@
       <c r="V341" s="2"/>
       <c r="W341" s="2"/>
     </row>
-    <row r="342" ht="13.2" spans="3:23">
+    <row r="342" ht="12.75" spans="3:23">
       <c r="C342" s="2"/>
       <c r="D342" s="2"/>
       <c r="E342" s="2"/>
@@ -10130,7 +10126,7 @@
       <c r="V342" s="2"/>
       <c r="W342" s="2"/>
     </row>
-    <row r="343" ht="13.2" spans="3:23">
+    <row r="343" ht="12.75" spans="3:23">
       <c r="C343" s="2"/>
       <c r="D343" s="2"/>
       <c r="E343" s="2"/>
@@ -10153,7 +10149,7 @@
       <c r="V343" s="2"/>
       <c r="W343" s="2"/>
     </row>
-    <row r="344" ht="13.2" spans="3:23">
+    <row r="344" ht="12.75" spans="3:23">
       <c r="C344" s="2"/>
       <c r="D344" s="2"/>
       <c r="E344" s="2"/>
@@ -10176,7 +10172,7 @@
       <c r="V344" s="2"/>
       <c r="W344" s="2"/>
     </row>
-    <row r="345" ht="13.2" spans="3:23">
+    <row r="345" ht="12.75" spans="3:23">
       <c r="C345" s="2"/>
       <c r="D345" s="2"/>
       <c r="E345" s="2"/>
@@ -10199,7 +10195,7 @@
       <c r="V345" s="2"/>
       <c r="W345" s="2"/>
     </row>
-    <row r="346" ht="13.2" spans="3:23">
+    <row r="346" ht="12.75" spans="3:23">
       <c r="C346" s="2"/>
       <c r="D346" s="2"/>
       <c r="E346" s="2"/>
@@ -10222,7 +10218,7 @@
       <c r="V346" s="2"/>
       <c r="W346" s="2"/>
     </row>
-    <row r="347" ht="13.2" spans="3:23">
+    <row r="347" ht="12.75" spans="3:23">
       <c r="C347" s="2"/>
       <c r="D347" s="2"/>
       <c r="E347" s="2"/>
@@ -10245,7 +10241,7 @@
       <c r="V347" s="2"/>
       <c r="W347" s="2"/>
     </row>
-    <row r="348" ht="13.2" spans="3:23">
+    <row r="348" ht="12.75" spans="3:23">
       <c r="C348" s="2"/>
       <c r="D348" s="2"/>
       <c r="E348" s="2"/>
@@ -10268,7 +10264,7 @@
       <c r="V348" s="2"/>
       <c r="W348" s="2"/>
     </row>
-    <row r="349" ht="13.2" spans="3:23">
+    <row r="349" ht="12.75" spans="3:23">
       <c r="C349" s="2"/>
       <c r="D349" s="2"/>
       <c r="E349" s="2"/>
@@ -10291,7 +10287,7 @@
       <c r="V349" s="2"/>
       <c r="W349" s="2"/>
     </row>
-    <row r="350" ht="13.2" spans="3:23">
+    <row r="350" ht="12.75" spans="3:23">
       <c r="C350" s="2"/>
       <c r="D350" s="2"/>
       <c r="E350" s="2"/>
@@ -10314,7 +10310,7 @@
       <c r="V350" s="2"/>
       <c r="W350" s="2"/>
     </row>
-    <row r="351" ht="13.2" spans="3:23">
+    <row r="351" ht="12.75" spans="3:23">
       <c r="C351" s="2"/>
       <c r="D351" s="2"/>
       <c r="E351" s="2"/>
@@ -10337,7 +10333,7 @@
       <c r="V351" s="2"/>
       <c r="W351" s="2"/>
     </row>
-    <row r="352" ht="13.2" spans="3:23">
+    <row r="352" ht="12.75" spans="3:23">
       <c r="C352" s="2"/>
       <c r="D352" s="2"/>
       <c r="E352" s="2"/>
@@ -10360,7 +10356,7 @@
       <c r="V352" s="2"/>
       <c r="W352" s="2"/>
     </row>
-    <row r="353" ht="13.2" spans="3:23">
+    <row r="353" ht="12.75" spans="3:23">
       <c r="C353" s="2"/>
       <c r="D353" s="2"/>
       <c r="E353" s="2"/>
@@ -10383,7 +10379,7 @@
       <c r="V353" s="2"/>
       <c r="W353" s="2"/>
     </row>
-    <row r="354" ht="13.2" spans="3:23">
+    <row r="354" ht="12.75" spans="3:23">
       <c r="C354" s="2"/>
       <c r="D354" s="2"/>
       <c r="E354" s="2"/>
@@ -10406,7 +10402,7 @@
       <c r="V354" s="2"/>
       <c r="W354" s="2"/>
     </row>
-    <row r="355" ht="13.2" spans="3:23">
+    <row r="355" ht="12.75" spans="3:23">
       <c r="C355" s="2"/>
       <c r="D355" s="2"/>
       <c r="E355" s="2"/>
@@ -10429,7 +10425,7 @@
       <c r="V355" s="2"/>
       <c r="W355" s="2"/>
     </row>
-    <row r="356" ht="13.2" spans="3:23">
+    <row r="356" ht="12.75" spans="3:23">
       <c r="C356" s="2"/>
       <c r="D356" s="2"/>
       <c r="E356" s="2"/>
@@ -10452,7 +10448,7 @@
       <c r="V356" s="2"/>
       <c r="W356" s="2"/>
     </row>
-    <row r="357" ht="13.2" spans="3:23">
+    <row r="357" ht="12.75" spans="3:23">
       <c r="C357" s="2"/>
       <c r="D357" s="2"/>
       <c r="E357" s="2"/>
@@ -10475,7 +10471,7 @@
       <c r="V357" s="2"/>
       <c r="W357" s="2"/>
     </row>
-    <row r="358" ht="13.2" spans="3:23">
+    <row r="358" ht="12.75" spans="3:23">
       <c r="C358" s="2"/>
       <c r="D358" s="2"/>
       <c r="E358" s="2"/>
@@ -10498,7 +10494,7 @@
       <c r="V358" s="2"/>
       <c r="W358" s="2"/>
     </row>
-    <row r="359" ht="13.2" spans="3:23">
+    <row r="359" ht="12.75" spans="3:23">
       <c r="C359" s="2"/>
       <c r="D359" s="2"/>
       <c r="E359" s="2"/>
@@ -10521,7 +10517,7 @@
       <c r="V359" s="2"/>
       <c r="W359" s="2"/>
     </row>
-    <row r="360" ht="13.2" spans="3:23">
+    <row r="360" ht="12.75" spans="3:23">
       <c r="C360" s="2"/>
       <c r="D360" s="2"/>
       <c r="E360" s="2"/>
@@ -10544,7 +10540,7 @@
       <c r="V360" s="2"/>
       <c r="W360" s="2"/>
     </row>
-    <row r="361" ht="13.2" spans="3:23">
+    <row r="361" ht="12.75" spans="3:23">
       <c r="C361" s="2"/>
       <c r="D361" s="2"/>
       <c r="E361" s="2"/>
@@ -10567,7 +10563,7 @@
       <c r="V361" s="2"/>
       <c r="W361" s="2"/>
     </row>
-    <row r="362" ht="13.2" spans="3:23">
+    <row r="362" ht="12.75" spans="3:23">
       <c r="C362" s="2"/>
       <c r="D362" s="2"/>
       <c r="E362" s="2"/>
@@ -10590,7 +10586,7 @@
       <c r="V362" s="2"/>
       <c r="W362" s="2"/>
     </row>
-    <row r="363" ht="13.2" spans="3:23">
+    <row r="363" ht="12.75" spans="3:23">
       <c r="C363" s="2"/>
       <c r="D363" s="2"/>
       <c r="E363" s="2"/>
@@ -10613,7 +10609,7 @@
       <c r="V363" s="2"/>
       <c r="W363" s="2"/>
     </row>
-    <row r="364" ht="13.2" spans="3:23">
+    <row r="364" ht="12.75" spans="3:23">
       <c r="C364" s="2"/>
       <c r="D364" s="2"/>
       <c r="E364" s="2"/>
@@ -10636,7 +10632,7 @@
       <c r="V364" s="2"/>
       <c r="W364" s="2"/>
     </row>
-    <row r="365" ht="13.2" spans="3:23">
+    <row r="365" ht="12.75" spans="3:23">
       <c r="C365" s="2"/>
       <c r="D365" s="2"/>
       <c r="E365" s="2"/>
@@ -10659,7 +10655,7 @@
       <c r="V365" s="2"/>
       <c r="W365" s="2"/>
     </row>
-    <row r="366" ht="13.2" spans="3:23">
+    <row r="366" ht="12.75" spans="3:23">
       <c r="C366" s="2"/>
       <c r="D366" s="2"/>
       <c r="E366" s="2"/>
@@ -10682,7 +10678,7 @@
       <c r="V366" s="2"/>
       <c r="W366" s="2"/>
     </row>
-    <row r="367" ht="13.2" spans="3:23">
+    <row r="367" ht="12.75" spans="3:23">
       <c r="C367" s="2"/>
       <c r="D367" s="2"/>
       <c r="E367" s="2"/>
@@ -10705,7 +10701,7 @@
       <c r="V367" s="2"/>
       <c r="W367" s="2"/>
     </row>
-    <row r="368" ht="13.2" spans="3:23">
+    <row r="368" ht="12.75" spans="3:23">
       <c r="C368" s="2"/>
       <c r="D368" s="2"/>
       <c r="E368" s="2"/>
@@ -10728,7 +10724,7 @@
       <c r="V368" s="2"/>
       <c r="W368" s="2"/>
     </row>
-    <row r="369" ht="13.2" spans="3:23">
+    <row r="369" ht="12.75" spans="3:23">
       <c r="C369" s="2"/>
       <c r="D369" s="2"/>
       <c r="E369" s="2"/>
@@ -10751,7 +10747,7 @@
       <c r="V369" s="2"/>
       <c r="W369" s="2"/>
     </row>
-    <row r="370" ht="13.2" spans="3:23">
+    <row r="370" ht="12.75" spans="3:23">
       <c r="C370" s="2"/>
       <c r="D370" s="2"/>
       <c r="E370" s="2"/>
@@ -10774,7 +10770,7 @@
       <c r="V370" s="2"/>
       <c r="W370" s="2"/>
     </row>
-    <row r="371" ht="13.2" spans="3:23">
+    <row r="371" ht="12.75" spans="3:23">
       <c r="C371" s="2"/>
       <c r="D371" s="2"/>
       <c r="E371" s="2"/>
@@ -10797,7 +10793,7 @@
       <c r="V371" s="2"/>
       <c r="W371" s="2"/>
     </row>
-    <row r="372" ht="13.2" spans="3:23">
+    <row r="372" ht="12.75" spans="3:23">
       <c r="C372" s="2"/>
       <c r="D372" s="2"/>
       <c r="E372" s="2"/>
@@ -10820,7 +10816,7 @@
       <c r="V372" s="2"/>
       <c r="W372" s="2"/>
     </row>
-    <row r="373" ht="13.2" spans="3:23">
+    <row r="373" ht="12.75" spans="3:23">
       <c r="C373" s="2"/>
       <c r="D373" s="2"/>
       <c r="E373" s="2"/>
@@ -10843,7 +10839,7 @@
       <c r="V373" s="2"/>
       <c r="W373" s="2"/>
     </row>
-    <row r="374" ht="13.2" spans="3:23">
+    <row r="374" ht="12.75" spans="3:23">
       <c r="C374" s="2"/>
       <c r="D374" s="2"/>
       <c r="E374" s="2"/>
@@ -10866,7 +10862,7 @@
       <c r="V374" s="2"/>
       <c r="W374" s="2"/>
     </row>
-    <row r="375" ht="13.2" spans="3:23">
+    <row r="375" ht="12.75" spans="3:23">
       <c r="C375" s="2"/>
       <c r="D375" s="2"/>
       <c r="E375" s="2"/>
@@ -10889,7 +10885,7 @@
       <c r="V375" s="2"/>
       <c r="W375" s="2"/>
     </row>
-    <row r="376" ht="13.2" spans="3:23">
+    <row r="376" ht="12.75" spans="3:23">
       <c r="C376" s="2"/>
       <c r="D376" s="2"/>
       <c r="E376" s="2"/>
@@ -10912,7 +10908,7 @@
       <c r="V376" s="2"/>
       <c r="W376" s="2"/>
     </row>
-    <row r="377" ht="13.2" spans="3:23">
+    <row r="377" ht="12.75" spans="3:23">
       <c r="C377" s="2"/>
       <c r="D377" s="2"/>
       <c r="E377" s="2"/>
@@ -10935,7 +10931,7 @@
       <c r="V377" s="2"/>
       <c r="W377" s="2"/>
     </row>
-    <row r="378" ht="13.2" spans="3:23">
+    <row r="378" ht="12.75" spans="3:23">
       <c r="C378" s="2"/>
       <c r="D378" s="2"/>
       <c r="E378" s="2"/>
@@ -10958,7 +10954,7 @@
       <c r="V378" s="2"/>
       <c r="W378" s="2"/>
     </row>
-    <row r="379" ht="13.2" spans="3:23">
+    <row r="379" ht="12.75" spans="3:23">
       <c r="C379" s="2"/>
       <c r="D379" s="2"/>
       <c r="E379" s="2"/>
@@ -10981,7 +10977,7 @@
       <c r="V379" s="2"/>
       <c r="W379" s="2"/>
     </row>
-    <row r="380" ht="13.2" spans="3:23">
+    <row r="380" ht="12.75" spans="3:23">
       <c r="C380" s="2"/>
       <c r="D380" s="2"/>
       <c r="E380" s="2"/>
@@ -11004,7 +11000,7 @@
       <c r="V380" s="2"/>
       <c r="W380" s="2"/>
     </row>
-    <row r="381" ht="13.2" spans="3:23">
+    <row r="381" ht="12.75" spans="3:23">
       <c r="C381" s="2"/>
       <c r="D381" s="2"/>
       <c r="E381" s="2"/>
@@ -11027,7 +11023,7 @@
       <c r="V381" s="2"/>
       <c r="W381" s="2"/>
     </row>
-    <row r="382" ht="13.2" spans="3:23">
+    <row r="382" ht="12.75" spans="3:23">
       <c r="C382" s="2"/>
       <c r="D382" s="2"/>
       <c r="E382" s="2"/>
@@ -11050,7 +11046,7 @@
       <c r="V382" s="2"/>
       <c r="W382" s="2"/>
     </row>
-    <row r="383" ht="13.2" spans="3:23">
+    <row r="383" ht="12.75" spans="3:23">
       <c r="C383" s="2"/>
       <c r="D383" s="2"/>
       <c r="E383" s="2"/>
@@ -11073,7 +11069,7 @@
       <c r="V383" s="2"/>
       <c r="W383" s="2"/>
     </row>
-    <row r="384" ht="13.2" spans="3:23">
+    <row r="384" ht="12.75" spans="3:23">
       <c r="C384" s="2"/>
       <c r="D384" s="2"/>
       <c r="E384" s="2"/>
@@ -11096,7 +11092,7 @@
       <c r="V384" s="2"/>
       <c r="W384" s="2"/>
     </row>
-    <row r="385" ht="13.2" spans="3:23">
+    <row r="385" ht="12.75" spans="3:23">
       <c r="C385" s="2"/>
       <c r="D385" s="2"/>
       <c r="E385" s="2"/>
@@ -11119,7 +11115,7 @@
       <c r="V385" s="2"/>
       <c r="W385" s="2"/>
     </row>
-    <row r="386" ht="13.2" spans="3:23">
+    <row r="386" ht="12.75" spans="3:23">
       <c r="C386" s="2"/>
       <c r="D386" s="2"/>
       <c r="E386" s="2"/>
@@ -11142,7 +11138,7 @@
       <c r="V386" s="2"/>
       <c r="W386" s="2"/>
     </row>
-    <row r="387" ht="13.2" spans="3:23">
+    <row r="387" ht="12.75" spans="3:23">
       <c r="C387" s="2"/>
       <c r="D387" s="2"/>
       <c r="E387" s="2"/>
@@ -11165,7 +11161,7 @@
       <c r="V387" s="2"/>
       <c r="W387" s="2"/>
     </row>
-    <row r="388" ht="13.2" spans="3:23">
+    <row r="388" ht="12.75" spans="3:23">
       <c r="C388" s="2"/>
       <c r="D388" s="2"/>
       <c r="E388" s="2"/>
@@ -11188,7 +11184,7 @@
       <c r="V388" s="2"/>
       <c r="W388" s="2"/>
     </row>
-    <row r="389" ht="13.2" spans="3:23">
+    <row r="389" ht="12.75" spans="3:23">
       <c r="C389" s="2"/>
       <c r="D389" s="2"/>
       <c r="E389" s="2"/>
@@ -11211,7 +11207,7 @@
       <c r="V389" s="2"/>
       <c r="W389" s="2"/>
     </row>
-    <row r="390" ht="13.2" spans="3:23">
+    <row r="390" ht="12.75" spans="3:23">
       <c r="C390" s="2"/>
       <c r="D390" s="2"/>
       <c r="E390" s="2"/>
@@ -11234,7 +11230,7 @@
       <c r="V390" s="2"/>
       <c r="W390" s="2"/>
     </row>
-    <row r="391" ht="13.2" spans="3:23">
+    <row r="391" ht="12.75" spans="3:23">
       <c r="C391" s="2"/>
       <c r="D391" s="2"/>
       <c r="E391" s="2"/>
@@ -11257,7 +11253,7 @@
       <c r="V391" s="2"/>
       <c r="W391" s="2"/>
     </row>
-    <row r="392" ht="13.2" spans="3:23">
+    <row r="392" ht="12.75" spans="3:23">
       <c r="C392" s="2"/>
       <c r="D392" s="2"/>
       <c r="E392" s="2"/>
@@ -11280,7 +11276,7 @@
       <c r="V392" s="2"/>
       <c r="W392" s="2"/>
     </row>
-    <row r="393" ht="13.2" spans="3:23">
+    <row r="393" ht="12.75" spans="3:23">
       <c r="C393" s="2"/>
       <c r="D393" s="2"/>
       <c r="E393" s="2"/>
@@ -11303,7 +11299,7 @@
       <c r="V393" s="2"/>
       <c r="W393" s="2"/>
     </row>
-    <row r="394" ht="13.2" spans="3:23">
+    <row r="394" ht="12.75" spans="3:23">
       <c r="C394" s="2"/>
       <c r="D394" s="2"/>
       <c r="E394" s="2"/>
@@ -11326,7 +11322,7 @@
       <c r="V394" s="2"/>
       <c r="W394" s="2"/>
     </row>
-    <row r="395" ht="13.2" spans="3:23">
+    <row r="395" ht="12.75" spans="3:23">
       <c r="C395" s="2"/>
       <c r="D395" s="2"/>
       <c r="E395" s="2"/>
@@ -11349,7 +11345,7 @@
       <c r="V395" s="2"/>
       <c r="W395" s="2"/>
     </row>
-    <row r="396" ht="13.2" spans="3:23">
+    <row r="396" ht="12.75" spans="3:23">
       <c r="C396" s="2"/>
       <c r="D396" s="2"/>
       <c r="E396" s="2"/>
@@ -11372,7 +11368,7 @@
       <c r="V396" s="2"/>
       <c r="W396" s="2"/>
     </row>
-    <row r="397" ht="13.2" spans="3:23">
+    <row r="397" ht="12.75" spans="3:23">
       <c r="C397" s="2"/>
       <c r="D397" s="2"/>
       <c r="E397" s="2"/>
@@ -11395,7 +11391,7 @@
       <c r="V397" s="2"/>
       <c r="W397" s="2"/>
     </row>
-    <row r="398" ht="13.2" spans="3:23">
+    <row r="398" ht="12.75" spans="3:23">
       <c r="C398" s="2"/>
       <c r="D398" s="2"/>
       <c r="E398" s="2"/>
@@ -11418,7 +11414,7 @@
       <c r="V398" s="2"/>
       <c r="W398" s="2"/>
     </row>
-    <row r="399" ht="13.2" spans="3:23">
+    <row r="399" ht="12.75" spans="3:23">
       <c r="C399" s="2"/>
       <c r="D399" s="2"/>
       <c r="E399" s="2"/>
@@ -11441,7 +11437,7 @@
       <c r="V399" s="2"/>
       <c r="W399" s="2"/>
     </row>
-    <row r="400" ht="13.2" spans="3:23">
+    <row r="400" ht="12.75" spans="3:23">
       <c r="C400" s="2"/>
       <c r="D400" s="2"/>
       <c r="E400" s="2"/>
@@ -11464,7 +11460,7 @@
       <c r="V400" s="2"/>
       <c r="W400" s="2"/>
     </row>
-    <row r="401" ht="13.2" spans="3:23">
+    <row r="401" ht="12.75" spans="3:23">
       <c r="C401" s="2"/>
       <c r="D401" s="2"/>
       <c r="E401" s="2"/>
@@ -11487,7 +11483,7 @@
       <c r="V401" s="2"/>
       <c r="W401" s="2"/>
     </row>
-    <row r="402" ht="13.2" spans="3:23">
+    <row r="402" ht="12.75" spans="3:23">
       <c r="C402" s="2"/>
       <c r="D402" s="2"/>
       <c r="E402" s="2"/>
@@ -11510,7 +11506,7 @@
       <c r="V402" s="2"/>
       <c r="W402" s="2"/>
     </row>
-    <row r="403" ht="13.2" spans="3:23">
+    <row r="403" ht="12.75" spans="3:23">
       <c r="C403" s="2"/>
       <c r="D403" s="2"/>
       <c r="E403" s="2"/>
@@ -11533,7 +11529,7 @@
       <c r="V403" s="2"/>
       <c r="W403" s="2"/>
     </row>
-    <row r="404" ht="13.2" spans="3:23">
+    <row r="404" ht="12.75" spans="3:23">
       <c r="C404" s="2"/>
       <c r="D404" s="2"/>
       <c r="E404" s="2"/>
@@ -11556,7 +11552,7 @@
       <c r="V404" s="2"/>
       <c r="W404" s="2"/>
     </row>
-    <row r="405" ht="13.2" spans="3:23">
+    <row r="405" ht="12.75" spans="3:23">
       <c r="C405" s="2"/>
       <c r="D405" s="2"/>
       <c r="E405" s="2"/>
@@ -11579,7 +11575,7 @@
       <c r="V405" s="2"/>
       <c r="W405" s="2"/>
     </row>
-    <row r="406" ht="13.2" spans="3:23">
+    <row r="406" ht="12.75" spans="3:23">
       <c r="C406" s="2"/>
       <c r="D406" s="2"/>
       <c r="E406" s="2"/>
@@ -11602,7 +11598,7 @@
       <c r="V406" s="2"/>
       <c r="W406" s="2"/>
     </row>
-    <row r="407" ht="13.2" spans="3:23">
+    <row r="407" ht="12.75" spans="3:23">
       <c r="C407" s="2"/>
       <c r="D407" s="2"/>
       <c r="E407" s="2"/>
@@ -11625,7 +11621,7 @@
       <c r="V407" s="2"/>
       <c r="W407" s="2"/>
     </row>
-    <row r="408" ht="13.2" spans="3:23">
+    <row r="408" ht="12.75" spans="3:23">
       <c r="C408" s="2"/>
       <c r="D408" s="2"/>
       <c r="E408" s="2"/>
@@ -11648,7 +11644,7 @@
       <c r="V408" s="2"/>
       <c r="W408" s="2"/>
     </row>
-    <row r="409" ht="13.2" spans="3:23">
+    <row r="409" ht="12.75" spans="3:23">
       <c r="C409" s="2"/>
       <c r="D409" s="2"/>
       <c r="E409" s="2"/>
@@ -11671,7 +11667,7 @@
       <c r="V409" s="2"/>
       <c r="W409" s="2"/>
     </row>
-    <row r="410" ht="13.2" spans="3:23">
+    <row r="410" ht="12.75" spans="3:23">
       <c r="C410" s="2"/>
       <c r="D410" s="2"/>
       <c r="E410" s="2"/>
@@ -11694,7 +11690,7 @@
       <c r="V410" s="2"/>
       <c r="W410" s="2"/>
     </row>
-    <row r="411" ht="13.2" spans="3:23">
+    <row r="411" ht="12.75" spans="3:23">
       <c r="C411" s="2"/>
       <c r="D411" s="2"/>
       <c r="E411" s="2"/>
@@ -11717,7 +11713,7 @@
       <c r="V411" s="2"/>
       <c r="W411" s="2"/>
     </row>
-    <row r="412" ht="13.2" spans="3:23">
+    <row r="412" ht="12.75" spans="3:23">
       <c r="C412" s="2"/>
       <c r="D412" s="2"/>
       <c r="E412" s="2"/>
@@ -11740,7 +11736,7 @@
       <c r="V412" s="2"/>
       <c r="W412" s="2"/>
     </row>
-    <row r="413" ht="13.2" spans="3:23">
+    <row r="413" ht="12.75" spans="3:23">
       <c r="C413" s="2"/>
       <c r="D413" s="2"/>
       <c r="E413" s="2"/>
@@ -11763,7 +11759,7 @@
       <c r="V413" s="2"/>
       <c r="W413" s="2"/>
     </row>
-    <row r="414" ht="13.2" spans="3:23">
+    <row r="414" ht="12.75" spans="3:23">
       <c r="C414" s="2"/>
       <c r="D414" s="2"/>
       <c r="E414" s="2"/>
@@ -11786,7 +11782,7 @@
       <c r="V414" s="2"/>
       <c r="W414" s="2"/>
     </row>
-    <row r="415" ht="13.2" spans="3:23">
+    <row r="415" ht="12.75" spans="3:23">
       <c r="C415" s="2"/>
       <c r="D415" s="2"/>
       <c r="E415" s="2"/>
@@ -11809,7 +11805,7 @@
       <c r="V415" s="2"/>
       <c r="W415" s="2"/>
     </row>
-    <row r="416" ht="13.2" spans="3:23">
+    <row r="416" ht="12.75" spans="3:23">
       <c r="C416" s="2"/>
       <c r="D416" s="2"/>
       <c r="E416" s="2"/>
@@ -11832,7 +11828,7 @@
       <c r="V416" s="2"/>
       <c r="W416" s="2"/>
     </row>
-    <row r="417" ht="13.2" spans="3:23">
+    <row r="417" ht="12.75" spans="3:23">
       <c r="C417" s="2"/>
       <c r="D417" s="2"/>
       <c r="E417" s="2"/>
@@ -11855,7 +11851,7 @@
       <c r="V417" s="2"/>
       <c r="W417" s="2"/>
     </row>
-    <row r="418" ht="13.2" spans="3:23">
+    <row r="418" ht="12.75" spans="3:23">
       <c r="C418" s="2"/>
       <c r="D418" s="2"/>
       <c r="E418" s="2"/>
@@ -11878,7 +11874,7 @@
       <c r="V418" s="2"/>
       <c r="W418" s="2"/>
     </row>
-    <row r="419" ht="13.2" spans="3:23">
+    <row r="419" ht="12.75" spans="3:23">
       <c r="C419" s="2"/>
       <c r="D419" s="2"/>
       <c r="E419" s="2"/>
@@ -11901,7 +11897,7 @@
       <c r="V419" s="2"/>
       <c r="W419" s="2"/>
     </row>
-    <row r="420" ht="13.2" spans="3:23">
+    <row r="420" ht="12.75" spans="3:23">
       <c r="C420" s="2"/>
       <c r="D420" s="2"/>
       <c r="E420" s="2"/>
@@ -11924,7 +11920,7 @@
       <c r="V420" s="2"/>
       <c r="W420" s="2"/>
     </row>
-    <row r="421" ht="13.2" spans="3:23">
+    <row r="421" ht="12.75" spans="3:23">
       <c r="C421" s="2"/>
       <c r="D421" s="2"/>
       <c r="E421" s="2"/>
@@ -11947,7 +11943,7 @@
       <c r="V421" s="2"/>
       <c r="W421" s="2"/>
     </row>
-    <row r="422" ht="13.2" spans="3:23">
+    <row r="422" ht="12.75" spans="3:23">
       <c r="C422" s="2"/>
       <c r="D422" s="2"/>
       <c r="E422" s="2"/>
@@ -11970,7 +11966,7 @@
       <c r="V422" s="2"/>
       <c r="W422" s="2"/>
     </row>
-    <row r="423" ht="13.2" spans="3:23">
+    <row r="423" ht="12.75" spans="3:23">
       <c r="C423" s="2"/>
       <c r="D423" s="2"/>
       <c r="E423" s="2"/>
@@ -11993,7 +11989,7 @@
       <c r="V423" s="2"/>
       <c r="W423" s="2"/>
     </row>
-    <row r="424" ht="13.2" spans="3:23">
+    <row r="424" ht="12.75" spans="3:23">
       <c r="C424" s="2"/>
       <c r="D424" s="2"/>
       <c r="E424" s="2"/>
@@ -12016,7 +12012,7 @@
       <c r="V424" s="2"/>
       <c r="W424" s="2"/>
     </row>
-    <row r="425" ht="13.2" spans="3:23">
+    <row r="425" ht="12.75" spans="3:23">
       <c r="C425" s="2"/>
       <c r="D425" s="2"/>
       <c r="E425" s="2"/>
@@ -12039,7 +12035,7 @@
       <c r="V425" s="2"/>
       <c r="W425" s="2"/>
     </row>
-    <row r="426" ht="13.2" spans="3:23">
+    <row r="426" ht="12.75" spans="3:23">
       <c r="C426" s="2"/>
       <c r="D426" s="2"/>
       <c r="E426" s="2"/>
@@ -12062,7 +12058,7 @@
       <c r="V426" s="2"/>
       <c r="W426" s="2"/>
     </row>
-    <row r="427" ht="13.2" spans="3:23">
+    <row r="427" ht="12.75" spans="3:23">
       <c r="C427" s="2"/>
       <c r="D427" s="2"/>
       <c r="E427" s="2"/>
@@ -12085,7 +12081,7 @@
       <c r="V427" s="2"/>
       <c r="W427" s="2"/>
     </row>
-    <row r="428" ht="13.2" spans="3:23">
+    <row r="428" ht="12.75" spans="3:23">
       <c r="C428" s="2"/>
       <c r="D428" s="2"/>
       <c r="E428" s="2"/>
@@ -12108,7 +12104,7 @@
       <c r="V428" s="2"/>
       <c r="W428" s="2"/>
     </row>
-    <row r="429" ht="13.2" spans="3:23">
+    <row r="429" ht="12.75" spans="3:23">
       <c r="C429" s="2"/>
       <c r="D429" s="2"/>
       <c r="E429" s="2"/>
@@ -12131,7 +12127,7 @@
       <c r="V429" s="2"/>
       <c r="W429" s="2"/>
     </row>
-    <row r="430" ht="13.2" spans="3:23">
+    <row r="430" ht="12.75" spans="3:23">
       <c r="C430" s="2"/>
       <c r="D430" s="2"/>
       <c r="E430" s="2"/>
@@ -12154,7 +12150,7 @@
       <c r="V430" s="2"/>
       <c r="W430" s="2"/>
     </row>
-    <row r="431" ht="13.2" spans="3:23">
+    <row r="431" ht="12.75" spans="3:23">
       <c r="C431" s="2"/>
       <c r="D431" s="2"/>
       <c r="E431" s="2"/>
@@ -12177,7 +12173,7 @@
       <c r="V431" s="2"/>
       <c r="W431" s="2"/>
     </row>
-    <row r="432" ht="13.2" spans="3:23">
+    <row r="432" ht="12.75" spans="3:23">
       <c r="C432" s="2"/>
       <c r="D432" s="2"/>
       <c r="E432" s="2"/>
@@ -12200,7 +12196,7 @@
       <c r="V432" s="2"/>
       <c r="W432" s="2"/>
     </row>
-    <row r="433" ht="13.2" spans="3:23">
+    <row r="433" ht="12.75" spans="3:23">
       <c r="C433" s="2"/>
       <c r="D433" s="2"/>
       <c r="E433" s="2"/>
@@ -12223,7 +12219,7 @@
       <c r="V433" s="2"/>
       <c r="W433" s="2"/>
     </row>
-    <row r="434" ht="13.2" spans="3:23">
+    <row r="434" ht="12.75" spans="3:23">
       <c r="C434" s="2"/>
       <c r="D434" s="2"/>
       <c r="E434" s="2"/>
@@ -12246,7 +12242,7 @@
       <c r="V434" s="2"/>
       <c r="W434" s="2"/>
     </row>
-    <row r="435" ht="13.2" spans="3:23">
+    <row r="435" ht="12.75" spans="3:23">
       <c r="C435" s="2"/>
       <c r="D435" s="2"/>
       <c r="E435" s="2"/>
@@ -12269,7 +12265,7 @@
       <c r="V435" s="2"/>
       <c r="W435" s="2"/>
     </row>
-    <row r="436" ht="13.2" spans="3:23">
+    <row r="436" ht="12.75" spans="3:23">
       <c r="C436" s="2"/>
       <c r="D436" s="2"/>
       <c r="E436" s="2"/>
@@ -12292,7 +12288,7 @@
       <c r="V436" s="2"/>
       <c r="W436" s="2"/>
     </row>
-    <row r="437" ht="13.2" spans="3:23">
+    <row r="437" ht="12.75" spans="3:23">
       <c r="C437" s="2"/>
       <c r="D437" s="2"/>
       <c r="E437" s="2"/>
@@ -12315,7 +12311,7 @@
       <c r="V437" s="2"/>
       <c r="W437" s="2"/>
     </row>
-    <row r="438" ht="13.2" spans="3:23">
+    <row r="438" ht="12.75" spans="3:23">
       <c r="C438" s="2"/>
       <c r="D438" s="2"/>
       <c r="E438" s="2"/>
@@ -12338,7 +12334,7 @@
       <c r="V438" s="2"/>
       <c r="W438" s="2"/>
     </row>
-    <row r="439" ht="13.2" spans="3:23">
+    <row r="439" ht="12.75" spans="3:23">
       <c r="C439" s="2"/>
       <c r="D439" s="2"/>
       <c r="E439" s="2"/>
@@ -12361,7 +12357,7 @@
       <c r="V439" s="2"/>
       <c r="W439" s="2"/>
     </row>
-    <row r="440" ht="13.2" spans="3:23">
+    <row r="440" ht="12.75" spans="3:23">
       <c r="C440" s="2"/>
       <c r="D440" s="2"/>
       <c r="E440" s="2"/>
@@ -12384,7 +12380,7 @@
       <c r="V440" s="2"/>
       <c r="W440" s="2"/>
     </row>
-    <row r="441" ht="13.2" spans="3:23">
+    <row r="441" ht="12.75" spans="3:23">
       <c r="C441" s="2"/>
       <c r="D441" s="2"/>
       <c r="E441" s="2"/>
@@ -12407,7 +12403,7 @@
       <c r="V441" s="2"/>
       <c r="W441" s="2"/>
     </row>
-    <row r="442" ht="13.2" spans="3:23">
+    <row r="442" ht="12.75" spans="3:23">
       <c r="C442" s="2"/>
       <c r="D442" s="2"/>
       <c r="E442" s="2"/>
@@ -12430,7 +12426,7 @@
       <c r="V442" s="2"/>
       <c r="W442" s="2"/>
     </row>
-    <row r="443" ht="13.2" spans="3:23">
+    <row r="443" ht="12.75" spans="3:23">
       <c r="C443" s="2"/>
       <c r="D443" s="2"/>
       <c r="E443" s="2"/>
@@ -12453,7 +12449,7 @@
       <c r="V443" s="2"/>
       <c r="W443" s="2"/>
     </row>
-    <row r="444" ht="13.2" spans="3:23">
+    <row r="444" ht="12.75" spans="3:23">
       <c r="C444" s="2"/>
       <c r="D444" s="2"/>
       <c r="E444" s="2"/>
@@ -12476,7 +12472,7 @@
       <c r="V444" s="2"/>
       <c r="W444" s="2"/>
     </row>
-    <row r="445" ht="13.2" spans="3:23">
+    <row r="445" ht="12.75" spans="3:23">
       <c r="C445" s="2"/>
       <c r="D445" s="2"/>
       <c r="E445" s="2"/>
@@ -12499,7 +12495,7 @@
       <c r="V445" s="2"/>
       <c r="W445" s="2"/>
     </row>
-    <row r="446" ht="13.2" spans="3:23">
+    <row r="446" ht="12.75" spans="3:23">
       <c r="C446" s="2"/>
       <c r="D446" s="2"/>
       <c r="E446" s="2"/>
@@ -12522,7 +12518,7 @@
       <c r="V446" s="2"/>
       <c r="W446" s="2"/>
     </row>
-    <row r="447" ht="13.2" spans="3:23">
+    <row r="447" ht="12.75" spans="3:23">
       <c r="C447" s="2"/>
       <c r="D447" s="2"/>
       <c r="E447" s="2"/>
@@ -12545,7 +12541,7 @@
       <c r="V447" s="2"/>
       <c r="W447" s="2"/>
     </row>
-    <row r="448" ht="13.2" spans="3:23">
+    <row r="448" ht="12.75" spans="3:23">
       <c r="C448" s="2"/>
       <c r="D448" s="2"/>
       <c r="E448" s="2"/>
@@ -12568,7 +12564,7 @@
       <c r="V448" s="2"/>
       <c r="W448" s="2"/>
     </row>
-    <row r="449" ht="13.2" spans="3:23">
+    <row r="449" ht="12.75" spans="3:23">
       <c r="C449" s="2"/>
       <c r="D449" s="2"/>
       <c r="E449" s="2"/>
@@ -12591,7 +12587,7 @@
       <c r="V449" s="2"/>
       <c r="W449" s="2"/>
     </row>
-    <row r="450" ht="13.2" spans="3:23">
+    <row r="450" ht="12.75" spans="3:23">
       <c r="C450" s="2"/>
       <c r="D450" s="2"/>
       <c r="E450" s="2"/>
@@ -12614,7 +12610,7 @@
       <c r="V450" s="2"/>
       <c r="W450" s="2"/>
     </row>
-    <row r="451" ht="13.2" spans="3:23">
+    <row r="451" ht="12.75" spans="3:23">
       <c r="C451" s="2"/>
       <c r="D451" s="2"/>
       <c r="E451" s="2"/>
@@ -12637,7 +12633,7 @@
       <c r="V451" s="2"/>
       <c r="W451" s="2"/>
     </row>
-    <row r="452" ht="13.2" spans="3:23">
+    <row r="452" ht="12.75" spans="3:23">
       <c r="C452" s="2"/>
       <c r="D452" s="2"/>
       <c r="E452" s="2"/>
@@ -12660,7 +12656,7 @@
       <c r="V452" s="2"/>
       <c r="W452" s="2"/>
     </row>
-    <row r="453" ht="13.2" spans="3:23">
+    <row r="453" ht="12.75" spans="3:23">
       <c r="C453" s="2"/>
       <c r="D453" s="2"/>
       <c r="E453" s="2"/>
@@ -12683,7 +12679,7 @@
       <c r="V453" s="2"/>
       <c r="W453" s="2"/>
     </row>
-    <row r="454" ht="13.2" spans="3:23">
+    <row r="454" ht="12.75" spans="3:23">
       <c r="C454" s="2"/>
       <c r="D454" s="2"/>
       <c r="E454" s="2"/>
@@ -12706,7 +12702,7 @@
       <c r="V454" s="2"/>
       <c r="W454" s="2"/>
     </row>
-    <row r="455" ht="13.2" spans="3:23">
+    <row r="455" ht="12.75" spans="3:23">
       <c r="C455" s="2"/>
       <c r="D455" s="2"/>
       <c r="E455" s="2"/>
@@ -12729,7 +12725,7 @@
       <c r="V455" s="2"/>
       <c r="W455" s="2"/>
     </row>
-    <row r="456" ht="13.2" spans="3:23">
+    <row r="456" ht="12.75" spans="3:23">
       <c r="C456" s="2"/>
       <c r="D456" s="2"/>
       <c r="E456" s="2"/>
@@ -12752,7 +12748,7 @@
       <c r="V456" s="2"/>
       <c r="W456" s="2"/>
     </row>
-    <row r="457" ht="13.2" spans="3:23">
+    <row r="457" ht="12.75" spans="3:23">
       <c r="C457" s="2"/>
       <c r="D457" s="2"/>
       <c r="E457" s="2"/>
@@ -12775,7 +12771,7 @@
       <c r="V457" s="2"/>
       <c r="W457" s="2"/>
     </row>
-    <row r="458" ht="13.2" spans="3:23">
+    <row r="458" ht="12.75" spans="3:23">
       <c r="C458" s="2"/>
       <c r="D458" s="2"/>
       <c r="E458" s="2"/>
@@ -12798,7 +12794,7 @@
       <c r="V458" s="2"/>
       <c r="W458" s="2"/>
     </row>
-    <row r="459" ht="13.2" spans="3:23">
+    <row r="459" ht="12.75" spans="3:23">
       <c r="C459" s="2"/>
       <c r="D459" s="2"/>
       <c r="E459" s="2"/>
@@ -12821,7 +12817,7 @@
       <c r="V459" s="2"/>
       <c r="W459" s="2"/>
     </row>
-    <row r="460" ht="13.2" spans="3:23">
+    <row r="460" ht="12.75" spans="3:23">
       <c r="C460" s="2"/>
       <c r="D460" s="2"/>
       <c r="E460" s="2"/>
@@ -12844,7 +12840,7 @@
       <c r="V460" s="2"/>
       <c r="W460" s="2"/>
     </row>
-    <row r="461" ht="13.2" spans="3:23">
+    <row r="461" ht="12.75" spans="3:23">
       <c r="C461" s="2"/>
       <c r="D461" s="2"/>
       <c r="E461" s="2"/>
@@ -12867,7 +12863,7 @@
       <c r="V461" s="2"/>
       <c r="W461" s="2"/>
     </row>
-    <row r="462" ht="13.2" spans="3:23">
+    <row r="462" ht="12.75" spans="3:23">
       <c r="C462" s="2"/>
       <c r="D462" s="2"/>
       <c r="E462" s="2"/>
@@ -12890,7 +12886,7 @@
       <c r="V462" s="2"/>
       <c r="W462" s="2"/>
     </row>
-    <row r="463" ht="13.2" spans="3:23">
+    <row r="463" ht="12.75" spans="3:23">
       <c r="C463" s="2"/>
       <c r="D463" s="2"/>
       <c r="E463" s="2"/>
@@ -12913,7 +12909,7 @@
       <c r="V463" s="2"/>
       <c r="W463" s="2"/>
     </row>
-    <row r="464" ht="13.2" spans="3:23">
+    <row r="464" ht="12.75" spans="3:23">
       <c r="C464" s="2"/>
       <c r="D464" s="2"/>
       <c r="E464" s="2"/>
@@ -12936,7 +12932,7 @@
       <c r="V464" s="2"/>
       <c r="W464" s="2"/>
     </row>
-    <row r="465" ht="13.2" spans="3:23">
+    <row r="465" ht="12.75" spans="3:23">
       <c r="C465" s="2"/>
       <c r="D465" s="2"/>
       <c r="E465" s="2"/>
@@ -12959,7 +12955,7 @@
       <c r="V465" s="2"/>
       <c r="W465" s="2"/>
     </row>
-    <row r="466" ht="13.2" spans="3:23">
+    <row r="466" ht="12.75" spans="3:23">
       <c r="C466" s="2"/>
       <c r="D466" s="2"/>
       <c r="E466" s="2"/>
@@ -12982,7 +12978,7 @@
       <c r="V466" s="2"/>
       <c r="W466" s="2"/>
     </row>
-    <row r="467" ht="13.2" spans="3:23">
+    <row r="467" ht="12.75" spans="3:23">
       <c r="C467" s="2"/>
       <c r="D467" s="2"/>
       <c r="E467" s="2"/>
@@ -13005,7 +13001,7 @@
       <c r="V467" s="2"/>
       <c r="W467" s="2"/>
     </row>
-    <row r="468" ht="13.2" spans="3:23">
+    <row r="468" ht="12.75" spans="3:23">
       <c r="C468" s="2"/>
       <c r="D468" s="2"/>
       <c r="E468" s="2"/>
@@ -13028,7 +13024,7 @@
       <c r="V468" s="2"/>
       <c r="W468" s="2"/>
     </row>
-    <row r="469" ht="13.2" spans="3:23">
+    <row r="469" ht="12.75" spans="3:23">
       <c r="C469" s="2"/>
       <c r="D469" s="2"/>
       <c r="E469" s="2"/>
@@ -13051,7 +13047,7 @@
       <c r="V469" s="2"/>
       <c r="W469" s="2"/>
     </row>
-    <row r="470" ht="13.2" spans="3:23">
+    <row r="470" ht="12.75" spans="3:23">
       <c r="C470" s="2"/>
       <c r="D470" s="2"/>
       <c r="E470" s="2"/>
@@ -13074,7 +13070,7 @@
       <c r="V470" s="2"/>
       <c r="W470" s="2"/>
     </row>
-    <row r="471" ht="13.2" spans="3:23">
+    <row r="471" ht="12.75" spans="3:23">
       <c r="C471" s="2"/>
       <c r="D471" s="2"/>
       <c r="E471" s="2"/>
@@ -13097,7 +13093,7 @@
       <c r="V471" s="2"/>
       <c r="W471" s="2"/>
     </row>
-    <row r="472" ht="13.2" spans="3:23">
+    <row r="472" ht="12.75" spans="3:23">
       <c r="C472" s="2"/>
       <c r="D472" s="2"/>
       <c r="E472" s="2"/>
@@ -13120,7 +13116,7 @@
       <c r="V472" s="2"/>
       <c r="W472" s="2"/>
     </row>
-    <row r="473" ht="13.2" spans="3:23">
+    <row r="473" ht="12.75" spans="3:23">
       <c r="C473" s="2"/>
       <c r="D473" s="2"/>
       <c r="E473" s="2"/>
@@ -13143,7 +13139,7 @@
       <c r="V473" s="2"/>
       <c r="W473" s="2"/>
     </row>
-    <row r="474" ht="13.2" spans="3:23">
+    <row r="474" ht="12.75" spans="3:23">
       <c r="C474" s="2"/>
       <c r="D474" s="2"/>
       <c r="E474" s="2"/>
@@ -13166,7 +13162,7 @@
       <c r="V474" s="2"/>
       <c r="W474" s="2"/>
     </row>
-    <row r="475" ht="13.2" spans="3:23">
+    <row r="475" ht="12.75" spans="3:23">
       <c r="C475" s="2"/>
       <c r="D475" s="2"/>
       <c r="E475" s="2"/>
@@ -13189,7 +13185,7 @@
       <c r="V475" s="2"/>
       <c r="W475" s="2"/>
     </row>
-    <row r="476" ht="13.2" spans="3:23">
+    <row r="476" ht="12.75" spans="3:23">
       <c r="C476" s="2"/>
       <c r="D476" s="2"/>
       <c r="E476" s="2"/>
@@ -13212,7 +13208,7 @@
       <c r="V476" s="2"/>
       <c r="W476" s="2"/>
     </row>
-    <row r="477" ht="13.2" spans="3:23">
+    <row r="477" ht="12.75" spans="3:23">
       <c r="C477" s="2"/>
       <c r="D477" s="2"/>
       <c r="E477" s="2"/>
@@ -13235,7 +13231,7 @@
       <c r="V477" s="2"/>
       <c r="W477" s="2"/>
     </row>
-    <row r="478" ht="13.2" spans="3:23">
+    <row r="478" ht="12.75" spans="3:23">
       <c r="C478" s="2"/>
       <c r="D478" s="2"/>
       <c r="E478" s="2"/>
@@ -13258,7 +13254,7 @@
       <c r="V478" s="2"/>
       <c r="W478" s="2"/>
     </row>
-    <row r="479" ht="13.2" spans="3:23">
+    <row r="479" ht="12.75" spans="3:23">
       <c r="C479" s="2"/>
       <c r="D479" s="2"/>
       <c r="E479" s="2"/>
@@ -13281,7 +13277,7 @@
       <c r="V479" s="2"/>
       <c r="W479" s="2"/>
     </row>
-    <row r="480" ht="13.2" spans="3:23">
+    <row r="480" ht="12.75" spans="3:23">
       <c r="C480" s="2"/>
       <c r="D480" s="2"/>
       <c r="E480" s="2"/>
@@ -13304,7 +13300,7 @@
       <c r="V480" s="2"/>
       <c r="W480" s="2"/>
     </row>
-    <row r="481" ht="13.2" spans="3:23">
+    <row r="481" ht="12.75" spans="3:23">
       <c r="C481" s="2"/>
       <c r="D481" s="2"/>
       <c r="E481" s="2"/>
@@ -13327,7 +13323,7 @@
       <c r="V481" s="2"/>
       <c r="W481" s="2"/>
     </row>
-    <row r="482" ht="13.2" spans="3:23">
+    <row r="482" ht="12.75" spans="3:23">
       <c r="C482" s="2"/>
       <c r="D482" s="2"/>
       <c r="E482" s="2"/>
@@ -13350,7 +13346,7 @@
       <c r="V482" s="2"/>
       <c r="W482" s="2"/>
     </row>
-    <row r="483" ht="13.2" spans="3:23">
+    <row r="483" ht="12.75" spans="3:23">
       <c r="C483" s="2"/>
       <c r="D483" s="2"/>
       <c r="E483" s="2"/>
@@ -13373,7 +13369,7 @@
       <c r="V483" s="2"/>
       <c r="W483" s="2"/>
     </row>
-    <row r="484" ht="13.2" spans="3:23">
+    <row r="484" ht="12.75" spans="3:23">
       <c r="C484" s="2"/>
       <c r="D484" s="2"/>
       <c r="E484" s="2"/>
@@ -13396,7 +13392,7 @@
       <c r="V484" s="2"/>
       <c r="W484" s="2"/>
     </row>
-    <row r="485" ht="13.2" spans="3:23">
+    <row r="485" ht="12.75" spans="3:23">
       <c r="C485" s="2"/>
       <c r="D485" s="2"/>
       <c r="E485" s="2"/>
@@ -13419,7 +13415,7 @@
       <c r="V485" s="2"/>
       <c r="W485" s="2"/>
     </row>
-    <row r="486" ht="13.2" spans="3:23">
+    <row r="486" ht="12.75" spans="3:23">
       <c r="C486" s="2"/>
       <c r="D486" s="2"/>
       <c r="E486" s="2"/>
@@ -13442,7 +13438,7 @@
       <c r="V486" s="2"/>
       <c r="W486" s="2"/>
     </row>
-    <row r="487" ht="13.2" spans="3:23">
+    <row r="487" ht="12.75" spans="3:23">
       <c r="C487" s="2"/>
       <c r="D487" s="2"/>
       <c r="E487" s="2"/>
@@ -13465,7 +13461,7 @@
       <c r="V487" s="2"/>
       <c r="W487" s="2"/>
     </row>
-    <row r="488" ht="13.2" spans="3:23">
+    <row r="488" ht="12.75" spans="3:23">
       <c r="C488" s="2"/>
       <c r="D488" s="2"/>
       <c r="E488" s="2"/>
@@ -13488,7 +13484,7 @@
       <c r="V488" s="2"/>
       <c r="W488" s="2"/>
     </row>
-    <row r="489" ht="13.2" spans="3:23">
+    <row r="489" ht="12.75" spans="3:23">
       <c r="C489" s="2"/>
       <c r="D489" s="2"/>
       <c r="E489" s="2"/>
@@ -13511,7 +13507,7 @@
       <c r="V489" s="2"/>
       <c r="W489" s="2"/>
     </row>
-    <row r="490" ht="13.2" spans="3:23">
+    <row r="490" ht="12.75" spans="3:23">
       <c r="C490" s="2"/>
       <c r="D490" s="2"/>
       <c r="E490" s="2"/>
@@ -13534,7 +13530,7 @@
       <c r="V490" s="2"/>
       <c r="W490" s="2"/>
     </row>
-    <row r="491" ht="13.2" spans="3:23">
+    <row r="491" ht="12.75" spans="3:23">
       <c r="C491" s="2"/>
       <c r="D491" s="2"/>
       <c r="E491" s="2"/>
@@ -13557,7 +13553,7 @@
       <c r="V491" s="2"/>
       <c r="W491" s="2"/>
     </row>
-    <row r="492" ht="13.2" spans="3:23">
+    <row r="492" ht="12.75" spans="3:23">
       <c r="C492" s="2"/>
       <c r="D492" s="2"/>
       <c r="E492" s="2"/>
@@ -13580,7 +13576,7 @@
       <c r="V492" s="2"/>
       <c r="W492" s="2"/>
     </row>
-    <row r="493" ht="13.2" spans="3:23">
+    <row r="493" ht="12.75" spans="3:23">
       <c r="C493" s="2"/>
       <c r="D493" s="2"/>
       <c r="E493" s="2"/>
@@ -13603,7 +13599,7 @@
       <c r="V493" s="2"/>
       <c r="W493" s="2"/>
     </row>
-    <row r="494" ht="13.2" spans="3:23">
+    <row r="494" ht="12.75" spans="3:23">
       <c r="C494" s="2"/>
       <c r="D494" s="2"/>
       <c r="E494" s="2"/>
@@ -13626,7 +13622,7 @@
       <c r="V494" s="2"/>
       <c r="W494" s="2"/>
     </row>
-    <row r="495" ht="13.2" spans="3:23">
+    <row r="495" ht="12.75" spans="3:23">
       <c r="C495" s="2"/>
       <c r="D495" s="2"/>
       <c r="E495" s="2"/>
@@ -13649,7 +13645,7 @@
       <c r="V495" s="2"/>
       <c r="W495" s="2"/>
     </row>
-    <row r="496" ht="13.2" spans="3:23">
+    <row r="496" ht="12.75" spans="3:23">
       <c r="C496" s="2"/>
       <c r="D496" s="2"/>
       <c r="E496" s="2"/>
@@ -13672,7 +13668,7 @@
       <c r="V496" s="2"/>
       <c r="W496" s="2"/>
     </row>
-    <row r="497" ht="13.2" spans="3:23">
+    <row r="497" ht="12.75" spans="3:23">
       <c r="C497" s="2"/>
       <c r="D497" s="2"/>
       <c r="E497" s="2"/>
@@ -13695,7 +13691,7 @@
       <c r="V497" s="2"/>
       <c r="W497" s="2"/>
     </row>
-    <row r="498" ht="13.2" spans="3:23">
+    <row r="498" ht="12.75" spans="3:23">
       <c r="C498" s="2"/>
       <c r="D498" s="2"/>
       <c r="E498" s="2"/>
@@ -13718,7 +13714,7 @@
       <c r="V498" s="2"/>
       <c r="W498" s="2"/>
     </row>
-    <row r="499" ht="13.2" spans="3:23">
+    <row r="499" ht="12.75" spans="3:23">
       <c r="C499" s="2"/>
       <c r="D499" s="2"/>
       <c r="E499" s="2"/>
@@ -13741,7 +13737,7 @@
       <c r="V499" s="2"/>
       <c r="W499" s="2"/>
     </row>
-    <row r="500" ht="13.2" spans="3:23">
+    <row r="500" ht="12.75" spans="3:23">
       <c r="C500" s="2"/>
       <c r="D500" s="2"/>
       <c r="E500" s="2"/>
@@ -13764,7 +13760,7 @@
       <c r="V500" s="2"/>
       <c r="W500" s="2"/>
     </row>
-    <row r="501" ht="13.2" spans="3:23">
+    <row r="501" ht="12.75" spans="3:23">
       <c r="C501" s="2"/>
       <c r="D501" s="2"/>
       <c r="E501" s="2"/>
@@ -13787,7 +13783,7 @@
       <c r="V501" s="2"/>
       <c r="W501" s="2"/>
     </row>
-    <row r="502" ht="13.2" spans="3:23">
+    <row r="502" ht="12.75" spans="3:23">
       <c r="C502" s="2"/>
       <c r="D502" s="2"/>
       <c r="E502" s="2"/>
@@ -13810,7 +13806,7 @@
       <c r="V502" s="2"/>
       <c r="W502" s="2"/>
     </row>
-    <row r="503" ht="13.2" spans="3:23">
+    <row r="503" ht="12.75" spans="3:23">
       <c r="C503" s="2"/>
       <c r="D503" s="2"/>
       <c r="E503" s="2"/>
@@ -13833,7 +13829,7 @@
       <c r="V503" s="2"/>
       <c r="W503" s="2"/>
     </row>
-    <row r="504" ht="13.2" spans="3:23">
+    <row r="504" ht="12.75" spans="3:23">
       <c r="C504" s="2"/>
       <c r="D504" s="2"/>
       <c r="E504" s="2"/>
@@ -13856,7 +13852,7 @@
       <c r="V504" s="2"/>
       <c r="W504" s="2"/>
     </row>
-    <row r="505" ht="13.2" spans="3:23">
+    <row r="505" ht="12.75" spans="3:23">
       <c r="C505" s="2"/>
       <c r="D505" s="2"/>
       <c r="E505" s="2"/>
@@ -13879,7 +13875,7 @@
       <c r="V505" s="2"/>
       <c r="W505" s="2"/>
     </row>
-    <row r="506" ht="13.2" spans="3:23">
+    <row r="506" ht="12.75" spans="3:23">
       <c r="C506" s="2"/>
       <c r="D506" s="2"/>
       <c r="E506" s="2"/>
@@ -13902,7 +13898,7 @@
       <c r="V506" s="2"/>
       <c r="W506" s="2"/>
     </row>
-    <row r="507" ht="13.2" spans="3:23">
+    <row r="507" ht="12.75" spans="3:23">
       <c r="C507" s="2"/>
       <c r="D507" s="2"/>
       <c r="E507" s="2"/>
@@ -13925,7 +13921,7 @@
       <c r="V507" s="2"/>
       <c r="W507" s="2"/>
     </row>
-    <row r="508" ht="13.2" spans="3:23">
+    <row r="508" ht="12.75" spans="3:23">
       <c r="C508" s="2"/>
       <c r="D508" s="2"/>
       <c r="E508" s="2"/>
@@ -13948,7 +13944,7 @@
       <c r="V508" s="2"/>
       <c r="W508" s="2"/>
     </row>
-    <row r="509" ht="13.2" spans="3:23">
+    <row r="509" ht="12.75" spans="3:23">
       <c r="C509" s="2"/>
       <c r="D509" s="2"/>
       <c r="E509" s="2"/>
@@ -13971,7 +13967,7 @@
       <c r="V509" s="2"/>
       <c r="W509" s="2"/>
     </row>
-    <row r="510" ht="13.2" spans="3:23">
+    <row r="510" ht="12.75" spans="3:23">
       <c r="C510" s="2"/>
       <c r="D510" s="2"/>
       <c r="E510" s="2"/>
@@ -13994,7 +13990,7 @@
       <c r="V510" s="2"/>
       <c r="W510" s="2"/>
     </row>
-    <row r="511" ht="13.2" spans="3:23">
+    <row r="511" ht="12.75" spans="3:23">
       <c r="C511" s="2"/>
       <c r="D511" s="2"/>
       <c r="E511" s="2"/>
@@ -14017,7 +14013,7 @@
       <c r="V511" s="2"/>
       <c r="W511" s="2"/>
     </row>
-    <row r="512" ht="13.2" spans="3:23">
+    <row r="512" ht="12.75" spans="3:23">
       <c r="C512" s="2"/>
       <c r="D512" s="2"/>
       <c r="E512" s="2"/>
@@ -14040,7 +14036,7 @@
       <c r="V512" s="2"/>
       <c r="W512" s="2"/>
     </row>
-    <row r="513" ht="13.2" spans="3:23">
+    <row r="513" ht="12.75" spans="3:23">
       <c r="C513" s="2"/>
       <c r="D513" s="2"/>
       <c r="E513" s="2"/>
@@ -14063,7 +14059,7 @@
       <c r="V513" s="2"/>
       <c r="W513" s="2"/>
     </row>
-    <row r="514" ht="13.2" spans="3:23">
+    <row r="514" ht="12.75" spans="3:23">
       <c r="C514" s="2"/>
       <c r="D514" s="2"/>
       <c r="E514" s="2"/>
@@ -14086,7 +14082,7 @@
       <c r="V514" s="2"/>
       <c r="W514" s="2"/>
     </row>
-    <row r="515" ht="13.2" spans="3:23">
+    <row r="515" ht="12.75" spans="3:23">
       <c r="C515" s="2"/>
       <c r="D515" s="2"/>
       <c r="E515" s="2"/>
@@ -14109,7 +14105,7 @@
       <c r="V515" s="2"/>
       <c r="W515" s="2"/>
     </row>
-    <row r="516" ht="13.2" spans="3:23">
+    <row r="516" ht="12.75" spans="3:23">
       <c r="C516" s="2"/>
       <c r="D516" s="2"/>
       <c r="E516" s="2"/>
@@ -14132,7 +14128,7 @@
       <c r="V516" s="2"/>
       <c r="W516" s="2"/>
     </row>
-    <row r="517" ht="13.2" spans="3:23">
+    <row r="517" ht="12.75" spans="3:23">
       <c r="C517" s="2"/>
       <c r="D517" s="2"/>
       <c r="E517" s="2"/>
@@ -14155,7 +14151,7 @@
       <c r="V517" s="2"/>
       <c r="W517" s="2"/>
     </row>
-    <row r="518" ht="13.2" spans="3:23">
+    <row r="518" ht="12.75" spans="3:23">
       <c r="C518" s="2"/>
       <c r="D518" s="2"/>
       <c r="E518" s="2"/>
@@ -14178,7 +14174,7 @@
       <c r="V518" s="2"/>
       <c r="W518" s="2"/>
     </row>
-    <row r="519" ht="13.2" spans="3:23">
+    <row r="519" ht="12.75" spans="3:23">
       <c r="C519" s="2"/>
       <c r="D519" s="2"/>
       <c r="E519" s="2"/>
@@ -14201,7 +14197,7 @@
       <c r="V519" s="2"/>
       <c r="W519" s="2"/>
     </row>
-    <row r="520" ht="13.2" spans="3:23">
+    <row r="520" ht="12.75" spans="3:23">
       <c r="C520" s="2"/>
       <c r="D520" s="2"/>
       <c r="E520" s="2"/>
@@ -14224,7 +14220,7 @@
       <c r="V520" s="2"/>
       <c r="W520" s="2"/>
     </row>
-    <row r="521" ht="13.2" spans="3:23">
+    <row r="521" ht="12.75" spans="3:23">
       <c r="C521" s="2"/>
       <c r="D521" s="2"/>
       <c r="E521" s="2"/>
@@ -14247,7 +14243,7 @@
       <c r="V521" s="2"/>
       <c r="W521" s="2"/>
     </row>
-    <row r="522" ht="13.2" spans="3:23">
+    <row r="522" ht="12.75" spans="3:23">
       <c r="C522" s="2"/>
       <c r="D522" s="2"/>
       <c r="E522" s="2"/>
@@ -14270,7 +14266,7 @@
       <c r="V522" s="2"/>
       <c r="W522" s="2"/>
     </row>
-    <row r="523" ht="13.2" spans="3:23">
+    <row r="523" ht="12.75" spans="3:23">
       <c r="C523" s="2"/>
       <c r="D523" s="2"/>
       <c r="E523" s="2"/>
@@ -14293,7 +14289,7 @@
       <c r="V523" s="2"/>
       <c r="W523" s="2"/>
     </row>
-    <row r="524" ht="13.2" spans="3:23">
+    <row r="524" ht="12.75" spans="3:23">
       <c r="C524" s="2"/>
       <c r="D524" s="2"/>
       <c r="E524" s="2"/>
@@ -14316,7 +14312,7 @@
       <c r="V524" s="2"/>
       <c r="W524" s="2"/>
     </row>
-    <row r="525" ht="13.2" spans="3:23">
+    <row r="525" ht="12.75" spans="3:23">
       <c r="C525" s="2"/>
       <c r="D525" s="2"/>
       <c r="E525" s="2"/>
@@ -14339,7 +14335,7 @@
       <c r="V525" s="2"/>
       <c r="W525" s="2"/>
     </row>
-    <row r="526" ht="13.2" spans="3:23">
+    <row r="526" ht="12.75" spans="3:23">
       <c r="C526" s="2"/>
       <c r="D526" s="2"/>
       <c r="E526" s="2"/>
@@ -14362,7 +14358,7 @@
       <c r="V526" s="2"/>
       <c r="W526" s="2"/>
     </row>
-    <row r="527" ht="13.2" spans="3:23">
+    <row r="527" ht="12.75" spans="3:23">
       <c r="C527" s="2"/>
       <c r="D527" s="2"/>
       <c r="E527" s="2"/>
@@ -14385,7 +14381,7 @@
       <c r="V527" s="2"/>
       <c r="W527" s="2"/>
     </row>
-    <row r="528" ht="13.2" spans="3:23">
+    <row r="528" ht="12.75" spans="3:23">
       <c r="C528" s="2"/>
       <c r="D528" s="2"/>
       <c r="E528" s="2"/>
@@ -14408,7 +14404,7 @@
       <c r="V528" s="2"/>
       <c r="W528" s="2"/>
     </row>
-    <row r="529" ht="13.2" spans="3:23">
+    <row r="529" ht="12.75" spans="3:23">
       <c r="C529" s="2"/>
       <c r="D529" s="2"/>
       <c r="E529" s="2"/>
@@ -14431,7 +14427,7 @@
       <c r="V529" s="2"/>
       <c r="W529" s="2"/>
     </row>
-    <row r="530" ht="13.2" spans="3:23">
+    <row r="530" ht="12.75" spans="3:23">
       <c r="C530" s="2"/>
       <c r="D530" s="2"/>
       <c r="E530" s="2"/>
@@ -14454,7 +14450,7 @@
       <c r="V530" s="2"/>
       <c r="W530" s="2"/>
     </row>
-    <row r="531" ht="13.2" spans="3:23">
+    <row r="531" ht="12.75" spans="3:23">
       <c r="C531" s="2"/>
       <c r="D531" s="2"/>
       <c r="E531" s="2"/>
@@ -14477,7 +14473,7 @@
       <c r="V531" s="2"/>
       <c r="W531" s="2"/>
     </row>
-    <row r="532" ht="13.2" spans="3:23">
+    <row r="532" ht="12.75" spans="3:23">
       <c r="C532" s="2"/>
       <c r="D532" s="2"/>
       <c r="E532" s="2"/>
@@ -14500,7 +14496,7 @@
       <c r="V532" s="2"/>
       <c r="W532" s="2"/>
     </row>
-    <row r="533" ht="13.2" spans="3:23">
+    <row r="533" ht="12.75" spans="3:23">
       <c r="C533" s="2"/>
       <c r="D533" s="2"/>
       <c r="E533" s="2"/>
@@ -14523,7 +14519,7 @@
       <c r="V533" s="2"/>
       <c r="W533" s="2"/>
     </row>
-    <row r="534" ht="13.2" spans="3:23">
+    <row r="534" ht="12.75" spans="3:23">
       <c r="C534" s="2"/>
       <c r="D534" s="2"/>
       <c r="E534" s="2"/>
@@ -14546,7 +14542,7 @@
       <c r="V534" s="2"/>
       <c r="W534" s="2"/>
     </row>
-    <row r="535" ht="13.2" spans="3:23">
+    <row r="535" ht="12.75" spans="3:23">
       <c r="C535" s="2"/>
       <c r="D535" s="2"/>
       <c r="E535" s="2"/>
@@ -14569,7 +14565,7 @@
       <c r="V535" s="2"/>
       <c r="W535" s="2"/>
     </row>
-    <row r="536" ht="13.2" spans="3:23">
+    <row r="536" ht="12.75" spans="3:23">
       <c r="C536" s="2"/>
       <c r="D536" s="2"/>
       <c r="E536" s="2"/>
@@ -14592,7 +14588,7 @@
       <c r="V536" s="2"/>
       <c r="W536" s="2"/>
     </row>
-    <row r="537" ht="13.2" spans="3:23">
+    <row r="537" ht="12.75" spans="3:23">
       <c r="C537" s="2"/>
       <c r="D537" s="2"/>
       <c r="E537" s="2"/>
@@ -14615,7 +14611,7 @@
       <c r="V537" s="2"/>
       <c r="W537" s="2"/>
     </row>
-    <row r="538" ht="13.2" spans="3:23">
+    <row r="538" ht="12.75" spans="3:23">
       <c r="C538" s="2"/>
       <c r="D538" s="2"/>
       <c r="E538" s="2"/>
@@ -14638,7 +14634,7 @@
       <c r="V538" s="2"/>
       <c r="W538" s="2"/>
     </row>
-    <row r="539" ht="13.2" spans="3:23">
+    <row r="539" ht="12.75" spans="3:23">
       <c r="C539" s="2"/>
       <c r="D539" s="2"/>
       <c r="E539" s="2"/>
@@ -14661,7 +14657,7 @@
       <c r="V539" s="2"/>
       <c r="W539" s="2"/>
     </row>
-    <row r="540" ht="13.2" spans="3:23">
+    <row r="540" ht="12.75" spans="3:23">
       <c r="C540" s="2"/>
       <c r="D540" s="2"/>
       <c r="E540" s="2"/>
@@ -14684,7 +14680,7 @@
       <c r="V540" s="2"/>
       <c r="W540" s="2"/>
     </row>
-    <row r="541" ht="13.2" spans="3:23">
+    <row r="541" ht="12.75" spans="3:23">
       <c r="C541" s="2"/>
       <c r="D541" s="2"/>
       <c r="E541" s="2"/>
@@ -14707,7 +14703,7 @@
       <c r="V541" s="2"/>
       <c r="W541" s="2"/>
     </row>
-    <row r="542" ht="13.2" spans="3:23">
+    <row r="542" ht="12.75" spans="3:23">
       <c r="C542" s="2"/>
       <c r="D542" s="2"/>
       <c r="E542" s="2"/>
@@ -14730,7 +14726,7 @@
       <c r="V542" s="2"/>
       <c r="W542" s="2"/>
     </row>
-    <row r="543" ht="13.2" spans="3:23">
+    <row r="543" ht="12.75" spans="3:23">
       <c r="C543" s="2"/>
       <c r="D543" s="2"/>
       <c r="E543" s="2"/>
@@ -14753,7 +14749,7 @@
       <c r="V543" s="2"/>
       <c r="W543" s="2"/>
     </row>
-    <row r="544" ht="13.2" spans="3:23">
+    <row r="544" ht="12.75" spans="3:23">
       <c r="C544" s="2"/>
       <c r="D544" s="2"/>
       <c r="E544" s="2"/>
@@ -14776,7 +14772,7 @@
       <c r="V544" s="2"/>
       <c r="W544" s="2"/>
     </row>
-    <row r="545" ht="13.2" spans="3:23">
+    <row r="545" ht="12.75" spans="3:23">
       <c r="C545" s="2"/>
       <c r="D545" s="2"/>
       <c r="E545" s="2"/>
@@ -14799,7 +14795,7 @@
       <c r="V545" s="2"/>
       <c r="W545" s="2"/>
     </row>
-    <row r="546" ht="13.2" spans="3:23">
+    <row r="546" ht="12.75" spans="3:23">
       <c r="C546" s="2"/>
       <c r="D546" s="2"/>
       <c r="E546" s="2"/>
@@ -14822,7 +14818,7 @@
       <c r="V546" s="2"/>
       <c r="W546" s="2"/>
     </row>
-    <row r="547" ht="13.2" spans="3:23">
+    <row r="547" ht="12.75" spans="3:23">
       <c r="C547" s="2"/>
       <c r="D547" s="2"/>
       <c r="E547" s="2"/>
@@ -14845,7 +14841,7 @@
       <c r="V547" s="2"/>
       <c r="W547" s="2"/>
     </row>
-    <row r="548" ht="13.2" spans="3:23">
+    <row r="548" ht="12.75" spans="3:23">
       <c r="C548" s="2"/>
       <c r="D548" s="2"/>
       <c r="E548" s="2"/>
@@ -14868,7 +14864,7 @@
       <c r="V548" s="2"/>
       <c r="W548" s="2"/>
     </row>
-    <row r="549" ht="13.2" spans="3:23">
+    <row r="549" ht="12.75" spans="3:23">
       <c r="C549" s="2"/>
       <c r="D549" s="2"/>
       <c r="E549" s="2"/>
@@ -14891,7 +14887,7 @@
       <c r="V549" s="2"/>
       <c r="W549" s="2"/>
     </row>
-    <row r="550" ht="13.2" spans="3:23">
+    <row r="550" ht="12.75" spans="3:23">
       <c r="C550" s="2"/>
       <c r="D550" s="2"/>
       <c r="E550" s="2"/>
@@ -14914,7 +14910,7 @@
       <c r="V550" s="2"/>
       <c r="W550" s="2"/>
     </row>
-    <row r="551" ht="13.2" spans="3:23">
+    <row r="551" ht="12.75" spans="3:23">
       <c r="C551" s="2"/>
       <c r="D551" s="2"/>
       <c r="E551" s="2"/>
@@ -14937,7 +14933,7 @@
       <c r="V551" s="2"/>
       <c r="W551" s="2"/>
     </row>
-    <row r="552" ht="13.2" spans="3:23">
+    <row r="552" ht="12.75" spans="3:23">
       <c r="C552" s="2"/>
       <c r="D552" s="2"/>
       <c r="E552" s="2"/>
@@ -14960,7 +14956,7 @@
       <c r="V552" s="2"/>
       <c r="W552" s="2"/>
     </row>
-    <row r="553" ht="13.2" spans="3:23">
+    <row r="553" ht="12.75" spans="3:23">
       <c r="C553" s="2"/>
       <c r="D553" s="2"/>
       <c r="E553" s="2"/>
@@ -14983,7 +14979,7 @@
       <c r="V553" s="2"/>
       <c r="W553" s="2"/>
     </row>
-    <row r="554" ht="13.2" spans="3:23">
+    <row r="554" ht="12.75" spans="3:23">
       <c r="C554" s="2"/>
       <c r="D554" s="2"/>
       <c r="E554" s="2"/>
@@ -15006,7 +15002,7 @@
       <c r="V554" s="2"/>
       <c r="W554" s="2"/>
     </row>
-    <row r="555" ht="13.2" spans="3:23">
+    <row r="555" ht="12.75" spans="3:23">
       <c r="C555" s="2"/>
       <c r="D555" s="2"/>
       <c r="E555" s="2"/>
@@ -15029,7 +15025,7 @@
       <c r="V555" s="2"/>
       <c r="W555" s="2"/>
     </row>
-    <row r="556" ht="13.2" spans="3:23">
+    <row r="556" ht="12.75" spans="3:23">
       <c r="C556" s="2"/>
       <c r="D556" s="2"/>
       <c r="E556" s="2"/>
@@ -15052,7 +15048,7 @@
       <c r="V556" s="2"/>
       <c r="W556" s="2"/>
     </row>
-    <row r="557" ht="13.2" spans="3:23">
+    <row r="557" ht="12.75" spans="3:23">
       <c r="C557" s="2"/>
       <c r="D557" s="2"/>
       <c r="E557" s="2"/>
@@ -15075,7 +15071,7 @@
       <c r="V557" s="2"/>
       <c r="W557" s="2"/>
     </row>
-    <row r="558" ht="13.2" spans="3:23">
+    <row r="558" ht="12.75" spans="3:23">
       <c r="C558" s="2"/>
       <c r="D558" s="2"/>
       <c r="E558" s="2"/>
@@ -15098,7 +15094,7 @@
       <c r="V558" s="2"/>
       <c r="W558" s="2"/>
     </row>
-    <row r="559" ht="13.2" spans="3:23">
+    <row r="559" ht="12.75" spans="3:23">
       <c r="C559" s="2"/>
       <c r="D559" s="2"/>
       <c r="E559" s="2"/>
@@ -15121,7 +15117,7 @@
       <c r="V559" s="2"/>
       <c r="W559" s="2"/>
     </row>
-    <row r="560" ht="13.2" spans="3:23">
+    <row r="560" ht="12.75" spans="3:23">
       <c r="C560" s="2"/>
       <c r="D560" s="2"/>
       <c r="E560" s="2"/>
@@ -15144,7 +15140,7 @@
       <c r="V560" s="2"/>
       <c r="W560" s="2"/>
     </row>
-    <row r="561" ht="13.2" spans="3:23">
+    <row r="561" ht="12.75" spans="3:23">
       <c r="C561" s="2"/>
       <c r="D561" s="2"/>
       <c r="E561" s="2"/>
@@ -15167,7 +15163,7 @@
       <c r="V561" s="2"/>
       <c r="W561" s="2"/>
     </row>
-    <row r="562" ht="13.2" spans="3:23">
+    <row r="562" ht="12.75" spans="3:23">
       <c r="C562" s="2"/>
       <c r="D562" s="2"/>
       <c r="E562" s="2"/>
@@ -15190,7 +15186,7 @@
       <c r="V562" s="2"/>
       <c r="W562" s="2"/>
     </row>
-    <row r="563" ht="13.2" spans="3:23">
+    <row r="563" ht="12.75" spans="3:23">
       <c r="C563" s="2"/>
       <c r="D563" s="2"/>
       <c r="E563" s="2"/>
@@ -15213,7 +15209,7 @@
       <c r="V563" s="2"/>
       <c r="W563" s="2"/>
     </row>
-    <row r="564" ht="13.2" spans="3:23">
+    <row r="564" ht="12.75" spans="3:23">
       <c r="C564" s="2"/>
       <c r="D564" s="2"/>
       <c r="E564" s="2"/>
@@ -15236,7 +15232,7 @@
       <c r="V564" s="2"/>
       <c r="W564" s="2"/>
     </row>
-    <row r="565" ht="13.2" spans="3:23">
+    <row r="565" ht="12.75" spans="3:23">
       <c r="C565" s="2"/>
       <c r="D565" s="2"/>
       <c r="E565" s="2"/>
@@ -15259,7 +15255,7 @@
       <c r="V565" s="2"/>
       <c r="W565" s="2"/>
     </row>
-    <row r="566" ht="13.2" spans="3:23">
+    <row r="566" ht="12.75" spans="3:23">
       <c r="C566" s="2"/>
       <c r="D566" s="2"/>
       <c r="E566" s="2"/>
@@ -15282,7 +15278,7 @@
       <c r="V566" s="2"/>
       <c r="W566" s="2"/>
     </row>
-    <row r="567" ht="13.2" spans="3:23">
+    <row r="567" ht="12.75" spans="3:23">
       <c r="C567" s="2"/>
       <c r="D567" s="2"/>
       <c r="E567" s="2"/>
@@ -15305,7 +15301,7 @@
       <c r="V567" s="2"/>
       <c r="W567" s="2"/>
     </row>
-    <row r="568" ht="13.2" spans="3:23">
+    <row r="568" ht="12.75" spans="3:23">
       <c r="C568" s="2"/>
       <c r="D568" s="2"/>
       <c r="E568" s="2"/>
@@ -15328,7 +15324,7 @@
       <c r="V568" s="2"/>
       <c r="W568" s="2"/>
     </row>
-    <row r="569" ht="13.2" spans="3:23">
+    <row r="569" ht="12.75" spans="3:23">
       <c r="C569" s="2"/>
       <c r="D569" s="2"/>
       <c r="E569" s="2"/>
@@ -15351,7 +15347,7 @@
       <c r="V569" s="2"/>
       <c r="W569" s="2"/>
     </row>
-    <row r="570" ht="13.2" spans="3:23">
+    <row r="570" ht="12.75" spans="3:23">
       <c r="C570" s="2"/>
       <c r="D570" s="2"/>
       <c r="E570" s="2"/>
@@ -15374,7 +15370,7 @@
       <c r="V570" s="2"/>
       <c r="W570" s="2"/>
     </row>
-    <row r="571" ht="13.2" spans="3:23">
+    <row r="571" ht="12.75" spans="3:23">
       <c r="C571" s="2"/>
       <c r="D571" s="2"/>
       <c r="E571" s="2"/>
@@ -15397,7 +15393,7 @@
       <c r="V571" s="2"/>
       <c r="W571" s="2"/>
     </row>
-    <row r="572" ht="13.2" spans="3:23">
+    <row r="572" ht="12.75" spans="3:23">
       <c r="C572" s="2"/>
       <c r="D572" s="2"/>
       <c r="E572" s="2"/>
@@ -15420,7 +15416,7 @@
       <c r="V572" s="2"/>
       <c r="W572" s="2"/>
     </row>
-    <row r="573" ht="13.2" spans="3:23">
+    <row r="573" ht="12.75" spans="3:23">
       <c r="C573" s="2"/>
       <c r="D573" s="2"/>
       <c r="E573" s="2"/>
@@ -15443,7 +15439,7 @@
       <c r="V573" s="2"/>
       <c r="W573" s="2"/>
     </row>
-    <row r="574" ht="13.2" spans="3:23">
+    <row r="574" ht="12.75" spans="3:23">
       <c r="C574" s="2"/>
       <c r="D574" s="2"/>
       <c r="E574" s="2"/>
@@ -15466,7 +15462,7 @@
       <c r="V574" s="2"/>
       <c r="W574" s="2"/>
     </row>
-    <row r="575" ht="13.2" spans="3:23">
+    <row r="575" ht="12.75" spans="3:23">
       <c r="C575" s="2"/>
       <c r="D575" s="2"/>
       <c r="E575" s="2"/>
@@ -15489,7 +15485,7 @@
       <c r="V575" s="2"/>
       <c r="W575" s="2"/>
     </row>
-    <row r="576" ht="13.2" spans="3:23">
+    <row r="576" ht="12.75" spans="3:23">
       <c r="C576" s="2"/>
       <c r="D576" s="2"/>
       <c r="E576" s="2"/>
@@ -15512,7 +15508,7 @@
       <c r="V576" s="2"/>
       <c r="W576" s="2"/>
     </row>
-    <row r="577" ht="13.2" spans="3:23">
+    <row r="577" ht="12.75" spans="3:23">
       <c r="C577" s="2"/>
       <c r="D577" s="2"/>
       <c r="E577" s="2"/>
@@ -15535,7 +15531,7 @@
       <c r="V577" s="2"/>
       <c r="W577" s="2"/>
     </row>
-    <row r="578" ht="13.2" spans="3:23">
+    <row r="578" ht="12.75" spans="3:23">
       <c r="C578" s="2"/>
       <c r="D578" s="2"/>
       <c r="E578" s="2"/>
@@ -15558,7 +15554,7 @@
       <c r="V578" s="2"/>
       <c r="W578" s="2"/>
     </row>
-    <row r="579" ht="13.2" spans="3:23">
+    <row r="579" ht="12.75" spans="3:23">
       <c r="C579" s="2"/>
       <c r="D579" s="2"/>
       <c r="E579" s="2"/>
@@ -15581,7 +15577,7 @@
       <c r="V579" s="2"/>
       <c r="W579" s="2"/>
     </row>
-    <row r="580" ht="13.2" spans="3:23">
+    <row r="580" ht="12.75" spans="3:23">
       <c r="C580" s="2"/>
       <c r="D580" s="2"/>
       <c r="E580" s="2"/>
@@ -15604,7 +15600,7 @@
       <c r="V580" s="2"/>
       <c r="W580" s="2"/>
     </row>
-    <row r="581" ht="13.2" spans="3:23">
+    <row r="581" ht="12.75" spans="3:23">
       <c r="C581" s="2"/>
       <c r="D581" s="2"/>
       <c r="E581" s="2"/>
@@ -15627,7 +15623,7 @@
       <c r="V581" s="2"/>
       <c r="W581" s="2"/>
     </row>
-    <row r="582" ht="13.2" spans="3:23">
+    <row r="582" ht="12.75" spans="3:23">
       <c r="C582" s="2"/>
       <c r="D582" s="2"/>
       <c r="E582" s="2"/>
@@ -15650,7 +15646,7 @@
       <c r="V582" s="2"/>
       <c r="W582" s="2"/>
     </row>
-    <row r="583" ht="13.2" spans="3:23">
+    <row r="583" ht="12.75" spans="3:23">
       <c r="C583" s="2"/>
       <c r="D583" s="2"/>
       <c r="E583" s="2"/>
@@ -15673,7 +15669,7 @@
       <c r="V583" s="2"/>
       <c r="W583" s="2"/>
     </row>
-    <row r="584" ht="13.2" spans="3:23">
+    <row r="584" ht="12.75" spans="3:23">
       <c r="C584" s="2"/>
       <c r="D584" s="2"/>
       <c r="E584" s="2"/>
@@ -15696,7 +15692,7 @@
       <c r="V584" s="2"/>
       <c r="W584" s="2"/>
     </row>
-    <row r="585" ht="13.2" spans="3:23">
+    <row r="585" ht="12.75" spans="3:23">
       <c r="C585" s="2"/>
       <c r="D585" s="2"/>
       <c r="E585" s="2"/>
@@ -15719,7 +15715,7 @@
       <c r="V585" s="2"/>
       <c r="W585" s="2"/>
     </row>
-    <row r="586" ht="13.2" spans="3:23">
+    <row r="586" ht="12.75" spans="3:23">
       <c r="C586" s="2"/>
       <c r="D586" s="2"/>
       <c r="E586" s="2"/>
@@ -15742,7 +15738,7 @@
       <c r="V586" s="2"/>
       <c r="W586" s="2"/>
     </row>
-    <row r="587" ht="13.2" spans="3:23">
+    <row r="587" ht="12.75" spans="3:23">
       <c r="C587" s="2"/>
       <c r="D587" s="2"/>
       <c r="E587" s="2"/>
@@ -15765,7 +15761,7 @@
       <c r="V587" s="2"/>
       <c r="W587" s="2"/>
     </row>
-    <row r="588" ht="13.2" spans="3:23">
+    <row r="588" ht="12.75" spans="3:23">
       <c r="C588" s="2"/>
       <c r="D588" s="2"/>
       <c r="E588" s="2"/>
@@ -15788,7 +15784,7 @@
       <c r="V588" s="2"/>
       <c r="W588" s="2"/>
     </row>
-    <row r="589" ht="13.2" spans="3:23">
+    <row r="589" ht="12.75" spans="3:23">
       <c r="C589" s="2"/>
       <c r="D589" s="2"/>
       <c r="E589" s="2"/>
@@ -15811,7 +15807,7 @@
       <c r="V589" s="2"/>
       <c r="W589" s="2"/>
     </row>
-    <row r="590" ht="13.2" spans="3:23">
+    <row r="590" ht="12.75" spans="3:23">
       <c r="C590" s="2"/>
       <c r="D590" s="2"/>
       <c r="E590" s="2"/>
@@ -15834,7 +15830,7 @@
       <c r="V590" s="2"/>
       <c r="W590" s="2"/>
     </row>
-    <row r="591" ht="13.2" spans="3:23">
+    <row r="591" ht="12.75" spans="3:23">
       <c r="C591" s="2"/>
       <c r="D591" s="2"/>
       <c r="E591" s="2"/>
@@ -15857,7 +15853,7 @@
       <c r="V591" s="2"/>
       <c r="W591" s="2"/>
     </row>
-    <row r="592" ht="13.2" spans="3:23">
+    <row r="592" ht="12.75" spans="3:23">
       <c r="C592" s="2"/>
       <c r="D592" s="2"/>
       <c r="E592" s="2"/>
@@ -15880,7 +15876,7 @@
       <c r="V592" s="2"/>
       <c r="W592" s="2"/>
     </row>
-    <row r="593" ht="13.2" spans="3:23">
+    <row r="593" ht="12.75" spans="3:23">
       <c r="C593" s="2"/>
       <c r="D593" s="2"/>
       <c r="E593" s="2"/>
@@ -15903,7 +15899,7 @@
       <c r="V593" s="2"/>
       <c r="W593" s="2"/>
     </row>
-    <row r="594" ht="13.2" spans="3:23">
+    <row r="594" ht="12.75" spans="3:23">
       <c r="C594" s="2"/>
       <c r="D594" s="2"/>
       <c r="E594" s="2"/>
@@ -15926,7 +15922,7 @@
       <c r="V594" s="2"/>
       <c r="W594" s="2"/>
     </row>
-    <row r="595" ht="13.2" spans="3:23">
+    <row r="595" ht="12.75" spans="3:23">
       <c r="C595" s="2"/>
       <c r="D595" s="2"/>
       <c r="E595" s="2"/>
@@ -15949,7 +15945,7 @@
       <c r="V595" s="2"/>
       <c r="W595" s="2"/>
     </row>
-    <row r="596" ht="13.2" spans="3:23">
+    <row r="596" ht="12.75" spans="3:23">
       <c r="C596" s="2"/>
       <c r="D596" s="2"/>
       <c r="E596" s="2"/>
@@ -15972,7 +15968,7 @@
       <c r="V596" s="2"/>
       <c r="W596" s="2"/>
     </row>
-    <row r="597" ht="13.2" spans="3:23">
+    <row r="597" ht="12.75" spans="3:23">
       <c r="C597" s="2"/>
       <c r="D597" s="2"/>
       <c r="E597" s="2"/>
@@ -15995,7 +15991,7 @@
       <c r="V597" s="2"/>
       <c r="W597" s="2"/>
     </row>
-    <row r="598" ht="13.2" spans="3:23">
+    <row r="598" ht="12.75" spans="3:23">
       <c r="C598" s="2"/>
       <c r="D598" s="2"/>
       <c r="E598" s="2"/>
@@ -16018,7 +16014,7 @@
       <c r="V598" s="2"/>
       <c r="W598" s="2"/>
     </row>
-    <row r="599" ht="13.2" spans="3:23">
+    <row r="599" ht="12.75" spans="3:23">
       <c r="C599" s="2"/>
       <c r="D599" s="2"/>
       <c r="E599" s="2"/>
@@ -16041,7 +16037,7 @@
       <c r="V599" s="2"/>
       <c r="W599" s="2"/>
     </row>
-    <row r="600" ht="13.2" spans="3:23">
+    <row r="600" ht="12.75" spans="3:23">
       <c r="C600" s="2"/>
       <c r="D600" s="2"/>
       <c r="E600" s="2"/>
@@ -16064,7 +16060,7 @@
       <c r="V600" s="2"/>
       <c r="W600" s="2"/>
     </row>
-    <row r="601" ht="13.2" spans="3:23">
+    <row r="601" ht="12.75" spans="3:23">
       <c r="C601" s="2"/>
       <c r="D601" s="2"/>
       <c r="E601" s="2"/>
@@ -16087,7 +16083,7 @@
       <c r="V601" s="2"/>
       <c r="W601" s="2"/>
     </row>
-    <row r="602" ht="13.2" spans="3:23">
+    <row r="602" ht="12.75" spans="3:23">
       <c r="C602" s="2"/>
       <c r="D602" s="2"/>
       <c r="E602" s="2"/>
@@ -16110,7 +16106,7 @@
       <c r="V602" s="2"/>
       <c r="W602" s="2"/>
     </row>
-    <row r="603" ht="13.2" spans="3:23">
+    <row r="603" ht="12.75" spans="3:23">
       <c r="C603" s="2"/>
       <c r="D603" s="2"/>
       <c r="E603" s="2"/>
@@ -16133,7 +16129,7 @@
       <c r="V603" s="2"/>
       <c r="W603" s="2"/>
     </row>
-    <row r="604" ht="13.2" spans="3:23">
+    <row r="604" ht="12.75" spans="3:23">
       <c r="C604" s="2"/>
       <c r="D604" s="2"/>
       <c r="E604" s="2"/>
@@ -16156,7 +16152,7 @@
       <c r="V604" s="2"/>
       <c r="W604" s="2"/>
     </row>
-    <row r="605" ht="13.2" spans="3:23">
+    <row r="605" ht="12.75" spans="3:23">
       <c r="C605" s="2"/>
       <c r="D605" s="2"/>
       <c r="E605" s="2"/>
@@ -16179,7 +16175,7 @@
       <c r="V605" s="2"/>
       <c r="W605" s="2"/>
     </row>
-    <row r="606" ht="13.2" spans="3:23">
+    <row r="606" ht="12.75" spans="3:23">
       <c r="C606" s="2"/>
       <c r="D606" s="2"/>
       <c r="E606" s="2"/>
@@ -16202,7 +16198,7 @@
       <c r="V606" s="2"/>
       <c r="W606" s="2"/>
     </row>
-    <row r="607" ht="13.2" spans="3:23">
+    <row r="607" ht="12.75" spans="3:23">
       <c r="C607" s="2"/>
       <c r="D607" s="2"/>
       <c r="E607" s="2"/>
@@ -16225,7 +16221,7 @@
       <c r="V607" s="2"/>
       <c r="W607" s="2"/>
     </row>
-    <row r="608" ht="13.2" spans="3:23">
+    <row r="608" ht="12.75" spans="3:23">
       <c r="C608" s="2"/>
       <c r="D608" s="2"/>
       <c r="E608" s="2"/>
@@ -16248,7 +16244,7 @@
       <c r="V608" s="2"/>
       <c r="W608" s="2"/>
     </row>
-    <row r="609" ht="13.2" spans="3:23">
+    <row r="609" ht="12.75" spans="3:23">
       <c r="C609" s="2"/>
       <c r="D609" s="2"/>
       <c r="E609" s="2"/>
@@ -16271,7 +16267,7 @@
       <c r="V609" s="2"/>
       <c r="W609" s="2"/>
     </row>
-    <row r="610" ht="13.2" spans="3:23">
+    <row r="610" ht="12.75" spans="3:23">
       <c r="C610" s="2"/>
       <c r="D610" s="2"/>
       <c r="E610" s="2"/>
@@ -16294,7 +16290,7 @@
       <c r="V610" s="2"/>
       <c r="W610" s="2"/>
     </row>
-    <row r="611" ht="13.2" spans="3:23">
+    <row r="611" ht="12.75" spans="3:23">
       <c r="C611" s="2"/>
       <c r="D611" s="2"/>
       <c r="E611" s="2"/>
@@ -16317,7 +16313,7 @@
       <c r="V611" s="2"/>
       <c r="W611" s="2"/>
     </row>
-    <row r="612" ht="13.2" spans="3:23">
+    <row r="612" ht="12.75" spans="3:23">
       <c r="C612" s="2"/>
       <c r="D612" s="2"/>
       <c r="E612" s="2"/>
@@ -16340,7 +16336,7 @@
       <c r="V612" s="2"/>
       <c r="W612" s="2"/>
     </row>
-    <row r="613" ht="13.2" spans="3:23">
+    <row r="613" ht="12.75" spans="3:23">
       <c r="C613" s="2"/>
       <c r="D613" s="2"/>
       <c r="E613" s="2"/>
@@ -16363,7 +16359,7 @@
       <c r="V613" s="2"/>
       <c r="W613" s="2"/>
     </row>
-    <row r="614" ht="13.2" spans="3:23">
+    <row r="614" ht="12.75" spans="3:23">
       <c r="C614" s="2"/>
       <c r="D614" s="2"/>
       <c r="E614" s="2"/>
@@ -16386,7 +16382,7 @@
       <c r="V614" s="2"/>
       <c r="W614" s="2"/>
     </row>
-    <row r="615" ht="13.2" spans="3:23">
+    <row r="615" ht="12.75" spans="3:23">
       <c r="C615" s="2"/>
       <c r="D615" s="2"/>
       <c r="E615" s="2"/>
@@ -16409,7 +16405,7 @@
       <c r="V615" s="2"/>
       <c r="W615" s="2"/>
     </row>
-    <row r="616" ht="13.2" spans="3:23">
+    <row r="616" ht="12.75" spans="3:23">
       <c r="C616" s="2"/>
       <c r="D616" s="2"/>
       <c r="E616" s="2"/>
@@ -16432,7 +16428,7 @@
       <c r="V616" s="2"/>
       <c r="W616" s="2"/>
     </row>
-    <row r="617" ht="13.2" spans="3:23">
+    <row r="617" ht="12.75" spans="3:23">
       <c r="C617" s="2"/>
       <c r="D617" s="2"/>
       <c r="E617" s="2"/>
@@ -16455,7 +16451,7 @@
       <c r="V617" s="2"/>
       <c r="W617" s="2"/>
     </row>
-    <row r="618" ht="13.2" spans="3:23">
+    <row r="618" ht="12.75" spans="3:23">
       <c r="C618" s="2"/>
       <c r="D618" s="2"/>
       <c r="E618" s="2"/>
@@ -16478,7 +16474,7 @@
       <c r="V618" s="2"/>
       <c r="W618" s="2"/>
     </row>
-    <row r="619" ht="13.2" spans="3:23">
+    <row r="619" ht="12.75" spans="3:23">
       <c r="C619" s="2"/>
       <c r="D619" s="2"/>
       <c r="E619" s="2"/>
@@ -16501,7 +16497,7 @@
       <c r="V619" s="2"/>
       <c r="W619" s="2"/>
     </row>
-    <row r="620" ht="13.2" spans="3:23">
+    <row r="620" ht="12.75" spans="3:23">
       <c r="C620" s="2"/>
       <c r="D620" s="2"/>
       <c r="E620" s="2"/>
@@ -16524,7 +16520,7 @@
       <c r="V620" s="2"/>
       <c r="W620" s="2"/>
     </row>
-    <row r="621" ht="13.2" spans="3:23">
+    <row r="621" ht="12.75" spans="3:23">
       <c r="C621" s="2"/>
       <c r="D621" s="2"/>
       <c r="E621" s="2"/>
@@ -16547,7 +16543,7 @@
       <c r="V621" s="2"/>
       <c r="W621" s="2"/>
     </row>
-    <row r="622" ht="13.2" spans="3:23">
+    <row r="622" ht="12.75" spans="3:23">
       <c r="C622" s="2"/>
       <c r="D622" s="2"/>
       <c r="E622" s="2"/>
@@ -16570,7 +16566,7 @@
       <c r="V622" s="2"/>
       <c r="W622" s="2"/>
     </row>
-    <row r="623" ht="13.2" spans="3:23">
+    <row r="623" ht="12.75" spans="3:23">
       <c r="C623" s="2"/>
       <c r="D623" s="2"/>
       <c r="E623" s="2"/>
@@ -16593,7 +16589,7 @@
       <c r="V623" s="2"/>
       <c r="W623" s="2"/>
     </row>
-    <row r="624" ht="13.2" spans="3:23">
+    <row r="624" ht="12.75" spans="3:23">
       <c r="C624" s="2"/>
       <c r="D624" s="2"/>
       <c r="E624" s="2"/>
@@ -16616,7 +16612,7 @@
       <c r="V624" s="2"/>
       <c r="W624" s="2"/>
     </row>
-    <row r="625" ht="13.2" spans="3:23">
+    <row r="625" ht="12.75" spans="3:23">
       <c r="C625" s="2"/>
       <c r="D625" s="2"/>
       <c r="E625" s="2"/>
@@ -16639,7 +16635,7 @@
       <c r="V625" s="2"/>
       <c r="W625" s="2"/>
     </row>
-    <row r="626" ht="13.2" spans="3:23">
+    <row r="626" ht="12.75" spans="3:23">
       <c r="C626" s="2"/>
       <c r="D626" s="2"/>
       <c r="E626" s="2"/>
@@ -16662,7 +16658,7 @@
       <c r="V626" s="2"/>
       <c r="W626" s="2"/>
     </row>
-    <row r="627" ht="13.2" spans="3:23">
+    <row r="627" ht="12.75" spans="3:23">
       <c r="C627" s="2"/>
       <c r="D627" s="2"/>
       <c r="E627" s="2"/>
@@ -16685,7 +16681,7 @@
       <c r="V627" s="2"/>
       <c r="W627" s="2"/>
     </row>
-    <row r="628" ht="13.2" spans="3:23">
+    <row r="628" ht="12.75" spans="3:23">
       <c r="C628" s="2"/>
       <c r="D628" s="2"/>
       <c r="E628" s="2"/>
@@ -16708,7 +16704,7 @@
       <c r="V628" s="2"/>
       <c r="W628" s="2"/>
     </row>
-    <row r="629" ht="13.2" spans="3:23">
+    <row r="629" ht="12.75" spans="3:23">
       <c r="C629" s="2"/>
       <c r="D629" s="2"/>
       <c r="E629" s="2"/>
@@ -16731,7 +16727,7 @@
       <c r="V629" s="2"/>
       <c r="W629" s="2"/>
     </row>
-    <row r="630" ht="13.2" spans="3:23">
+    <row r="630" ht="12.75" spans="3:23">
       <c r="C630" s="2"/>
       <c r="D630" s="2"/>
       <c r="E630" s="2"/>
@@ -16754,7 +16750,7 @@
       <c r="V630" s="2"/>
       <c r="W630" s="2"/>
     </row>
-    <row r="631" ht="13.2" spans="3:23">
+    <row r="631" ht="12.75" spans="3:23">
       <c r="C631" s="2"/>
       <c r="D631" s="2"/>
       <c r="E631" s="2"/>
@@ -16777,7 +16773,7 @@
       <c r="V631" s="2"/>
       <c r="W631" s="2"/>
     </row>
-    <row r="632" ht="13.2" spans="3:23">
+    <row r="632" ht="12.75" spans="3:23">
       <c r="C632" s="2"/>
       <c r="D632" s="2"/>
       <c r="E632" s="2"/>
@@ -16800,7 +16796,7 @@
       <c r="V632" s="2"/>
       <c r="W632" s="2"/>
     </row>
-    <row r="633" ht="13.2" spans="3:23">
+    <row r="633" ht="12.75" spans="3:23">
       <c r="C633" s="2"/>
       <c r="D633" s="2"/>
       <c r="E633" s="2"/>
@@ -16823,7 +16819,7 @@
       <c r="V633" s="2"/>
       <c r="W633" s="2"/>
     </row>
-    <row r="634" ht="13.2" spans="3:23">
+    <row r="634" ht="12.75" spans="3:23">
       <c r="C634" s="2"/>
       <c r="D634" s="2"/>
       <c r="E634" s="2"/>
@@ -16846,7 +16842,7 @@
       <c r="V634" s="2"/>
       <c r="W634" s="2"/>
     </row>
-    <row r="635" ht="13.2" spans="3:23">
+    <row r="635" ht="12.75" spans="3:23">
       <c r="C635" s="2"/>
       <c r="D635" s="2"/>
       <c r="E635" s="2"/>
@@ -16869,7 +16865,7 @@
       <c r="V635" s="2"/>
       <c r="W635" s="2"/>
     </row>
-    <row r="636" ht="13.2" spans="3:23">
+    <row r="636" ht="12.75" spans="3:23">
       <c r="C636" s="2"/>
       <c r="D636" s="2"/>
       <c r="E636" s="2"/>
@@ -16892,7 +16888,7 @@
       <c r="V636" s="2"/>
       <c r="W636" s="2"/>
     </row>
-    <row r="637" ht="13.2" spans="3:23">
+    <row r="637" ht="12.75" spans="3:23">
       <c r="C637" s="2"/>
       <c r="D637" s="2"/>
       <c r="E637" s="2"/>
@@ -16915,7 +16911,7 @@
       <c r="V637" s="2"/>
       <c r="W637" s="2"/>
     </row>
-    <row r="638" ht="13.2" spans="3:23">
+    <row r="638" ht="12.75" spans="3:23">
       <c r="C638" s="2"/>
       <c r="D638" s="2"/>
       <c r="E638" s="2"/>
@@ -16938,7 +16934,7 @@
       <c r="V638" s="2"/>
       <c r="W638" s="2"/>
     </row>
-    <row r="639" ht="13.2" spans="3:23">
+    <row r="639" ht="12.75" spans="3:23">
       <c r="C639" s="2"/>
       <c r="D639" s="2"/>
       <c r="E639" s="2"/>
@@ -16961,7 +16957,7 @@
       <c r="V639" s="2"/>
       <c r="W639" s="2"/>
     </row>
-    <row r="640" ht="13.2" spans="3:23">
+    <row r="640" ht="12.75" spans="3:23">
       <c r="C640" s="2"/>
       <c r="D640" s="2"/>
       <c r="E640" s="2"/>
@@ -16984,7 +16980,7 @@
       <c r="V640" s="2"/>
       <c r="W640" s="2"/>
     </row>
-    <row r="641" ht="13.2" spans="3:23">
+    <row r="641" ht="12.75" spans="3:23">
       <c r="C641" s="2"/>
       <c r="D641" s="2"/>
       <c r="E641" s="2"/>
@@ -17007,7 +17003,7 @@
       <c r="V641" s="2"/>
       <c r="W641" s="2"/>
     </row>
-    <row r="642" ht="13.2" spans="3:23">
+    <row r="642" ht="12.75" spans="3:23">
       <c r="C642" s="2"/>
       <c r="D642" s="2"/>
       <c r="E642" s="2"/>
@@ -17030,7 +17026,7 @@
       <c r="V642" s="2"/>
       <c r="W642" s="2"/>
     </row>
-    <row r="643" ht="13.2" spans="3:23">
+    <row r="643" ht="12.75" spans="3:23">
       <c r="C643" s="2"/>
       <c r="D643" s="2"/>
       <c r="E643" s="2"/>
@@ -17053,7 +17049,7 @@
       <c r="V643" s="2"/>
       <c r="W643" s="2"/>
     </row>
-    <row r="644" ht="13.2" spans="3:23">
+    <row r="644" ht="12.75" spans="3:23">
       <c r="C644" s="2"/>
       <c r="D644" s="2"/>
       <c r="E644" s="2"/>
@@ -17076,7 +17072,7 @@
       <c r="V644" s="2"/>
       <c r="W644" s="2"/>
     </row>
-    <row r="645" ht="13.2" spans="3:23">
+    <row r="645" ht="12.75" spans="3:23">
       <c r="C645" s="2"/>
       <c r="D645" s="2"/>
       <c r="E645" s="2"/>
@@ -17099,7 +17095,7 @@
       <c r="V645" s="2"/>
       <c r="W645" s="2"/>
     </row>
-    <row r="646" ht="13.2" spans="3:23">
+    <row r="646" ht="12.75" spans="3:23">
       <c r="C646" s="2"/>
       <c r="D646" s="2"/>
       <c r="E646" s="2"/>
@@ -17122,7 +17118,7 @@
       <c r="V646" s="2"/>
       <c r="W646" s="2"/>
     </row>
-    <row r="647" ht="13.2" spans="3:23">
+    <row r="647" ht="12.75" spans="3:23">
       <c r="C647" s="2"/>
       <c r="D647" s="2"/>
       <c r="E647" s="2"/>
@@ -17145,7 +17141,7 @@
       <c r="V647" s="2"/>
       <c r="W647" s="2"/>
     </row>
-    <row r="648" ht="13.2" spans="3:23">
+    <row r="648" ht="12.75" spans="3:23">
       <c r="C648" s="2"/>
       <c r="D648" s="2"/>
       <c r="E648" s="2"/>
@@ -17168,7 +17164,7 @@
       <c r="V648" s="2"/>
       <c r="W648" s="2"/>
     </row>
-    <row r="649" ht="13.2" spans="3:23">
+    <row r="649" ht="12.75" spans="3:23">
       <c r="C649" s="2"/>
       <c r="D649" s="2"/>
       <c r="E649" s="2"/>
@@ -17191,7 +17187,7 @@
       <c r="V649" s="2"/>
       <c r="W649" s="2"/>
     </row>
-    <row r="650" ht="13.2" spans="3:23">
+    <row r="650" ht="12.75" spans="3:23">
       <c r="C650" s="2"/>
       <c r="D650" s="2"/>
       <c r="E650" s="2"/>
@@ -17214,7 +17210,7 @@
       <c r="V650" s="2"/>
       <c r="W650" s="2"/>
     </row>
-    <row r="651" ht="13.2" spans="3:23">
+    <row r="651" ht="12.75" spans="3:23">
       <c r="C651" s="2"/>
       <c r="D651" s="2"/>
       <c r="E651" s="2"/>
@@ -17237,7 +17233,7 @@
       <c r="V651" s="2"/>
       <c r="W651" s="2"/>
     </row>
-    <row r="652" ht="13.2" spans="3:23">
+    <row r="652" ht="12.75" spans="3:23">
       <c r="C652" s="2"/>
       <c r="D652" s="2"/>
       <c r="E652" s="2"/>
@@ -17260,7 +17256,7 @@
       <c r="V652" s="2"/>
       <c r="W652" s="2"/>
     </row>
-    <row r="653" ht="13.2" spans="3:23">
+    <row r="653" ht="12.75" spans="3:23">
       <c r="C653" s="2"/>
       <c r="D653" s="2"/>
       <c r="E653" s="2"/>
@@ -17283,7 +17279,7 @@
       <c r="V653" s="2"/>
       <c r="W653" s="2"/>
     </row>
-    <row r="654" ht="13.2" spans="3:23">
+    <row r="654" ht="12.75" spans="3:23">
       <c r="C654" s="2"/>
       <c r="D654" s="2"/>
       <c r="E654" s="2"/>
@@ -17306,7 +17302,7 @@
       <c r="V654" s="2"/>
       <c r="W654" s="2"/>
     </row>
-    <row r="655" ht="13.2" spans="3:23">
+    <row r="655" ht="12.75" spans="3:23">
       <c r="C655" s="2"/>
       <c r="D655" s="2"/>
       <c r="E655" s="2"/>
@@ -17329,7 +17325,7 @@
       <c r="V655" s="2"/>
       <c r="W655" s="2"/>
     </row>
-    <row r="656" ht="13.2" spans="3:23">
+    <row r="656" ht="12.75" spans="3:23">
       <c r="C656" s="2"/>
       <c r="D656" s="2"/>
       <c r="E656" s="2"/>
@@ -17352,7 +17348,7 @@
       <c r="V656" s="2"/>
       <c r="W656" s="2"/>
     </row>
-    <row r="657" ht="13.2" spans="3:23">
+    <row r="657" ht="12.75" spans="3:23">
       <c r="C657" s="2"/>
       <c r="D657" s="2"/>
       <c r="E657" s="2"/>
@@ -17375,7 +17371,7 @@
       <c r="V657" s="2"/>
       <c r="W657" s="2"/>
     </row>
-    <row r="658" ht="13.2" spans="3:23">
+    <row r="658" ht="12.75" spans="3:23">
       <c r="C658" s="2"/>
       <c r="D658" s="2"/>
       <c r="E658" s="2"/>
@@ -17398,7 +17394,7 @@
       <c r="V658" s="2"/>
       <c r="W658" s="2"/>
     </row>
-    <row r="659" ht="13.2" spans="3:23">
+    <row r="659" ht="12.75" spans="3:23">
       <c r="C659" s="2"/>
       <c r="D659" s="2"/>
       <c r="E659" s="2"/>
@@ -17421,7 +17417,7 @@
       <c r="V659" s="2"/>
       <c r="W659" s="2"/>
     </row>
-    <row r="660" ht="13.2" spans="3:23">
+    <row r="660" ht="12.75" spans="3:23">
       <c r="C660" s="2"/>
       <c r="D660" s="2"/>
       <c r="E660" s="2"/>
@@ -17444,7 +17440,7 @@
       <c r="V660" s="2"/>
       <c r="W660" s="2"/>
     </row>
-    <row r="661" ht="13.2" spans="3:23">
+    <row r="661" ht="12.75" spans="3:23">
       <c r="C661" s="2"/>
       <c r="D661" s="2"/>
       <c r="E661" s="2"/>
@@ -17467,7 +17463,7 @@
       <c r="V661" s="2"/>
       <c r="W661" s="2"/>
     </row>
-    <row r="662" ht="13.2" spans="3:23">
+    <row r="662" ht="12.75" spans="3:23">
       <c r="C662" s="2"/>
       <c r="D662" s="2"/>
       <c r="E662" s="2"/>
@@ -17490,7 +17486,7 @@
       <c r="V662" s="2"/>
       <c r="W662" s="2"/>
     </row>
-    <row r="663" ht="13.2" spans="3:23">
+    <row r="663" ht="12.75" spans="3:23">
       <c r="C663" s="2"/>
       <c r="D663" s="2"/>
       <c r="E663" s="2"/>
@@ -17513,7 +17509,7 @@
       <c r="V663" s="2"/>
       <c r="W663" s="2"/>
     </row>
-    <row r="664" ht="13.2" spans="3:23">
+    <row r="664" ht="12.75" spans="3:23">
       <c r="C664" s="2"/>
       <c r="D664" s="2"/>
       <c r="E664" s="2"/>
@@ -17536,7 +17532,7 @@
       <c r="V664" s="2"/>
       <c r="W664" s="2"/>
     </row>
-    <row r="665" ht="13.2" spans="3:23">
+    <row r="665" ht="12.75" spans="3:23">
       <c r="C665" s="2"/>
       <c r="D665" s="2"/>
       <c r="E665" s="2"/>
@@ -17559,7 +17555,7 @@
       <c r="V665" s="2"/>
       <c r="W665" s="2"/>
     </row>
-    <row r="666" ht="13.2" spans="3:23">
+    <row r="666" ht="12.75" spans="3:23">
       <c r="C666" s="2"/>
       <c r="D666" s="2"/>
       <c r="E666" s="2"/>
@@ -17582,7 +17578,7 @@
       <c r="V666" s="2"/>
       <c r="W666" s="2"/>
     </row>
-    <row r="667" ht="13.2" spans="3:23">
+    <row r="667" ht="12.75" spans="3:23">
       <c r="C667" s="2"/>
       <c r="D667" s="2"/>
       <c r="E667" s="2"/>
@@ -17605,7 +17601,7 @@
       <c r="V667" s="2"/>
       <c r="W667" s="2"/>
     </row>
-    <row r="668" ht="13.2" spans="3:23">
+    <row r="668" ht="12.75" spans="3:23">
       <c r="C668" s="2"/>
       <c r="D668" s="2"/>
       <c r="E668" s="2"/>
@@ -17628,7 +17624,7 @@
       <c r="V668" s="2"/>
       <c r="W668" s="2"/>
     </row>
-    <row r="669" ht="13.2" spans="3:23">
+    <row r="669" ht="12.75" spans="3:23">
       <c r="C669" s="2"/>
       <c r="D669" s="2"/>
       <c r="E669" s="2"/>
@@ -17651,7 +17647,7 @@
       <c r="V669" s="2"/>
       <c r="W669" s="2"/>
     </row>
-    <row r="670" ht="13.2" spans="3:23">
+    <row r="670" ht="12.75" spans="3:23">
       <c r="C670" s="2"/>
       <c r="D670" s="2"/>
       <c r="E670" s="2"/>
@@ -17674,7 +17670,7 @@
       <c r="V670" s="2"/>
       <c r="W670" s="2"/>
     </row>
-    <row r="671" ht="13.2" spans="3:23">
+    <row r="671" ht="12.75" spans="3:23">
       <c r="C671" s="2"/>
       <c r="D671" s="2"/>
       <c r="E671" s="2"/>
@@ -17697,7 +17693,7 @@
       <c r="V671" s="2"/>
       <c r="W671" s="2"/>
     </row>
-    <row r="672" ht="13.2" spans="3:23">
+    <row r="672" ht="12.75" spans="3:23">
       <c r="C672" s="2"/>
       <c r="D672" s="2"/>
       <c r="E672" s="2"/>
@@ -17720,7 +17716,7 @@
       <c r="V672" s="2"/>
       <c r="W672" s="2"/>
     </row>
-    <row r="673" ht="13.2" spans="3:23">
+    <row r="673" ht="12.75" spans="3:23">
       <c r="C673" s="2"/>
       <c r="D673" s="2"/>
       <c r="E673" s="2"/>
@@ -17743,7 +17739,7 @@
       <c r="V673" s="2"/>
       <c r="W673" s="2"/>
     </row>
-    <row r="674" ht="13.2" spans="3:23">
+    <row r="674" ht="12.75" spans="3:23">
       <c r="C674" s="2"/>
       <c r="D674" s="2"/>
       <c r="E674" s="2"/>
@@ -17766,7 +17762,7 @@
       <c r="V674" s="2"/>
       <c r="W674" s="2"/>
     </row>
-    <row r="675" ht="13.2" spans="3:23">
+    <row r="675" ht="12.75" spans="3:23">
       <c r="C675" s="2"/>
       <c r="D675" s="2"/>
       <c r="E675" s="2"/>
@@ -17789,7 +17785,7 @@
       <c r="V675" s="2"/>
       <c r="W675" s="2"/>
     </row>
-    <row r="676" ht="13.2" spans="3:23">
+    <row r="676" ht="12.75" spans="3:23">
       <c r="C676" s="2"/>
       <c r="D676" s="2"/>
       <c r="E676" s="2"/>
@@ -17812,7 +17808,7 @@
       <c r="V676" s="2"/>
       <c r="W676" s="2"/>
     </row>
-    <row r="677" ht="13.2" spans="3:23">
+    <row r="677" ht="12.75" spans="3:23">
       <c r="C677" s="2"/>
       <c r="D677" s="2"/>
       <c r="E677" s="2"/>
@@ -17835,7 +17831,7 @@
       <c r="V677" s="2"/>
       <c r="W677" s="2"/>
     </row>
-    <row r="678" ht="13.2" spans="3:23">
+    <row r="678" ht="12.75" spans="3:23">
       <c r="C678" s="2"/>
       <c r="D678" s="2"/>
       <c r="E678" s="2"/>
@@ -17858,7 +17854,7 @@
       <c r="V678" s="2"/>
       <c r="W678" s="2"/>
     </row>
-    <row r="679" ht="13.2" spans="3:23">
+    <row r="679" ht="12.75" spans="3:23">
       <c r="C679" s="2"/>
       <c r="D679" s="2"/>
       <c r="E679" s="2"/>
@@ -17881,7 +17877,7 @@
       <c r="V679" s="2"/>
       <c r="W679" s="2"/>
     </row>
-    <row r="680" ht="13.2" spans="3:23">
+    <row r="680" ht="12.75" spans="3:23">
       <c r="C680" s="2"/>
       <c r="D680" s="2"/>
       <c r="E680" s="2"/>
@@ -17904,7 +17900,7 @@
       <c r="V680" s="2"/>
       <c r="W680" s="2"/>
     </row>
-    <row r="681" ht="13.2" spans="3:23">
+    <row r="681" ht="12.75" spans="3:23">
       <c r="C681" s="2"/>
       <c r="D681" s="2"/>
       <c r="E681" s="2"/>
@@ -17927,7 +17923,7 @@
       <c r="V681" s="2"/>
       <c r="W681" s="2"/>
     </row>
-    <row r="682" ht="13.2" spans="3:23">
+    <row r="682" ht="12.75" spans="3:23">
       <c r="C682" s="2"/>
       <c r="D682" s="2"/>
       <c r="E682" s="2"/>
@@ -17950,7 +17946,7 @@
       <c r="V682" s="2"/>
       <c r="W682" s="2"/>
     </row>
-    <row r="683" ht="13.2" spans="3:23">
+    <row r="683" ht="12.75" spans="3:23">
       <c r="C683" s="2"/>
       <c r="D683" s="2"/>
       <c r="E683" s="2"/>
@@ -17973,7 +17969,7 @@
       <c r="V683" s="2"/>
       <c r="W683" s="2"/>
     </row>
-    <row r="684" ht="13.2" spans="3:23">
+    <row r="684" ht="12.75" spans="3:23">
       <c r="C684" s="2"/>
       <c r="D684" s="2"/>
       <c r="E684" s="2"/>
@@ -17996,7 +17992,7 @@
       <c r="V684" s="2"/>
       <c r="W684" s="2"/>
     </row>
-    <row r="685" ht="13.2" spans="3:23">
+    <row r="685" ht="12.75" spans="3:23">
       <c r="C685" s="2"/>
       <c r="D685" s="2"/>
       <c r="E685" s="2"/>
@@ -18019,7 +18015,7 @@
       <c r="V685" s="2"/>
       <c r="W685" s="2"/>
     </row>
-    <row r="686" ht="13.2" spans="3:23">
+    <row r="686" ht="12.75" spans="3:23">
       <c r="C686" s="2"/>
       <c r="D686" s="2"/>
       <c r="E686" s="2"/>
@@ -18042,7 +18038,7 @@
       <c r="V686" s="2"/>
       <c r="W686" s="2"/>
     </row>
-    <row r="687" ht="13.2" spans="3:23">
+    <row r="687" ht="12.75" spans="3:23">
       <c r="C687" s="2"/>
       <c r="D687" s="2"/>
       <c r="E687" s="2"/>
@@ -18065,7 +18061,7 @@
       <c r="V687" s="2"/>
       <c r="W687" s="2"/>
     </row>
-    <row r="688" ht="13.2" spans="3:23">
+    <row r="688" ht="12.75" spans="3:23">
       <c r="C688" s="2"/>
       <c r="D688" s="2"/>
       <c r="E688" s="2"/>
@@ -18088,7 +18084,7 @@
       <c r="V688" s="2"/>
       <c r="W688" s="2"/>
     </row>
-    <row r="689" ht="13.2" spans="3:23">
+    <row r="689" ht="12.75" spans="3:23">
       <c r="C689" s="2"/>
       <c r="D689" s="2"/>
       <c r="E689" s="2"/>
@@ -18111,7 +18107,7 @@
       <c r="V689" s="2"/>
       <c r="W689" s="2"/>
     </row>
-    <row r="690" ht="13.2" spans="3:23">
+    <row r="690" ht="12.75" spans="3:23">
       <c r="C690" s="2"/>
       <c r="D690" s="2"/>
       <c r="E690" s="2"/>
@@ -18134,7 +18130,7 @@
       <c r="V690" s="2"/>
       <c r="W690" s="2"/>
     </row>
-    <row r="691" ht="13.2" spans="3:23">
+    <row r="691" ht="12.75" spans="3:23">
       <c r="C691" s="2"/>
       <c r="D691" s="2"/>
       <c r="E691" s="2"/>
@@ -18157,7 +18153,7 @@
       <c r="V691" s="2"/>
       <c r="W691" s="2"/>
     </row>
-    <row r="692" ht="13.2" spans="3:23">
+    <row r="692" ht="12.75" spans="3:23">
       <c r="C692" s="2"/>
       <c r="D692" s="2"/>
       <c r="E692" s="2"/>
@@ -18180,7 +18176,7 @@
       <c r="V692" s="2"/>
       <c r="W692" s="2"/>
     </row>
-    <row r="693" ht="13.2" spans="3:23">
+    <row r="693" ht="12.75" spans="3:23">
       <c r="C693" s="2"/>
       <c r="D693" s="2"/>
       <c r="E693" s="2"/>
@@ -18203,7 +18199,7 @@
       <c r="V693" s="2"/>
       <c r="W693" s="2"/>
     </row>
-    <row r="694" ht="13.2" spans="3:23">
+    <row r="694" ht="12.75" spans="3:23">
       <c r="C694" s="2"/>
       <c r="D694" s="2"/>
       <c r="E694" s="2"/>
@@ -18226,7 +18222,7 @@
       <c r="V694" s="2"/>
       <c r="W694" s="2"/>
     </row>
-    <row r="695" ht="13.2" spans="3:23">
+    <row r="695" ht="12.75" spans="3:23">
       <c r="C695" s="2"/>
       <c r="D695" s="2"/>
       <c r="E695" s="2"/>
@@ -18249,7 +18245,7 @@
       <c r="V695" s="2"/>
       <c r="W695" s="2"/>
     </row>
-    <row r="696" ht="13.2" spans="3:23">
+    <row r="696" ht="12.75" spans="3:23">
       <c r="C696" s="2"/>
       <c r="D696" s="2"/>
       <c r="E696" s="2"/>
@@ -18272,7 +18268,7 @@
       <c r="V696" s="2"/>
       <c r="W696" s="2"/>
     </row>
-    <row r="697" ht="13.2" spans="3:23">
+    <row r="697" ht="12.75" spans="3:23">
       <c r="C697" s="2"/>
       <c r="D697" s="2"/>
       <c r="E697" s="2"/>
@@ -18295,7 +18291,7 @@
       <c r="V697" s="2"/>
       <c r="W697" s="2"/>
     </row>
-    <row r="698" ht="13.2" spans="3:23">
+    <row r="698" ht="12.75" spans="3:23">
       <c r="C698" s="2"/>
       <c r="D698" s="2"/>
       <c r="E698" s="2"/>
@@ -18318,7 +18314,7 @@
       <c r="V698" s="2"/>
       <c r="W698" s="2"/>
     </row>
-    <row r="699" ht="13.2" spans="3:23">
+    <row r="699" ht="12.75" spans="3:23">
       <c r="C699" s="2"/>
       <c r="D699" s="2"/>
       <c r="E699" s="2"/>
@@ -18341,7 +18337,7 @@
       <c r="V699" s="2"/>
       <c r="W699" s="2"/>
     </row>
-    <row r="700" ht="13.2" spans="3:23">
+    <row r="700" ht="12.75" spans="3:23">
       <c r="C700" s="2"/>
       <c r="D700" s="2"/>
       <c r="E700" s="2"/>
@@ -18364,7 +18360,7 @@
       <c r="V700" s="2"/>
       <c r="W700" s="2"/>
     </row>
-    <row r="701" ht="13.2" spans="3:23">
+    <row r="701" ht="12.75" spans="3:23">
       <c r="C701" s="2"/>
       <c r="D701" s="2"/>
       <c r="E701" s="2"/>
@@ -18387,7 +18383,7 @@
       <c r="V701" s="2"/>
       <c r="W701" s="2"/>
     </row>
-    <row r="702" ht="13.2" spans="3:23">
+    <row r="702" ht="12.75" spans="3:23">
       <c r="C702" s="2"/>
       <c r="D702" s="2"/>
       <c r="E702" s="2"/>
@@ -18410,7 +18406,7 @@
       <c r="V702" s="2"/>
       <c r="W702" s="2"/>
     </row>
-    <row r="703" ht="13.2" spans="3:23">
+    <row r="703" ht="12.75" spans="3:23">
       <c r="C703" s="2"/>
       <c r="D703" s="2"/>
       <c r="E703" s="2"/>
@@ -18433,7 +18429,7 @@
       <c r="V703" s="2"/>
       <c r="W703" s="2"/>
     </row>
-    <row r="704" ht="13.2" spans="3:23">
+    <row r="704" ht="12.75" spans="3:23">
       <c r="C704" s="2"/>
       <c r="D704" s="2"/>
       <c r="E704" s="2"/>
@@ -18456,7 +18452,7 @@
       <c r="V704" s="2"/>
       <c r="W704" s="2"/>
     </row>
-    <row r="705" ht="13.2" spans="3:23">
+    <row r="705" ht="12.75" spans="3:23">
       <c r="C705" s="2"/>
       <c r="D705" s="2"/>
       <c r="E705" s="2"/>
@@ -18479,7 +18475,7 @@
       <c r="V705" s="2"/>
       <c r="W705" s="2"/>
     </row>
-    <row r="706" ht="13.2" spans="3:23">
+    <row r="706" ht="12.75" spans="3:23">
       <c r="C706" s="2"/>
       <c r="D706" s="2"/>
       <c r="E706" s="2"/>
@@ -18502,7 +18498,7 @@
       <c r="V706" s="2"/>
       <c r="W706" s="2"/>
     </row>
-    <row r="707" ht="13.2" spans="3:23">
+    <row r="707" ht="12.75" spans="3:23">
       <c r="C707" s="2"/>
       <c r="D707" s="2"/>
       <c r="E707" s="2"/>
@@ -18525,7 +18521,7 @@
       <c r="V707" s="2"/>
       <c r="W707" s="2"/>
     </row>
-    <row r="708" ht="13.2" spans="3:23">
+    <row r="708" ht="12.75" spans="3:23">
       <c r="C708" s="2"/>
       <c r="D708" s="2"/>
       <c r="E708" s="2"/>
@@ -18548,7 +18544,7 @@
       <c r="V708" s="2"/>
       <c r="W708" s="2"/>
     </row>
-    <row r="709" ht="13.2" spans="3:23">
+    <row r="709" ht="12.75" spans="3:23">
       <c r="C709" s="2"/>
       <c r="D709" s="2"/>
       <c r="E709" s="2"/>
@@ -18571,7 +18567,7 @@
       <c r="V709" s="2"/>
       <c r="W709" s="2"/>
     </row>
-    <row r="710" ht="13.2" spans="3:23">
+    <row r="710" ht="12.75" spans="3:23">
       <c r="C710" s="2"/>
       <c r="D710" s="2"/>
       <c r="E710" s="2"/>
@@ -18594,7 +18590,7 @@
       <c r="V710" s="2"/>
       <c r="W710" s="2"/>
     </row>
-    <row r="711" ht="13.2" spans="3:23">
+    <row r="711" ht="12.75" spans="3:23">
       <c r="C711" s="2"/>
       <c r="D711" s="2"/>
       <c r="E711" s="2"/>
@@ -18617,7 +18613,7 @@
       <c r="V711" s="2"/>
       <c r="W711" s="2"/>
     </row>
-    <row r="712" ht="13.2" spans="3:23">
+    <row r="712" ht="12.75" spans="3:23">
       <c r="C712" s="2"/>
       <c r="D712" s="2"/>
       <c r="E712" s="2"/>
@@ -18640,7 +18636,7 @@
       <c r="V712" s="2"/>
       <c r="W712" s="2"/>
     </row>
-    <row r="713" ht="13.2" spans="3:23">
+    <row r="713" ht="12.75" spans="3:23">
       <c r="C713" s="2"/>
       <c r="D713" s="2"/>
       <c r="E713" s="2"/>
@@ -18663,7 +18659,7 @@
       <c r="V713" s="2"/>
       <c r="W713" s="2"/>
     </row>
-    <row r="714" ht="13.2" spans="3:23">
+    <row r="714" ht="12.75" spans="3:23">
       <c r="C714" s="2"/>
       <c r="D714" s="2"/>
       <c r="E714" s="2"/>
@@ -18686,7 +18682,7 @@
       <c r="V714" s="2"/>
       <c r="W714" s="2"/>
     </row>
-    <row r="715" ht="13.2" spans="3:23">
+    <row r="715" ht="12.75" spans="3:23">
       <c r="C715" s="2"/>
       <c r="D715" s="2"/>
       <c r="E715" s="2"/>
@@ -18709,7 +18705,7 @@
       <c r="V715" s="2"/>
       <c r="W715" s="2"/>
     </row>
-    <row r="716" ht="13.2" spans="3:23">
+    <row r="716" ht="12.75" spans="3:23">
       <c r="C716" s="2"/>
       <c r="D716" s="2"/>
       <c r="E716" s="2"/>
@@ -18732,7 +18728,7 @@
       <c r="V716" s="2"/>
       <c r="W716" s="2"/>
     </row>
-    <row r="717" ht="13.2" spans="3:23">
+    <row r="717" ht="12.75" spans="3:23">
       <c r="C717" s="2"/>
       <c r="D717" s="2"/>
       <c r="E717" s="2"/>
@@ -18755,7 +18751,7 @@
       <c r="V717" s="2"/>
       <c r="W717" s="2"/>
     </row>
-    <row r="718" ht="13.2" spans="3:23">
+    <row r="718" ht="12.75" spans="3:23">
       <c r="C718" s="2"/>
       <c r="D718" s="2"/>
       <c r="E718" s="2"/>
@@ -18778,7 +18774,7 @@
       <c r="V718" s="2"/>
       <c r="W718" s="2"/>
     </row>
-    <row r="719" ht="13.2" spans="3:23">
+    <row r="719" ht="12.75" spans="3:23">
       <c r="C719" s="2"/>
       <c r="D719" s="2"/>
       <c r="E719" s="2"/>
@@ -18801,7 +18797,7 @@
       <c r="V719" s="2"/>
       <c r="W719" s="2"/>
     </row>
-    <row r="720" ht="13.2" spans="3:23">
+    <row r="720" ht="12.75" spans="3:23">
       <c r="C720" s="2"/>
       <c r="D720" s="2"/>
       <c r="E720" s="2"/>
@@ -18824,7 +18820,7 @@
       <c r="V720" s="2"/>
       <c r="W720" s="2"/>
     </row>
-    <row r="721" ht="13.2" spans="3:23">
+    <row r="721" ht="12.75" spans="3:23">
       <c r="C721" s="2"/>
       <c r="D721" s="2"/>
       <c r="E721" s="2"/>
@@ -18847,7 +18843,7 @@
       <c r="V721" s="2"/>
       <c r="W721" s="2"/>
     </row>
-    <row r="722" ht="13.2" spans="3:23">
+    <row r="722" ht="12.75" spans="3:23">
       <c r="C722" s="2"/>
       <c r="D722" s="2"/>
       <c r="E722" s="2"/>
@@ -18870,7 +18866,7 @@
       <c r="V722" s="2"/>
       <c r="W722" s="2"/>
     </row>
-    <row r="723" ht="13.2" spans="3:23">
+    <row r="723" ht="12.75" spans="3:23">
       <c r="C723" s="2"/>
       <c r="D723" s="2"/>
       <c r="E723" s="2"/>
@@ -18893,7 +18889,7 @@
       <c r="V723" s="2"/>
       <c r="W723" s="2"/>
     </row>
-    <row r="724" ht="13.2" spans="3:23">
+    <row r="724" ht="12.75" spans="3:23">
       <c r="C724" s="2"/>
       <c r="D724" s="2"/>
       <c r="E724" s="2"/>
@@ -18916,7 +18912,7 @@
       <c r="V724" s="2"/>
       <c r="W724" s="2"/>
     </row>
-    <row r="725" ht="13.2" spans="3:23">
+    <row r="725" ht="12.75" spans="3:23">
       <c r="C725" s="2"/>
       <c r="D725" s="2"/>
       <c r="E725" s="2"/>
@@ -18939,7 +18935,7 @@
       <c r="V725" s="2"/>
       <c r="W725" s="2"/>
     </row>
-    <row r="726" ht="13.2" spans="3:23">
+    <row r="726" ht="12.75" spans="3:23">
       <c r="C726" s="2"/>
       <c r="D726" s="2"/>
       <c r="E726" s="2"/>
@@ -18962,7 +18958,7 @@
       <c r="V726" s="2"/>
       <c r="W726" s="2"/>
     </row>
-    <row r="727" ht="13.2" spans="3:23">
+    <row r="727" ht="12.75" spans="3:23">
       <c r="C727" s="2"/>
       <c r="D727" s="2"/>
       <c r="E727" s="2"/>
@@ -18985,7 +18981,7 @@
       <c r="V727" s="2"/>
       <c r="W727" s="2"/>
     </row>
-    <row r="728" ht="13.2" spans="3:23">
+    <row r="728" ht="12.75" spans="3:23">
       <c r="C728" s="2"/>
       <c r="D728" s="2"/>
       <c r="E728" s="2"/>
@@ -19008,7 +19004,7 @@
       <c r="V728" s="2"/>
       <c r="W728" s="2"/>
     </row>
-    <row r="729" ht="13.2" spans="3:23">
+    <row r="729" ht="12.75" spans="3:23">
       <c r="C729" s="2"/>
       <c r="D729" s="2"/>
       <c r="E729" s="2"/>
@@ -19031,7 +19027,7 @@
       <c r="V729" s="2"/>
       <c r="W729" s="2"/>
     </row>
-    <row r="730" ht="13.2" spans="3:23">
+    <row r="730" ht="12.75" spans="3:23">
       <c r="C730" s="2"/>
       <c r="D730" s="2"/>
       <c r="E730" s="2"/>
@@ -19054,7 +19050,7 @@
       <c r="V730" s="2"/>
       <c r="W730" s="2"/>
     </row>
-    <row r="731" ht="13.2" spans="3:23">
+    <row r="731" ht="12.75" spans="3:23">
       <c r="C731" s="2"/>
       <c r="D731" s="2"/>
       <c r="E731" s="2"/>
@@ -19077,7 +19073,7 @@
       <c r="V731" s="2"/>
       <c r="W731" s="2"/>
     </row>
-    <row r="732" ht="13.2" spans="3:23">
+    <row r="732" ht="12.75" spans="3:23">
       <c r="C732" s="2"/>
       <c r="D732" s="2"/>
       <c r="E732" s="2"/>
@@ -19100,7 +19096,7 @@
       <c r="V732" s="2"/>
       <c r="W732" s="2"/>
     </row>
-    <row r="733" ht="13.2" spans="3:23">
+    <row r="733" ht="12.75" spans="3:23">
       <c r="C733" s="2"/>
       <c r="D733" s="2"/>
       <c r="E733" s="2"/>
@@ -19123,7 +19119,7 @@
       <c r="V733" s="2"/>
       <c r="W733" s="2"/>
     </row>
-    <row r="734" ht="13.2" spans="3:23">
+    <row r="734" ht="12.75" spans="3:23">
       <c r="C734" s="2"/>
       <c r="D734" s="2"/>
       <c r="E734" s="2"/>
@@ -19146,7 +19142,7 @@
       <c r="V734" s="2"/>
       <c r="W734" s="2"/>
     </row>
-    <row r="735" ht="13.2" spans="3:23">
+    <row r="735" ht="12.75" spans="3:23">
       <c r="C735" s="2"/>
       <c r="D735" s="2"/>
       <c r="E735" s="2"/>
@@ -19169,7 +19165,7 @@
       <c r="V735" s="2"/>
       <c r="W735" s="2"/>
     </row>
-    <row r="736" ht="13.2" spans="3:23">
+    <row r="736" ht="12.75" spans="3:23">
       <c r="C736" s="2"/>
       <c r="D736" s="2"/>
       <c r="E736" s="2"/>
@@ -19192,7 +19188,7 @@
       <c r="V736" s="2"/>
       <c r="W736" s="2"/>
     </row>
-    <row r="737" ht="13.2" spans="3:23">
+    <row r="737" ht="12.75" spans="3:23">
       <c r="C737" s="2"/>
       <c r="D737" s="2"/>
       <c r="E737" s="2"/>
@@ -19215,7 +19211,7 @@
       <c r="V737" s="2"/>
       <c r="W737" s="2"/>
     </row>
-    <row r="738" ht="13.2" spans="3:23">
+    <row r="738" ht="12.75" spans="3:23">
       <c r="C738" s="2"/>
       <c r="D738" s="2"/>
       <c r="E738" s="2"/>
@@ -19238,7 +19234,7 @@
       <c r="V738" s="2"/>
       <c r="W738" s="2"/>
     </row>
-    <row r="739" ht="13.2" spans="3:23">
+    <row r="739" ht="12.75" spans="3:23">
       <c r="C739" s="2"/>
       <c r="D739" s="2"/>
       <c r="E739" s="2"/>
@@ -19261,7 +19257,7 @@
       <c r="V739" s="2"/>
       <c r="W739" s="2"/>
     </row>
-    <row r="740" ht="13.2" spans="3:23">
+    <row r="740" ht="12.75" spans="3:23">
       <c r="C740" s="2"/>
       <c r="D740" s="2"/>
       <c r="E740" s="2"/>
@@ -19284,7 +19280,7 @@
       <c r="V740" s="2"/>
       <c r="W740" s="2"/>
     </row>
-    <row r="741" ht="13.2" spans="3:23">
+    <row r="741" ht="12.75" spans="3:23">
       <c r="C741" s="2"/>
       <c r="D741" s="2"/>
       <c r="E741" s="2"/>
@@ -19307,7 +19303,7 @@
       <c r="V741" s="2"/>
       <c r="W741" s="2"/>
     </row>
-    <row r="742" ht="13.2" spans="3:23">
+    <row r="742" ht="12.75" spans="3:23">
       <c r="C742" s="2"/>
       <c r="D742" s="2"/>
       <c r="E742" s="2"/>
@@ -19330,7 +19326,7 @@
       <c r="V742" s="2"/>
       <c r="W742" s="2"/>
     </row>
-    <row r="743" ht="13.2" spans="3:23">
+    <row r="743" ht="12.75" spans="3:23">
       <c r="C743" s="2"/>
       <c r="D743" s="2"/>
       <c r="E743" s="2"/>
@@ -19353,7 +19349,7 @@
       <c r="V743" s="2"/>
       <c r="W743" s="2"/>
     </row>
-    <row r="744" ht="13.2" spans="3:23">
+    <row r="744" ht="12.75" spans="3:23">
       <c r="C744" s="2"/>
       <c r="D744" s="2"/>
       <c r="E744" s="2"/>
@@ -19376,7 +19372,7 @@
       <c r="V744" s="2"/>
       <c r="W744" s="2"/>
     </row>
-    <row r="745" ht="13.2" spans="3:23">
+    <row r="745" ht="12.75" spans="3:23">
       <c r="C745" s="2"/>
       <c r="D745" s="2"/>
       <c r="E745" s="2"/>
@@ -19399,7 +19395,7 @@
       <c r="V745" s="2"/>
       <c r="W745" s="2"/>
     </row>
-    <row r="746" ht="13.2" spans="3:23">
+    <row r="746" ht="12.75" spans="3:23">
       <c r="C746" s="2"/>
       <c r="D746" s="2"/>
       <c r="E746" s="2"/>
@@ -19422,7 +19418,7 @@
       <c r="V746" s="2"/>
       <c r="W746" s="2"/>
     </row>
-    <row r="747" ht="13.2" spans="3:23">
+    <row r="747" ht="12.75" spans="3:23">
       <c r="C747" s="2"/>
       <c r="D747" s="2"/>
       <c r="E747" s="2"/>
@@ -19445,7 +19441,7 @@
       <c r="V747" s="2"/>
       <c r="W747" s="2"/>
     </row>
-    <row r="748" ht="13.2" spans="3:23">
+    <row r="748" ht="12.75" spans="3:23">
       <c r="C748" s="2"/>
       <c r="D748" s="2"/>
       <c r="E748" s="2"/>
@@ -19468,7 +19464,7 @@
       <c r="V748" s="2"/>
       <c r="W748" s="2"/>
     </row>
-    <row r="749" ht="13.2" spans="3:23">
+    <row r="749" ht="12.75" spans="3:23">
       <c r="C749" s="2"/>
       <c r="D749" s="2"/>
       <c r="E749" s="2"/>
@@ -19491,7 +19487,7 @@
       <c r="V749" s="2"/>
       <c r="W749" s="2"/>
     </row>
-    <row r="750" ht="13.2" spans="3:23">
+    <row r="750" ht="12.75" spans="3:23">
       <c r="C750" s="2"/>
       <c r="D750" s="2"/>
       <c r="E750" s="2"/>
@@ -19514,7 +19510,7 @@
       <c r="V750" s="2"/>
       <c r="W750" s="2"/>
     </row>
-    <row r="751" ht="13.2" spans="3:23">
+    <row r="751" ht="12.75" spans="3:23">
       <c r="C751" s="2"/>
       <c r="D751" s="2"/>
       <c r="E751" s="2"/>
@@ -19537,7 +19533,7 @@
       <c r="V751" s="2"/>
       <c r="W751" s="2"/>
     </row>
-    <row r="752" ht="13.2" spans="3:23">
+    <row r="752" ht="12.75" spans="3:23">
       <c r="C752" s="2"/>
       <c r="D752" s="2"/>
       <c r="E752" s="2"/>
@@ -19560,7 +19556,7 @@
       <c r="V752" s="2"/>
       <c r="W752" s="2"/>
     </row>
-    <row r="753" ht="13.2" spans="3:23">
+    <row r="753" ht="12.75" spans="3:23">
       <c r="C753" s="2"/>
       <c r="D753" s="2"/>
       <c r="E753" s="2"/>
@@ -19583,7 +19579,7 @@
       <c r="V753" s="2"/>
       <c r="W753" s="2"/>
     </row>
-    <row r="754" ht="13.2" spans="3:23">
+    <row r="754" ht="12.75" spans="3:23">
       <c r="C754" s="2"/>
       <c r="D754" s="2"/>
       <c r="E754" s="2"/>
@@ -19606,7 +19602,7 @@
       <c r="V754" s="2"/>
       <c r="W754" s="2"/>
     </row>
-    <row r="755" ht="13.2" spans="3:23">
+    <row r="755" ht="12.75" spans="3:23">
       <c r="C755" s="2"/>
       <c r="D755" s="2"/>
       <c r="E755" s="2"/>
@@ -19629,7 +19625,7 @@
       <c r="V755" s="2"/>
       <c r="W755" s="2"/>
     </row>
-    <row r="756" ht="13.2" spans="3:23">
+    <row r="756" ht="12.75" spans="3:23">
       <c r="C756" s="2"/>
       <c r="D756" s="2"/>
       <c r="E756" s="2"/>
@@ -19652,7 +19648,7 @@
       <c r="V756" s="2"/>
       <c r="W756" s="2"/>
     </row>
-    <row r="757" ht="13.2" spans="3:23">
+    <row r="757" ht="12.75" spans="3:23">
       <c r="C757" s="2"/>
       <c r="D757" s="2"/>
       <c r="E757" s="2"/>
@@ -19675,7 +19671,7 @@
       <c r="V757" s="2"/>
       <c r="W757" s="2"/>
     </row>
-    <row r="758" ht="13.2" spans="3:23">
+    <row r="758" ht="12.75" spans="3:23">
       <c r="C758" s="2"/>
       <c r="D758" s="2"/>
       <c r="E758" s="2"/>
@@ -19698,7 +19694,7 @@
       <c r="V758" s="2"/>
       <c r="W758" s="2"/>
     </row>
-    <row r="759" ht="13.2" spans="3:23">
+    <row r="759" ht="12.75" spans="3:23">
       <c r="C759" s="2"/>
       <c r="D759" s="2"/>
       <c r="E759" s="2"/>
@@ -19721,7 +19717,7 @@
       <c r="V759" s="2"/>
       <c r="W759" s="2"/>
     </row>
-    <row r="760" ht="13.2" spans="3:23">
+    <row r="760" ht="12.75" spans="3:23">
       <c r="C760" s="2"/>
       <c r="D760" s="2"/>
       <c r="E760" s="2"/>
@@ -19744,7 +19740,7 @@
       <c r="V760" s="2"/>
       <c r="W760" s="2"/>
     </row>
-    <row r="761" ht="13.2" spans="3:23">
+    <row r="761" ht="12.75" spans="3:23">
       <c r="C761" s="2"/>
       <c r="D761" s="2"/>
       <c r="E761" s="2"/>
@@ -19767,7 +19763,7 @@
       <c r="V761" s="2"/>
       <c r="W761" s="2"/>
     </row>
-    <row r="762" ht="13.2" spans="3:23">
+    <row r="762" ht="12.75" spans="3:23">
       <c r="C762" s="2"/>
       <c r="D762" s="2"/>
       <c r="E762" s="2"/>
@@ -19790,7 +19786,7 @@
       <c r="V762" s="2"/>
       <c r="W762" s="2"/>
     </row>
-    <row r="763" ht="13.2" spans="3:23">
+    <row r="763" ht="12.75" spans="3:23">
       <c r="C763" s="2"/>
       <c r="D763" s="2"/>
       <c r="E763" s="2"/>
@@ -19813,7 +19809,7 @@
       <c r="V763" s="2"/>
       <c r="W763" s="2"/>
     </row>
-    <row r="764" ht="13.2" spans="3:23">
+    <row r="764" ht="12.75" spans="3:23">
       <c r="C764" s="2"/>
       <c r="D764" s="2"/>
       <c r="E764" s="2"/>
@@ -19836,7 +19832,7 @@
       <c r="V764" s="2"/>
       <c r="W764" s="2"/>
     </row>
-    <row r="765" ht="13.2" spans="3:23">
+    <row r="765" ht="12.75" spans="3:23">
       <c r="C765" s="2"/>
       <c r="D765" s="2"/>
       <c r="E765" s="2"/>
@@ -19859,7 +19855,7 @@
       <c r="V765" s="2"/>
       <c r="W765" s="2"/>
     </row>
-    <row r="766" ht="13.2" spans="3:23">
+    <row r="766" ht="12.75" spans="3:23">
       <c r="C766" s="2"/>
       <c r="D766" s="2"/>
       <c r="E766" s="2"/>
@@ -19882,7 +19878,7 @@
       <c r="V766" s="2"/>
       <c r="W766" s="2"/>
     </row>
-    <row r="767" ht="13.2" spans="3:23">
+    <row r="767" ht="12.75" spans="3:23">
       <c r="C767" s="2"/>
       <c r="D767" s="2"/>
       <c r="E767" s="2"/>
@@ -19905,7 +19901,7 @@
       <c r="V767" s="2"/>
       <c r="W767" s="2"/>
     </row>
-    <row r="768" ht="13.2" spans="3:23">
+    <row r="768" ht="12.75" spans="3:23">
       <c r="C768" s="2"/>
       <c r="D768" s="2"/>
       <c r="E768" s="2"/>
@@ -19928,7 +19924,7 @@
       <c r="V768" s="2"/>
       <c r="W768" s="2"/>
     </row>
-    <row r="769" ht="13.2" spans="3:23">
+    <row r="769" ht="12.75" spans="3:23">
       <c r="C769" s="2"/>
       <c r="D769" s="2"/>
       <c r="E769" s="2"/>
@@ -19951,7 +19947,7 @@
       <c r="V769" s="2"/>
       <c r="W769" s="2"/>
     </row>
-    <row r="770" ht="13.2" spans="3:23">
+    <row r="770" ht="12.75" spans="3:23">
       <c r="C770" s="2"/>
       <c r="D770" s="2"/>
       <c r="E770" s="2"/>
@@ -19974,7 +19970,7 @@
       <c r="V770" s="2"/>
       <c r="W770" s="2"/>
     </row>
-    <row r="771" ht="13.2" spans="3:23">
+    <row r="771" ht="12.75" spans="3:23">
       <c r="C771" s="2"/>
       <c r="D771" s="2"/>
       <c r="E771" s="2"/>
@@ -19997,7 +19993,7 @@
       <c r="V771" s="2"/>
       <c r="W771" s="2"/>
     </row>
-    <row r="772" ht="13.2" spans="3:23">
+    <row r="772" ht="12.75" spans="3:23">
       <c r="C772" s="2"/>
       <c r="D772" s="2"/>
       <c r="E772" s="2"/>
@@ -20020,7 +20016,7 @@
       <c r="V772" s="2"/>
       <c r="W772" s="2"/>
     </row>
-    <row r="773" ht="13.2" spans="3:23">
+    <row r="773" ht="12.75" spans="3:23">
       <c r="C773" s="2"/>
       <c r="D773" s="2"/>
       <c r="E773" s="2"/>
@@ -20043,7 +20039,7 @@
       <c r="V773" s="2"/>
       <c r="W773" s="2"/>
     </row>
-    <row r="774" ht="13.2" spans="3:23">
+    <row r="774" ht="12.75" spans="3:23">
       <c r="C774" s="2"/>
       <c r="D774" s="2"/>
       <c r="E774" s="2"/>
@@ -20066,7 +20062,7 @@
       <c r="V774" s="2"/>
       <c r="W774" s="2"/>
     </row>
-    <row r="775" ht="13.2" spans="3:23">
+    <row r="775" ht="12.75" spans="3:23">
       <c r="C775" s="2"/>
       <c r="D775" s="2"/>
       <c r="E775" s="2"/>
@@ -20089,7 +20085,7 @@
       <c r="V775" s="2"/>
       <c r="W775" s="2"/>
     </row>
-    <row r="776" ht="13.2" spans="3:23">
+    <row r="776" ht="12.75" spans="3:23">
       <c r="C776" s="2"/>
       <c r="D776" s="2"/>
       <c r="E776" s="2"/>
@@ -20112,7 +20108,7 @@
       <c r="V776" s="2"/>
       <c r="W776" s="2"/>
     </row>
-    <row r="777" ht="13.2" spans="3:23">
+    <row r="777" ht="12.75" spans="3:23">
       <c r="C777" s="2"/>
       <c r="D777" s="2"/>
       <c r="E777" s="2"/>
@@ -20135,7 +20131,7 @@
       <c r="V777" s="2"/>
       <c r="W777" s="2"/>
     </row>
-    <row r="778" ht="13.2" spans="3:23">
+    <row r="778" ht="12.75" spans="3:23">
       <c r="C778" s="2"/>
       <c r="D778" s="2"/>
       <c r="E778" s="2"/>
@@ -20158,7 +20154,7 @@
       <c r="V778" s="2"/>
       <c r="W778" s="2"/>
     </row>
-    <row r="779" ht="13.2" spans="3:23">
+    <row r="779" ht="12.75" spans="3:23">
       <c r="C779" s="2"/>
       <c r="D779" s="2"/>
       <c r="E779" s="2"/>
@@ -20181,7 +20177,7 @@
       <c r="V779" s="2"/>
       <c r="W779" s="2"/>
     </row>
-    <row r="780" ht="13.2" spans="3:23">
+    <row r="780" ht="12.75" spans="3:23">
       <c r="C780" s="2"/>
       <c r="D780" s="2"/>
       <c r="E780" s="2"/>
@@ -20204,7 +20200,7 @@
       <c r="V780" s="2"/>
       <c r="W780" s="2"/>
     </row>
-    <row r="781" ht="13.2" spans="3:23">
+    <row r="781" ht="12.75" spans="3:23">
       <c r="C781" s="2"/>
       <c r="D781" s="2"/>
       <c r="E781" s="2"/>
@@ -20227,7 +20223,7 @@
       <c r="V781" s="2"/>
       <c r="W781" s="2"/>
     </row>
-    <row r="782" ht="13.2" spans="3:23">
+    <row r="782" ht="12.75" spans="3:23">
       <c r="C782" s="2"/>
       <c r="D782" s="2"/>
       <c r="E782" s="2"/>
@@ -20250,7 +20246,7 @@
       <c r="V782" s="2"/>
       <c r="W782" s="2"/>
     </row>
-    <row r="783" ht="13.2" spans="3:23">
+    <row r="783" ht="12.75" spans="3:23">
       <c r="C783" s="2"/>
       <c r="D783" s="2"/>
       <c r="E783" s="2"/>
@@ -20273,7 +20269,7 @@
       <c r="V783" s="2"/>
       <c r="W783" s="2"/>
     </row>
-    <row r="784" ht="13.2" spans="3:23">
+    <row r="784" ht="12.75" spans="3:23">
       <c r="C784" s="2"/>
       <c r="D784" s="2"/>
       <c r="E784" s="2"/>
@@ -20296,7 +20292,7 @@
       <c r="V784" s="2"/>
       <c r="W784" s="2"/>
     </row>
-    <row r="785" ht="13.2" spans="3:23">
+    <row r="785" ht="12.75" spans="3:23">
       <c r="C785" s="2"/>
       <c r="D785" s="2"/>
       <c r="E785" s="2"/>
@@ -20319,7 +20315,7 @@
       <c r="V785" s="2"/>
       <c r="W785" s="2"/>
     </row>
-    <row r="786" ht="13.2" spans="3:23">
+    <row r="786" ht="12.75" spans="3:23">
       <c r="C786" s="2"/>
       <c r="D786" s="2"/>
       <c r="E786" s="2"/>
@@ -20342,7 +20338,7 @@
       <c r="V786" s="2"/>
       <c r="W786" s="2"/>
     </row>
-    <row r="787" ht="13.2" spans="3:23">
+    <row r="787" ht="12.75" spans="3:23">
       <c r="C787" s="2"/>
       <c r="D787" s="2"/>
       <c r="E787" s="2"/>
@@ -20365,7 +20361,7 @@
       <c r="V787" s="2"/>
       <c r="W787" s="2"/>
     </row>
-    <row r="788" ht="13.2" spans="3:23">
+    <row r="788" ht="12.75" spans="3:23">
       <c r="C788" s="2"/>
       <c r="D788" s="2"/>
       <c r="E788" s="2"/>
@@ -20388,7 +20384,7 @@
       <c r="V788" s="2"/>
       <c r="W788" s="2"/>
     </row>
-    <row r="789" ht="13.2" spans="3:23">
+    <row r="789" ht="12.75" spans="3:23">
       <c r="C789" s="2"/>
       <c r="D789" s="2"/>
       <c r="E789" s="2"/>
@@ -20411,7 +20407,7 @@
       <c r="V789" s="2"/>
       <c r="W789" s="2"/>
     </row>
-    <row r="790" ht="13.2" spans="3:23">
+    <row r="790" ht="12.75" spans="3:23">
       <c r="C790" s="2"/>
       <c r="D790" s="2"/>
       <c r="E790" s="2"/>
@@ -20434,7 +20430,7 @@
       <c r="V790" s="2"/>
       <c r="W790" s="2"/>
     </row>
-    <row r="791" ht="13.2" spans="3:23">
+    <row r="791" ht="12.75" spans="3:23">
       <c r="C791" s="2"/>
       <c r="D791" s="2"/>
       <c r="E791" s="2"/>
@@ -20457,7 +20453,7 @@
       <c r="V791" s="2"/>
       <c r="W791" s="2"/>
     </row>
-    <row r="792" ht="13.2" spans="3:23">
+    <row r="792" ht="12.75" spans="3:23">
       <c r="C792" s="2"/>
       <c r="D792" s="2"/>
       <c r="E792" s="2"/>
@@ -20480,7 +20476,7 @@
       <c r="V792" s="2"/>
       <c r="W792" s="2"/>
     </row>
-    <row r="793" ht="13.2" spans="3:23">
+    <row r="793" ht="12.75" spans="3:23">
       <c r="C793" s="2"/>
       <c r="D793" s="2"/>
       <c r="E793" s="2"/>
@@ -20503,7 +20499,7 @@
       <c r="V793" s="2"/>
       <c r="W793" s="2"/>
     </row>
-    <row r="794" ht="13.2" spans="3:23">
+    <row r="794" ht="12.75" spans="3:23">
       <c r="C794" s="2"/>
       <c r="D794" s="2"/>
       <c r="E794" s="2"/>
@@ -20526,7 +20522,7 @@
       <c r="V794" s="2"/>
       <c r="W794" s="2"/>
     </row>
-    <row r="795" ht="13.2" spans="3:23">
+    <row r="795" ht="12.75" spans="3:23">
       <c r="C795" s="2"/>
       <c r="D795" s="2"/>
       <c r="E795" s="2"/>
@@ -20549,7 +20545,7 @@
       <c r="V795" s="2"/>
       <c r="W795" s="2"/>
     </row>
-    <row r="796" ht="13.2" spans="3:23">
+    <row r="796" ht="12.75" spans="3:23">
       <c r="C796" s="2"/>
       <c r="D796" s="2"/>
       <c r="E796" s="2"/>
@@ -20572,7 +20568,7 @@
       <c r="V796" s="2"/>
       <c r="W796" s="2"/>
     </row>
-    <row r="797" ht="13.2" spans="3:23">
+    <row r="797" ht="12.75" spans="3:23">
       <c r="C797" s="2"/>
       <c r="D797" s="2"/>
       <c r="E797" s="2"/>
@@ -20595,7 +20591,7 @@
       <c r="V797" s="2"/>
       <c r="W797" s="2"/>
     </row>
-    <row r="798" ht="13.2" spans="3:23">
+    <row r="798" ht="12.75" spans="3:23">
       <c r="C798" s="2"/>
       <c r="D798" s="2"/>
       <c r="E798" s="2"/>
@@ -20618,7 +20614,7 @@
       <c r="V798" s="2"/>
       <c r="W798" s="2"/>
     </row>
-    <row r="799" ht="13.2" spans="3:23">
+    <row r="799" ht="12.75" spans="3:23">
       <c r="C799" s="2"/>
       <c r="D799" s="2"/>
       <c r="E799" s="2"/>
@@ -20641,7 +20637,7 @@
       <c r="V799" s="2"/>
       <c r="W799" s="2"/>
     </row>
-    <row r="800" ht="13.2" spans="3:23">
+    <row r="800" ht="12.75" spans="3:23">
       <c r="C800" s="2"/>
       <c r="D800" s="2"/>
       <c r="E800" s="2"/>
@@ -20664,7 +20660,7 @@
       <c r="V800" s="2"/>
       <c r="W800" s="2"/>
     </row>
-    <row r="801" ht="13.2" spans="3:23">
+    <row r="801" ht="12.75" spans="3:23">
       <c r="C801" s="2"/>
       <c r="D801" s="2"/>
       <c r="E801" s="2"/>
@@ -20687,7 +20683,7 @@
       <c r="V801" s="2"/>
       <c r="W801" s="2"/>
     </row>
-    <row r="802" ht="13.2" spans="3:23">
+    <row r="802" ht="12.75" spans="3:23">
       <c r="C802" s="2"/>
       <c r="D802" s="2"/>
       <c r="E802" s="2"/>
@@ -20710,7 +20706,7 @@
       <c r="V802" s="2"/>
       <c r="W802" s="2"/>
     </row>
-    <row r="803" ht="13.2" spans="3:23">
+    <row r="803" ht="12.75" spans="3:23">
       <c r="C803" s="2"/>
       <c r="D803" s="2"/>
       <c r="E803" s="2"/>
@@ -20733,7 +20729,7 @@
       <c r="V803" s="2"/>
       <c r="W803" s="2"/>
     </row>
-    <row r="804" ht="13.2" spans="3:23">
+    <row r="804" ht="12.75" spans="3:23">
       <c r="C804" s="2"/>
       <c r="D804" s="2"/>
       <c r="E804" s="2"/>
@@ -20756,7 +20752,7 @@
       <c r="V804" s="2"/>
       <c r="W804" s="2"/>
     </row>
-    <row r="805" ht="13.2" spans="3:23">
+    <row r="805" ht="12.75" spans="3:23">
       <c r="C805" s="2"/>
       <c r="D805" s="2"/>
       <c r="E805" s="2"/>
@@ -20779,7 +20775,7 @@
       <c r="V805" s="2"/>
       <c r="W805" s="2"/>
     </row>
-    <row r="806" ht="13.2" spans="3:23">
+    <row r="806" ht="12.75" spans="3:23">
       <c r="C806" s="2"/>
       <c r="D806" s="2"/>
       <c r="E806" s="2"/>
@@ -20802,7 +20798,7 @@
       <c r="V806" s="2"/>
       <c r="W806" s="2"/>
     </row>
-    <row r="807" ht="13.2" spans="3:23">
+    <row r="807" ht="12.75" spans="3:23">
       <c r="C807" s="2"/>
       <c r="D807" s="2"/>
       <c r="E807" s="2"/>
@@ -20825,7 +20821,7 @@
       <c r="V807" s="2"/>
       <c r="W807" s="2"/>
     </row>
-    <row r="808" ht="13.2" spans="3:23">
+    <row r="808" ht="12.75" spans="3:23">
       <c r="C808" s="2"/>
       <c r="D808" s="2"/>
       <c r="E808" s="2"/>
@@ -20848,7 +20844,7 @@
       <c r="V808" s="2"/>
       <c r="W808" s="2"/>
     </row>
-    <row r="809" ht="13.2" spans="3:23">
+    <row r="809" ht="12.75" spans="3:23">
       <c r="C809" s="2"/>
       <c r="D809" s="2"/>
       <c r="E809" s="2"/>
@@ -20871,7 +20867,7 @@
       <c r="V809" s="2"/>
       <c r="W809" s="2"/>
     </row>
-    <row r="810" ht="13.2" spans="3:23">
+    <row r="810" ht="12.75" spans="3:23">
       <c r="C810" s="2"/>
       <c r="D810" s="2"/>
       <c r="E810" s="2"/>
@@ -20894,7 +20890,7 @@
       <c r="V810" s="2"/>
       <c r="W810" s="2"/>
     </row>
-    <row r="811" ht="13.2" spans="3:23">
+    <row r="811" ht="12.75" spans="3:23">
       <c r="C811" s="2"/>
       <c r="D811" s="2"/>
       <c r="E811" s="2"/>
@@ -20917,7 +20913,7 @@
       <c r="V811" s="2"/>
       <c r="W811" s="2"/>
     </row>
-    <row r="812" ht="13.2" spans="3:23">
+    <row r="812" ht="12.75" spans="3:23">
       <c r="C812" s="2"/>
       <c r="D812" s="2"/>
       <c r="E812" s="2"/>
@@ -20940,7 +20936,7 @@
       <c r="V812" s="2"/>
       <c r="W812" s="2"/>
     </row>
-    <row r="813" ht="13.2" spans="3:23">
+    <row r="813" ht="12.75" spans="3:23">
       <c r="C813" s="2"/>
       <c r="D813" s="2"/>
       <c r="E813" s="2"/>
@@ -20963,7 +20959,7 @@
       <c r="V813" s="2"/>
       <c r="W813" s="2"/>
     </row>
-    <row r="814" ht="13.2" spans="3:23">
+    <row r="814" ht="12.75" spans="3:23">
       <c r="C814" s="2"/>
       <c r="D814" s="2"/>
       <c r="E814" s="2"/>
@@ -20986,7 +20982,7 @@
       <c r="V814" s="2"/>
       <c r="W814" s="2"/>
     </row>
-    <row r="815" ht="13.2" spans="3:23">
+    <row r="815" ht="12.75" spans="3:23">
       <c r="C815" s="2"/>
       <c r="D815" s="2"/>
       <c r="E815" s="2"/>
@@ -21009,7 +21005,7 @@
       <c r="V815" s="2"/>
       <c r="W815" s="2"/>
     </row>
-    <row r="816" ht="13.2" spans="3:23">
+    <row r="816" ht="12.75" spans="3:23">
       <c r="C816" s="2"/>
       <c r="D816" s="2"/>
       <c r="E816" s="2"/>
@@ -21032,7 +21028,7 @@
       <c r="V816" s="2"/>
       <c r="W816" s="2"/>
     </row>
-    <row r="817" ht="13.2" spans="3:23">
+    <row r="817" ht="12.75" spans="3:23">
       <c r="C817" s="2"/>
       <c r="D817" s="2"/>
       <c r="E817" s="2"/>
@@ -21055,7 +21051,7 @@
       <c r="V817" s="2"/>
       <c r="W817" s="2"/>
     </row>
-    <row r="818" ht="13.2" spans="3:23">
+    <row r="818" ht="12.75" spans="3:23">
       <c r="C818" s="2"/>
       <c r="D818" s="2"/>
       <c r="E818" s="2"/>
@@ -21078,7 +21074,7 @@
       <c r="V818" s="2"/>
       <c r="W818" s="2"/>
     </row>
-    <row r="819" ht="13.2" spans="3:23">
+    <row r="819" ht="12.75" spans="3:23">
       <c r="C819" s="2"/>
       <c r="D819" s="2"/>
       <c r="E819" s="2"/>
@@ -21101,7 +21097,7 @@
       <c r="V819" s="2"/>
       <c r="W819" s="2"/>
     </row>
-    <row r="820" ht="13.2" spans="3:23">
+    <row r="820" ht="12.75" spans="3:23">
       <c r="C820" s="2"/>
       <c r="D820" s="2"/>
       <c r="E820" s="2"/>
@@ -21124,7 +21120,7 @@
       <c r="V820" s="2"/>
       <c r="W820" s="2"/>
     </row>
-    <row r="821" ht="13.2" spans="3:23">
+    <row r="821" ht="12.75" spans="3:23">
       <c r="C821" s="2"/>
       <c r="D821" s="2"/>
       <c r="E821" s="2"/>
@@ -21147,7 +21143,7 @@
       <c r="V821" s="2"/>
       <c r="W821" s="2"/>
     </row>
-    <row r="822" ht="13.2" spans="3:23">
+    <row r="822" ht="12.75" spans="3:23">
       <c r="C822" s="2"/>
       <c r="D822" s="2"/>
       <c r="E822" s="2"/>
@@ -21170,7 +21166,7 @@
       <c r="V822" s="2"/>
       <c r="W822" s="2"/>
     </row>
-    <row r="823" ht="13.2" spans="3:23">
+    <row r="823" ht="12.75" spans="3:23">
       <c r="C823" s="2"/>
       <c r="D823" s="2"/>
       <c r="E823" s="2"/>
@@ -21193,7 +21189,7 @@
       <c r="V823" s="2"/>
       <c r="W823" s="2"/>
     </row>
-    <row r="824" ht="13.2" spans="3:23">
+    <row r="824" ht="12.75" spans="3:23">
       <c r="C824" s="2"/>
       <c r="D824" s="2"/>
       <c r="E824" s="2"/>
@@ -21216,7 +21212,7 @@
       <c r="V824" s="2"/>
       <c r="W824" s="2"/>
     </row>
-    <row r="825" ht="13.2" spans="3:23">
+    <row r="825" ht="12.75" spans="3:23">
       <c r="C825" s="2"/>
       <c r="D825" s="2"/>
       <c r="E825" s="2"/>
@@ -21239,7 +21235,7 @@
       <c r="V825" s="2"/>
       <c r="W825" s="2"/>
     </row>
-    <row r="826" ht="13.2" spans="3:23">
+    <row r="826" ht="12.75" spans="3:23">
       <c r="C826" s="2"/>
       <c r="D826" s="2"/>
       <c r="E826" s="2"/>
@@ -21262,7 +21258,7 @@
       <c r="V826" s="2"/>
       <c r="W826" s="2"/>
     </row>
-    <row r="827" ht="13.2" spans="3:23">
+    <row r="827" ht="12.75" spans="3:23">
       <c r="C827" s="2"/>
       <c r="D827" s="2"/>
       <c r="E827" s="2"/>
@@ -21285,7 +21281,7 @@
       <c r="V827" s="2"/>
       <c r="W827" s="2"/>
     </row>
-    <row r="828" ht="13.2" spans="3:23">
+    <row r="828" ht="12.75" spans="3:23">
       <c r="C828" s="2"/>
       <c r="D828" s="2"/>
       <c r="E828" s="2"/>
@@ -21308,7 +21304,7 @@
       <c r="V828" s="2"/>
       <c r="W828" s="2"/>
     </row>
-    <row r="829" ht="13.2" spans="3:23">
+    <row r="829" ht="12.75" spans="3:23">
       <c r="C829" s="2"/>
       <c r="D829" s="2"/>
       <c r="E829" s="2"/>
@@ -21331,7 +21327,7 @@
       <c r="V829" s="2"/>
       <c r="W829" s="2"/>
     </row>
-    <row r="830" ht="13.2" spans="3:23">
+    <row r="830" ht="12.75" spans="3:23">
       <c r="C830" s="2"/>
       <c r="D830" s="2"/>
       <c r="E830" s="2"/>
@@ -21354,7 +21350,7 @@
       <c r="V830" s="2"/>
       <c r="W830" s="2"/>
     </row>
-    <row r="831" ht="13.2" spans="3:23">
+    <row r="831" ht="12.75" spans="3:23">
       <c r="C831" s="2"/>
       <c r="D831" s="2"/>
       <c r="E831" s="2"/>
@@ -21377,7 +21373,7 @@
       <c r="V831" s="2"/>
       <c r="W831" s="2"/>
     </row>
-    <row r="832" ht="13.2" spans="3:23">
+    <row r="832" ht="12.75" spans="3:23">
       <c r="C832" s="2"/>
       <c r="D832" s="2"/>
       <c r="E832" s="2"/>
@@ -21400,7 +21396,7 @@
       <c r="V832" s="2"/>
       <c r="W832" s="2"/>
     </row>
-    <row r="833" ht="13.2" spans="3:23">
+    <row r="833" ht="12.75" spans="3:23">
       <c r="C833" s="2"/>
       <c r="D833" s="2"/>
       <c r="E833" s="2"/>
@@ -21423,7 +21419,7 @@
       <c r="V833" s="2"/>
       <c r="W833" s="2"/>
     </row>
-    <row r="834" ht="13.2" spans="3:23">
+    <row r="834" ht="12.75" spans="3:23">
       <c r="C834" s="2"/>
       <c r="D834" s="2"/>
       <c r="E834" s="2"/>
@@ -21446,7 +21442,7 @@
       <c r="V834" s="2"/>
       <c r="W834" s="2"/>
     </row>
-    <row r="835" ht="13.2" spans="3:23">
+    <row r="835" ht="12.75" spans="3:23">
       <c r="C835" s="2"/>
       <c r="D835" s="2"/>
       <c r="E835" s="2"/>
@@ -21469,7 +21465,7 @@
       <c r="V835" s="2"/>
       <c r="W835" s="2"/>
     </row>
-    <row r="836" ht="13.2" spans="3:23">
+    <row r="836" ht="12.75" spans="3:23">
       <c r="C836" s="2"/>
       <c r="D836" s="2"/>
       <c r="E836" s="2"/>
@@ -21492,7 +21488,7 @@
       <c r="V836" s="2"/>
       <c r="W836" s="2"/>
     </row>
-    <row r="837" ht="13.2" spans="3:23">
+    <row r="837" ht="12.75" spans="3:23">
       <c r="C837" s="2"/>
       <c r="D837" s="2"/>
       <c r="E837" s="2"/>
@@ -21515,7 +21511,7 @@
       <c r="V837" s="2"/>
       <c r="W837" s="2"/>
     </row>
-    <row r="838" ht="13.2" spans="3:23">
+    <row r="838" ht="12.75" spans="3:23">
       <c r="C838" s="2"/>
       <c r="D838" s="2"/>
       <c r="E838" s="2"/>
@@ -21538,7 +21534,7 @@
       <c r="V838" s="2"/>
       <c r="W838" s="2"/>
     </row>
-    <row r="839" ht="13.2" spans="3:23">
+    <row r="839" ht="12.75" spans="3:23">
       <c r="C839" s="2"/>
       <c r="D839" s="2"/>
       <c r="E839" s="2"/>
@@ -21561,7 +21557,7 @@
       <c r="V839" s="2"/>
       <c r="W839" s="2"/>
     </row>
-    <row r="840" ht="13.2" spans="3:23">
+    <row r="840" ht="12.75" spans="3:23">
       <c r="C840" s="2"/>
       <c r="D840" s="2"/>
       <c r="E840" s="2"/>
@@ -21584,7 +21580,7 @@
       <c r="V840" s="2"/>
       <c r="W840" s="2"/>
     </row>
-    <row r="841" ht="13.2" spans="3:23">
+    <row r="841" ht="12.75" spans="3:23">
       <c r="C841" s="2"/>
       <c r="D841" s="2"/>
       <c r="E841" s="2"/>
@@ -21607,7 +21603,7 @@
       <c r="V841" s="2"/>
       <c r="W841" s="2"/>
     </row>
-    <row r="842" ht="13.2" spans="3:23">
+    <row r="842" ht="12.75" spans="3:23">
       <c r="C842" s="2"/>
       <c r="D842" s="2"/>
       <c r="E842" s="2"/>
@@ -21630,7 +21626,7 @@
       <c r="V842" s="2"/>
       <c r="W842" s="2"/>
     </row>
-    <row r="843" ht="13.2" spans="3:23">
+    <row r="843" ht="12.75" spans="3:23">
       <c r="C843" s="2"/>
       <c r="D843" s="2"/>
       <c r="E843" s="2"/>
@@ -21653,7 +21649,7 @@
       <c r="V843" s="2"/>
       <c r="W843" s="2"/>
     </row>
-    <row r="844" ht="13.2" spans="3:23">
+    <row r="844" ht="12.75" spans="3:23">
       <c r="C844" s="2"/>
       <c r="D844" s="2"/>
       <c r="E844" s="2"/>
@@ -21676,7 +21672,7 @@
       <c r="V844" s="2"/>
       <c r="W844" s="2"/>
     </row>
-    <row r="845" ht="13.2" spans="3:23">
+    <row r="845" ht="12.75" spans="3:23">
       <c r="C845" s="2"/>
       <c r="D845" s="2"/>
       <c r="E845" s="2"/>
@@ -21699,7 +21695,7 @@
       <c r="V845" s="2"/>
       <c r="W845" s="2"/>
     </row>
-    <row r="846" ht="13.2" spans="3:23">
+    <row r="846" ht="12.75" spans="3:23">
       <c r="C846" s="2"/>
       <c r="D846" s="2"/>
       <c r="E846" s="2"/>
@@ -21722,7 +21718,7 @@
       <c r="V846" s="2"/>
       <c r="W846" s="2"/>
     </row>
-    <row r="847" ht="13.2" spans="3:23">
+    <row r="847" ht="12.75" spans="3:23">
       <c r="C847" s="2"/>
       <c r="D847" s="2"/>
       <c r="E847" s="2"/>
@@ -21745,7 +21741,7 @@
       <c r="V847" s="2"/>
       <c r="W847" s="2"/>
     </row>
-    <row r="848" ht="13.2" spans="3:23">
+    <row r="848" ht="12.75" spans="3:23">
       <c r="C848" s="2"/>
       <c r="D848" s="2"/>
       <c r="E848" s="2"/>
@@ -21768,7 +21764,7 @@
       <c r="V848" s="2"/>
       <c r="W848" s="2"/>
     </row>
-    <row r="849" ht="13.2" spans="3:23">
+    <row r="849" ht="12.75" spans="3:23">
       <c r="C849" s="2"/>
       <c r="D849" s="2"/>
       <c r="E849" s="2"/>
@@ -21791,7 +21787,7 @@
       <c r="V849" s="2"/>
       <c r="W849" s="2"/>
     </row>
-    <row r="850" ht="13.2" spans="3:23">
+    <row r="850" ht="12.75" spans="3:23">
       <c r="C850" s="2"/>
       <c r="D850" s="2"/>
       <c r="E850" s="2"/>
@@ -21814,7 +21810,7 @@
       <c r="V850" s="2"/>
       <c r="W850" s="2"/>
     </row>
-    <row r="851" ht="13.2" spans="3:23">
+    <row r="851" ht="12.75" spans="3:23">
       <c r="C851" s="2"/>
       <c r="D851" s="2"/>
       <c r="E851" s="2"/>
@@ -21837,7 +21833,7 @@
       <c r="V851" s="2"/>
       <c r="W851" s="2"/>
     </row>
-    <row r="852" ht="13.2" spans="3:23">
+    <row r="852" ht="12.75" spans="3:23">
       <c r="C852" s="2"/>
       <c r="D852" s="2"/>
       <c r="E852" s="2"/>
@@ -21860,7 +21856,7 @@
       <c r="V852" s="2"/>
       <c r="W852" s="2"/>
     </row>
-    <row r="853" ht="13.2" spans="3:23">
+    <row r="853" ht="12.75" spans="3:23">
       <c r="C853" s="2"/>
       <c r="D853" s="2"/>
       <c r="E853" s="2"/>
@@ -21883,7 +21879,7 @@
       <c r="V853" s="2"/>
       <c r="W853" s="2"/>
     </row>
-    <row r="854" ht="13.2" spans="3:23">
+    <row r="854" ht="12.75" spans="3:23">
       <c r="C854" s="2"/>
       <c r="D854" s="2"/>
       <c r="E854" s="2"/>
@@ -21906,7 +21902,7 @@
       <c r="V854" s="2"/>
       <c r="W854" s="2"/>
     </row>
-    <row r="855" ht="13.2" spans="3:23">
+    <row r="855" ht="12.75" spans="3:23">
       <c r="C855" s="2"/>
       <c r="D855" s="2"/>
       <c r="E855" s="2"/>
@@ -21929,7 +21925,7 @@
       <c r="V855" s="2"/>
       <c r="W855" s="2"/>
     </row>
-    <row r="856" ht="13.2" spans="3:23">
+    <row r="856" ht="12.75" spans="3:23">
       <c r="C856" s="2"/>
       <c r="D856" s="2"/>
       <c r="E856" s="2"/>
@@ -21952,7 +21948,7 @@
       <c r="V856" s="2"/>
       <c r="W856" s="2"/>
     </row>
-    <row r="857" ht="13.2" spans="3:23">
+    <row r="857" ht="12.75" spans="3:23">
       <c r="C857" s="2"/>
       <c r="D857" s="2"/>
       <c r="E857" s="2"/>
@@ -21975,7 +21971,7 @@
       <c r="V857" s="2"/>
       <c r="W857" s="2"/>
     </row>
-    <row r="858" ht="13.2" spans="3:23">
+    <row r="858" ht="12.75" spans="3:23">
       <c r="C858" s="2"/>
       <c r="D858" s="2"/>
       <c r="E858" s="2"/>
@@ -21998,7 +21994,7 @@
       <c r="V858" s="2"/>
       <c r="W858" s="2"/>
     </row>
-    <row r="859" ht="13.2" spans="3:23">
+    <row r="859" ht="12.75" spans="3:23">
       <c r="C859" s="2"/>
       <c r="D859" s="2"/>
       <c r="E859" s="2"/>
@@ -22021,7 +22017,7 @@
       <c r="V859" s="2"/>
       <c r="W859" s="2"/>
     </row>
-    <row r="860" ht="13.2" spans="3:23">
+    <row r="860" ht="12.75" spans="3:23">
       <c r="C860" s="2"/>
       <c r="D860" s="2"/>
       <c r="E860" s="2"/>
@@ -22044,7 +22040,7 @@
       <c r="V860" s="2"/>
       <c r="W860" s="2"/>
     </row>
-    <row r="861" ht="13.2" spans="3:23">
+    <row r="861" ht="12.75" spans="3:23">
       <c r="C861" s="2"/>
       <c r="D861" s="2"/>
       <c r="E861" s="2"/>
@@ -22067,7 +22063,7 @@
       <c r="V861" s="2"/>
       <c r="W861" s="2"/>
     </row>
-    <row r="862" ht="13.2" spans="3:23">
+    <row r="862" ht="12.75" spans="3:23">
       <c r="C862" s="2"/>
       <c r="D862" s="2"/>
       <c r="E862" s="2"/>
@@ -22090,7 +22086,7 @@
       <c r="V862" s="2"/>
       <c r="W862" s="2"/>
     </row>
-    <row r="863" ht="13.2" spans="3:23">
+    <row r="863" ht="12.75" spans="3:23">
       <c r="C863" s="2"/>
       <c r="D863" s="2"/>
       <c r="E863" s="2"/>
@@ -22113,7 +22109,7 @@
       <c r="V863" s="2"/>
       <c r="W863" s="2"/>
     </row>
-    <row r="864" ht="13.2" spans="3:23">
+    <row r="864" ht="12.75" spans="3:23">
       <c r="C864" s="2"/>
       <c r="D864" s="2"/>
       <c r="E864" s="2"/>
@@ -22136,7 +22132,7 @@
       <c r="V864" s="2"/>
       <c r="W864" s="2"/>
     </row>
-    <row r="865" ht="13.2" spans="3:23">
+    <row r="865" ht="12.75" spans="3:23">
       <c r="C865" s="2"/>
       <c r="D865" s="2"/>
       <c r="E865" s="2"/>
@@ -22159,7 +22155,7 @@
       <c r="V865" s="2"/>
       <c r="W865" s="2"/>
     </row>
-    <row r="866" ht="13.2" spans="3:23">
+    <row r="866" ht="12.75" spans="3:23">
       <c r="C866" s="2"/>
       <c r="D866" s="2"/>
       <c r="E866" s="2"/>
@@ -22182,7 +22178,7 @@
       <c r="V866" s="2"/>
       <c r="W866" s="2"/>
     </row>
-    <row r="867" ht="13.2" spans="3:23">
+    <row r="867" ht="12.75" spans="3:23">
       <c r="C867" s="2"/>
       <c r="D867" s="2"/>
       <c r="E867" s="2"/>
@@ -22205,7 +22201,7 @@
       <c r="V867" s="2"/>
       <c r="W867" s="2"/>
     </row>
-    <row r="868" ht="13.2" spans="3:23">
+    <row r="868" ht="12.75" spans="3:23">
       <c r="C868" s="2"/>
       <c r="D868" s="2"/>
       <c r="E868" s="2"/>
@@ -22228,7 +22224,7 @@
       <c r="V868" s="2"/>
       <c r="W868" s="2"/>
     </row>
-    <row r="869" ht="13.2" spans="3:23">
+    <row r="869" ht="12.75" spans="3:23">
       <c r="C869" s="2"/>
       <c r="D869" s="2"/>
       <c r="E869" s="2"/>
@@ -22251,7 +22247,7 @@
       <c r="V869" s="2"/>
       <c r="W869" s="2"/>
     </row>
-    <row r="870" ht="13.2" spans="3:23">
+    <row r="870" ht="12.75" spans="3:23">
       <c r="C870" s="2"/>
       <c r="D870" s="2"/>
       <c r="E870" s="2"/>
@@ -22274,7 +22270,7 @@
       <c r="V870" s="2"/>
       <c r="W870" s="2"/>
     </row>
-    <row r="871" ht="13.2" spans="3:23">
+    <row r="871" ht="12.75" spans="3:23">
       <c r="C871" s="2"/>
       <c r="D871" s="2"/>
       <c r="E871" s="2"/>
@@ -22297,7 +22293,7 @@
       <c r="V871" s="2"/>
       <c r="W871" s="2"/>
     </row>
-    <row r="872" ht="13.2" spans="3:23">
+    <row r="872" ht="12.75" spans="3:23">
       <c r="C872" s="2"/>
       <c r="D872" s="2"/>
       <c r="E872" s="2"/>
@@ -22320,7 +22316,7 @@
       <c r="V872" s="2"/>
       <c r="W872" s="2"/>
     </row>
-    <row r="873" ht="13.2" spans="3:23">
+    <row r="873" ht="12.75" spans="3:23">
       <c r="C873" s="2"/>
       <c r="D873" s="2"/>
       <c r="E873" s="2"/>
@@ -22343,7 +22339,7 @@
       <c r="V873" s="2"/>
       <c r="W873" s="2"/>
     </row>
-    <row r="874" ht="13.2" spans="3:23">
+    <row r="874" ht="12.75" spans="3:23">
       <c r="C874" s="2"/>
       <c r="D874" s="2"/>
       <c r="E874" s="2"/>
@@ -22366,7 +22362,7 @@
       <c r="V874" s="2"/>
       <c r="W874" s="2"/>
     </row>
-    <row r="875" ht="13.2" spans="3:23">
+    <row r="875" ht="12.75" spans="3:23">
       <c r="C875" s="2"/>
       <c r="D875" s="2"/>
       <c r="E875" s="2"/>
@@ -22389,7 +22385,7 @@
       <c r="V875" s="2"/>
       <c r="W875" s="2"/>
     </row>
-    <row r="876" ht="13.2" spans="3:23">
+    <row r="876" ht="12.75" spans="3:23">
       <c r="C876" s="2"/>
       <c r="D876" s="2"/>
       <c r="E876" s="2"/>
@@ -22412,7 +22408,7 @@
       <c r="V876" s="2"/>
       <c r="W876" s="2"/>
     </row>
-    <row r="877" ht="13.2" spans="3:23">
+    <row r="877" ht="12.75" spans="3:23">
       <c r="C877" s="2"/>
       <c r="D877" s="2"/>
       <c r="E877" s="2"/>
@@ -22435,7 +22431,7 @@
       <c r="V877" s="2"/>
       <c r="W877" s="2"/>
     </row>
-    <row r="878" ht="13.2" spans="3:23">
+    <row r="878" ht="12.75" spans="3:23">
       <c r="C878" s="2"/>
       <c r="D878" s="2"/>
       <c r="E878" s="2"/>
@@ -22458,7 +22454,7 @@
       <c r="V878" s="2"/>
       <c r="W878" s="2"/>
     </row>
-    <row r="879" ht="13.2" spans="3:23">
+    <row r="879" ht="12.75" spans="3:23">
       <c r="C879" s="2"/>
       <c r="D879" s="2"/>
       <c r="E879" s="2"/>
@@ -22481,7 +22477,7 @@
       <c r="V879" s="2"/>
       <c r="W879" s="2"/>
     </row>
-    <row r="880" ht="13.2" spans="3:23">
+    <row r="880" ht="12.75" spans="3:23">
       <c r="C880" s="2"/>
       <c r="D880" s="2"/>
       <c r="E880" s="2"/>
@@ -22504,7 +22500,7 @@
       <c r="V880" s="2"/>
       <c r="W880" s="2"/>
     </row>
-    <row r="881" ht="13.2" spans="3:23">
+    <row r="881" ht="12.75" spans="3:23">
       <c r="C881" s="2"/>
       <c r="D881" s="2"/>
       <c r="E881" s="2"/>
@@ -22527,7 +22523,7 @@
       <c r="V881" s="2"/>
       <c r="W881" s="2"/>
     </row>
-    <row r="882" ht="13.2" spans="3:23">
+    <row r="882" ht="12.75" spans="3:23">
       <c r="C882" s="2"/>
       <c r="D882" s="2"/>
       <c r="E882" s="2"/>
@@ -22550,7 +22546,7 @@
       <c r="V882" s="2"/>
       <c r="W882" s="2"/>
     </row>
-    <row r="883" ht="13.2" spans="3:23">
+    <row r="883" ht="12.75" spans="3:23">
       <c r="C883" s="2"/>
       <c r="D883" s="2"/>
       <c r="E883" s="2"/>
@@ -22573,7 +22569,7 @@
       <c r="V883" s="2"/>
       <c r="W883" s="2"/>
     </row>
-    <row r="884" ht="13.2" spans="3:23">
+    <row r="884" ht="12.75" spans="3:23">
       <c r="C884" s="2"/>
       <c r="D884" s="2"/>
       <c r="E884" s="2"/>
@@ -22596,7 +22592,7 @@
       <c r="V884" s="2"/>
       <c r="W884" s="2"/>
     </row>
-    <row r="885" ht="13.2" spans="3:23">
+    <row r="885" ht="12.75" spans="3:23">
       <c r="C885" s="2"/>
       <c r="D885" s="2"/>
       <c r="E885" s="2"/>
@@ -22619,7 +22615,7 @@
       <c r="V885" s="2"/>
       <c r="W885" s="2"/>
     </row>
-    <row r="886" ht="13.2" spans="3:23">
+    <row r="886" ht="12.75" spans="3:23">
       <c r="C886" s="2"/>
       <c r="D886" s="2"/>
       <c r="E886" s="2"/>
@@ -22642,7 +22638,7 @@
       <c r="V886" s="2"/>
       <c r="W886" s="2"/>
     </row>
-    <row r="887" ht="13.2" spans="3:23">
+    <row r="887" ht="12.75" spans="3:23">
       <c r="C887" s="2"/>
       <c r="D887" s="2"/>
       <c r="E887" s="2"/>
@@ -22665,7 +22661,7 @@
       <c r="V887" s="2"/>
       <c r="W887" s="2"/>
     </row>
-    <row r="888" ht="13.2" spans="3:23">
+    <row r="888" ht="12.75" spans="3:23">
       <c r="C888" s="2"/>
       <c r="D888" s="2"/>
       <c r="E888" s="2"/>
@@ -22688,7 +22684,7 @@
       <c r="V888" s="2"/>
       <c r="W888" s="2"/>
     </row>
-    <row r="889" ht="13.2" spans="3:23">
+    <row r="889" ht="12.75" spans="3:23">
       <c r="C889" s="2"/>
       <c r="D889" s="2"/>
       <c r="E889" s="2"/>
@@ -22711,7 +22707,7 @@
       <c r="V889" s="2"/>
       <c r="W889" s="2"/>
     </row>
-    <row r="890" ht="13.2" spans="3:23">
+    <row r="890" ht="12.75" spans="3:23">
       <c r="C890" s="2"/>
       <c r="D890" s="2"/>
       <c r="E890" s="2"/>
@@ -22734,7 +22730,7 @@
       <c r="V890" s="2"/>
       <c r="W890" s="2"/>
     </row>
-    <row r="891" ht="13.2" spans="3:23">
+    <row r="891" ht="12.75" spans="3:23">
       <c r="C891" s="2"/>
       <c r="D891" s="2"/>
       <c r="E891" s="2"/>
@@ -22757,7 +22753,7 @@
       <c r="V891" s="2"/>
       <c r="W891" s="2"/>
     </row>
-    <row r="892" ht="13.2" spans="3:23">
+    <row r="892" ht="12.75" spans="3:23">
       <c r="C892" s="2"/>
       <c r="D892" s="2"/>
       <c r="E892" s="2"/>
@@ -22780,7 +22776,7 @@
       <c r="V892" s="2"/>
       <c r="W892" s="2"/>
     </row>
-    <row r="893" ht="13.2" spans="3:23">
+    <row r="893" ht="12.75" spans="3:23">
       <c r="C893" s="2"/>
       <c r="D893" s="2"/>
       <c r="E893" s="2"/>
@@ -22803,7 +22799,7 @@
       <c r="V893" s="2"/>
       <c r="W893" s="2"/>
     </row>
-    <row r="894" ht="13.2" spans="3:23">
+    <row r="894" ht="12.75" spans="3:23">
       <c r="C894" s="2"/>
       <c r="D894" s="2"/>
       <c r="E894" s="2"/>
@@ -22826,7 +22822,7 @@
       <c r="V894" s="2"/>
       <c r="W894" s="2"/>
     </row>
-    <row r="895" ht="13.2" spans="3:23">
+    <row r="895" ht="12.75" spans="3:23">
       <c r="C895" s="2"/>
       <c r="D895" s="2"/>
       <c r="E895" s="2"/>
@@ -22849,7 +22845,7 @@
       <c r="V895" s="2"/>
       <c r="W895" s="2"/>
     </row>
-    <row r="896" ht="13.2" spans="3:23">
+    <row r="896" ht="12.75" spans="3:23">
       <c r="C896" s="2"/>
       <c r="D896" s="2"/>
       <c r="E896" s="2"/>
@@ -22872,7 +22868,7 @@
       <c r="V896" s="2"/>
       <c r="W896" s="2"/>
     </row>
-    <row r="897" ht="13.2" spans="3:23">
+    <row r="897" ht="12.75" spans="3:23">
       <c r="C897" s="2"/>
       <c r="D897" s="2"/>
       <c r="E897" s="2"/>
@@ -22895,7 +22891,7 @@
       <c r="V897" s="2"/>
       <c r="W897" s="2"/>
     </row>
-    <row r="898" ht="13.2" spans="3:23">
+    <row r="898" ht="12.75" spans="3:23">
       <c r="C898" s="2"/>
       <c r="D898" s="2"/>
       <c r="E898" s="2"/>
@@ -22918,7 +22914,7 @@
       <c r="V898" s="2"/>
       <c r="W898" s="2"/>
     </row>
-    <row r="899" ht="13.2" spans="3:23">
+    <row r="899" ht="12.75" spans="3:23">
       <c r="C899" s="2"/>
       <c r="D899" s="2"/>
       <c r="E899" s="2"/>
@@ -22941,7 +22937,7 @@
       <c r="V899" s="2"/>
       <c r="W899" s="2"/>
     </row>
-    <row r="900" ht="13.2" spans="3:23">
+    <row r="900" ht="12.75" spans="3:23">
       <c r="C900" s="2"/>
       <c r="D900" s="2"/>
       <c r="E900" s="2"/>
@@ -22964,7 +22960,7 @@
       <c r="V900" s="2"/>
       <c r="W900" s="2"/>
     </row>
-    <row r="901" ht="13.2" spans="3:23">
+    <row r="901" ht="12.75" spans="3:23">
       <c r="C901" s="2"/>
       <c r="D901" s="2"/>
       <c r="E901" s="2"/>
@@ -22987,7 +22983,7 @@
       <c r="V901" s="2"/>
       <c r="W901" s="2"/>
     </row>
-    <row r="902" ht="13.2" spans="3:23">
+    <row r="902" ht="12.75" spans="3:23">
       <c r="C902" s="2"/>
       <c r="D902" s="2"/>
       <c r="E902" s="2"/>
@@ -23010,7 +23006,7 @@
       <c r="V902" s="2"/>
       <c r="W902" s="2"/>
     </row>
-    <row r="903" ht="13.2" spans="3:23">
+    <row r="903" ht="12.75" spans="3:23">
       <c r="C903" s="2"/>
       <c r="D903" s="2"/>
       <c r="E903" s="2"/>
@@ -23033,7 +23029,7 @@
       <c r="V903" s="2"/>
       <c r="W903" s="2"/>
     </row>
-    <row r="904" ht="13.2" spans="3:23">
+    <row r="904" ht="12.75" spans="3:23">
       <c r="C904" s="2"/>
       <c r="D904" s="2"/>
       <c r="E904" s="2"/>
@@ -23056,7 +23052,7 @@
       <c r="V904" s="2"/>
       <c r="W904" s="2"/>
     </row>
-    <row r="905" ht="13.2" spans="3:23">
+    <row r="905" ht="12.75" spans="3:23">
       <c r="C905" s="2"/>
       <c r="D905" s="2"/>
       <c r="E905" s="2"/>
@@ -23079,7 +23075,7 @@
       <c r="V905" s="2"/>
       <c r="W905" s="2"/>
     </row>
-    <row r="906" ht="13.2" spans="3:23">
+    <row r="906" ht="12.75" spans="3:23">
       <c r="C906" s="2"/>
       <c r="D906" s="2"/>
       <c r="E906" s="2"/>
@@ -23102,7 +23098,7 @@
       <c r="V906" s="2"/>
       <c r="W906" s="2"/>
     </row>
-    <row r="907" ht="13.2" spans="3:23">
+    <row r="907" ht="12.75" spans="3:23">
       <c r="C907" s="2"/>
       <c r="D907" s="2"/>
       <c r="E907" s="2"/>
@@ -23125,7 +23121,7 @@
       <c r="V907" s="2"/>
       <c r="W907" s="2"/>
     </row>
-    <row r="908" ht="13.2" spans="3:23">
+    <row r="908" ht="12.75" spans="3:23">
       <c r="C908" s="2"/>
       <c r="D908" s="2"/>
       <c r="E908" s="2"/>
@@ -23148,7 +23144,7 @@
       <c r="V908" s="2"/>
       <c r="W908" s="2"/>
     </row>
-    <row r="909" ht="13.2" spans="3:23">
+    <row r="909" ht="12.75" spans="3:23">
       <c r="C909" s="2"/>
       <c r="D909" s="2"/>
       <c r="E909" s="2"/>
@@ -23171,7 +23167,7 @@
       <c r="V909" s="2"/>
       <c r="W909" s="2"/>
     </row>
-    <row r="910" ht="13.2" spans="3:23">
+    <row r="910" ht="12.75" spans="3:23">
       <c r="C910" s="2"/>
       <c r="D910" s="2"/>
       <c r="E910" s="2"/>
@@ -23194,7 +23190,7 @@
       <c r="V910" s="2"/>
       <c r="W910" s="2"/>
     </row>
-    <row r="911" ht="13.2" spans="3:23">
+    <row r="911" ht="12.75" spans="3:23">
       <c r="C911" s="2"/>
       <c r="D911" s="2"/>
       <c r="E911" s="2"/>
@@ -23217,7 +23213,7 @@
       <c r="V911" s="2"/>
       <c r="W911" s="2"/>
     </row>
-    <row r="912" ht="13.2" spans="3:23">
+    <row r="912" ht="12.75" spans="3:23">
       <c r="C912" s="2"/>
       <c r="D912" s="2"/>
       <c r="E912" s="2"/>
@@ -23240,7 +23236,7 @@
       <c r="V912" s="2"/>
       <c r="W912" s="2"/>
     </row>
-    <row r="913" ht="13.2" spans="3:23">
+    <row r="913" ht="12.75" spans="3:23">
       <c r="C913" s="2"/>
       <c r="D913" s="2"/>
       <c r="E913" s="2"/>
@@ -23263,7 +23259,7 @@
       <c r="V913" s="2"/>
       <c r="W913" s="2"/>
     </row>
-    <row r="914" ht="13.2" spans="3:23">
+    <row r="914" ht="12.75" spans="3:23">
       <c r="C914" s="2"/>
       <c r="D914" s="2"/>
       <c r="E914" s="2"/>
@@ -23286,7 +23282,7 @@
       <c r="V914" s="2"/>
       <c r="W914" s="2"/>
     </row>
-    <row r="915" ht="13.2" spans="3:23">
+    <row r="915" ht="12.75" spans="3:23">
       <c r="C915" s="2"/>
       <c r="D915" s="2"/>
       <c r="E915" s="2"/>
@@ -23309,7 +23305,7 @@
       <c r="V915" s="2"/>
       <c r="W915" s="2"/>
     </row>
-    <row r="916" ht="13.2" spans="3:23">
+    <row r="916" ht="12.75" spans="3:23">
       <c r="C916" s="2"/>
       <c r="D916" s="2"/>
       <c r="E916" s="2"/>
@@ -23332,7 +23328,7 @@
       <c r="V916" s="2"/>
       <c r="W916" s="2"/>
     </row>
-    <row r="917" ht="13.2" spans="3:23">
+    <row r="917" ht="12.75" spans="3:23">
       <c r="C917" s="2"/>
       <c r="D917" s="2"/>
       <c r="E917" s="2"/>
@@ -23355,7 +23351,7 @@
       <c r="V917" s="2"/>
       <c r="W917" s="2"/>
     </row>
-    <row r="918" ht="13.2" spans="3:23">
+    <row r="918" ht="12.75" spans="3:23">
       <c r="C918" s="2"/>
       <c r="D918" s="2"/>
       <c r="E918" s="2"/>
@@ -23378,7 +23374,7 @@
       <c r="V918" s="2"/>
       <c r="W918" s="2"/>
     </row>
-    <row r="919" ht="13.2" spans="3:23">
+    <row r="919" ht="12.75" spans="3:23">
       <c r="C919" s="2"/>
       <c r="D919" s="2"/>
       <c r="E919" s="2"/>
@@ -23401,7 +23397,7 @@
       <c r="V919" s="2"/>
       <c r="W919" s="2"/>
     </row>
-    <row r="920" ht="13.2" spans="3:23">
+    <row r="920" ht="12.75" spans="3:23">
       <c r="C920" s="2"/>
       <c r="D920" s="2"/>
       <c r="E920" s="2"/>
@@ -23424,7 +23420,7 @@
       <c r="V920" s="2"/>
       <c r="W920" s="2"/>
     </row>
-    <row r="921" ht="13.2" spans="3:23">
+    <row r="921" ht="12.75" spans="3:23">
       <c r="C921" s="2"/>
       <c r="D921" s="2"/>
       <c r="E921" s="2"/>
@@ -23447,7 +23443,7 @@
       <c r="V921" s="2"/>
       <c r="W921" s="2"/>
     </row>
-    <row r="922" ht="13.2" spans="3:23">
+    <row r="922" ht="12.75" spans="3:23">
       <c r="C922" s="2"/>
       <c r="D922" s="2"/>
       <c r="E922" s="2"/>
@@ -23470,7 +23466,7 @@
       <c r="V922" s="2"/>
       <c r="W922" s="2"/>
     </row>
-    <row r="923" ht="13.2" spans="3:23">
+    <row r="923" ht="12.75" spans="3:23">
       <c r="C923" s="2"/>
       <c r="D923" s="2"/>
       <c r="E923" s="2"/>
@@ -23493,7 +23489,7 @@
       <c r="V923" s="2"/>
       <c r="W923" s="2"/>
     </row>
-    <row r="924" ht="13.2" spans="3:23">
+    <row r="924" ht="12.75" spans="3:23">
       <c r="C924" s="2"/>
       <c r="D924" s="2"/>
       <c r="E924" s="2"/>
@@ -23516,7 +23512,7 @@
       <c r="V924" s="2"/>
       <c r="W924" s="2"/>
     </row>
-    <row r="925" ht="13.2" spans="3:23">
+    <row r="925" ht="12.75" spans="3:23">
       <c r="C925" s="2"/>
       <c r="D925" s="2"/>
       <c r="E925" s="2"/>
@@ -23539,7 +23535,7 @@
       <c r="V925" s="2"/>
       <c r="W925" s="2"/>
     </row>
-    <row r="926" ht="13.2" spans="3:23">
+    <row r="926" ht="12.75" spans="3:23">
       <c r="C926" s="2"/>
       <c r="D926" s="2"/>
       <c r="E926" s="2"/>
@@ -23562,7 +23558,7 @@
       <c r="V926" s="2"/>
       <c r="W926" s="2"/>
     </row>
-    <row r="927" ht="13.2" spans="3:23">
+    <row r="927" ht="12.75" spans="3:23">
       <c r="C927" s="2"/>
       <c r="D927" s="2"/>
       <c r="E927" s="2"/>
@@ -23585,7 +23581,7 @@
       <c r="V927" s="2"/>
       <c r="W927" s="2"/>
     </row>
-    <row r="928" ht="13.2" spans="3:23">
+    <row r="928" ht="12.75" spans="3:23">
       <c r="C928" s="2"/>
       <c r="D928" s="2"/>
       <c r="E928" s="2"/>
@@ -23608,7 +23604,7 @@
       <c r="V928" s="2"/>
       <c r="W928" s="2"/>
     </row>
-    <row r="929" ht="13.2" spans="3:23">
+    <row r="929" ht="12.75" spans="3:23">
       <c r="C929" s="2"/>
       <c r="D929" s="2"/>
       <c r="E929" s="2"/>
@@ -23631,7 +23627,7 @@
       <c r="V929" s="2"/>
       <c r="W929" s="2"/>
     </row>
-    <row r="930" ht="13.2" spans="3:23">
+    <row r="930" ht="12.75" spans="3:23">
       <c r="C930" s="2"/>
       <c r="D930" s="2"/>
       <c r="E930" s="2"/>
@@ -23654,7 +23650,7 @@
       <c r="V930" s="2"/>
       <c r="W930" s="2"/>
     </row>
-    <row r="931" ht="13.2" spans="3:23">
+    <row r="931" ht="12.75" spans="3:23">
       <c r="C931" s="2"/>
       <c r="D931" s="2"/>
       <c r="E931" s="2"/>
@@ -23677,7 +23673,7 @@
       <c r="V931" s="2"/>
       <c r="W931" s="2"/>
     </row>
-    <row r="932" ht="13.2" spans="3:23">
+    <row r="932" ht="12.75" spans="3:23">
       <c r="C932" s="2"/>
       <c r="D932" s="2"/>
       <c r="E932" s="2"/>
@@ -23700,7 +23696,7 @@
       <c r="V932" s="2"/>
       <c r="W932" s="2"/>
     </row>
-    <row r="933" ht="13.2" spans="3:23">
+    <row r="933" ht="12.75" spans="3:23">
       <c r="C933" s="2"/>
       <c r="D933" s="2"/>
       <c r="E933" s="2"/>
@@ -23723,7 +23719,7 @@
       <c r="V933" s="2"/>
       <c r="W933" s="2"/>
     </row>
-    <row r="934" ht="13.2" spans="3:23">
+    <row r="934" ht="12.75" spans="3:23">
       <c r="C934" s="2"/>
       <c r="D934" s="2"/>
       <c r="E934" s="2"/>
@@ -23746,7 +23742,7 @@
       <c r="V934" s="2"/>
       <c r="W934" s="2"/>
     </row>
-    <row r="935" ht="13.2" spans="3:23">
+    <row r="935" ht="12.75" spans="3:23">
       <c r="C935" s="2"/>
       <c r="D935" s="2"/>
       <c r="E935" s="2"/>
@@ -23769,7 +23765,7 @@
       <c r="V935" s="2"/>
       <c r="W935" s="2"/>
     </row>
-    <row r="936" ht="13.2" spans="3:23">
+    <row r="936" ht="12.75" spans="3:23">
       <c r="C936" s="2"/>
       <c r="D936" s="2"/>
       <c r="E936" s="2"/>
@@ -23792,7 +23788,7 @@
       <c r="V936" s="2"/>
       <c r="W936" s="2"/>
     </row>
-    <row r="937" ht="13.2" spans="3:23">
+    <row r="937" ht="12.75" spans="3:23">
       <c r="C937" s="2"/>
       <c r="D937" s="2"/>
       <c r="E937" s="2"/>
@@ -23815,7 +23811,7 @@
       <c r="V937" s="2"/>
       <c r="W937" s="2"/>
     </row>
-    <row r="938" ht="13.2" spans="3:23">
+    <row r="938" ht="12.75" spans="3:23">
       <c r="C938" s="2"/>
       <c r="D938" s="2"/>
       <c r="E938" s="2"/>
@@ -23838,7 +23834,7 @@
       <c r="V938" s="2"/>
       <c r="W938" s="2"/>
     </row>
-    <row r="939" ht="13.2" spans="3:23">
+    <row r="939" ht="12.75" spans="3:23">
       <c r="C939" s="2"/>
       <c r="D939" s="2"/>
       <c r="E939" s="2"/>
@@ -23861,7 +23857,7 @@
       <c r="V939" s="2"/>
       <c r="W939" s="2"/>
     </row>
-    <row r="940" ht="13.2" spans="3:23">
+    <row r="940" ht="12.75" spans="3:23">
       <c r="C940" s="2"/>
       <c r="D940" s="2"/>
       <c r="E940" s="2"/>
@@ -23884,7 +23880,7 @@
       <c r="V940" s="2"/>
       <c r="W940" s="2"/>
     </row>
-    <row r="941" ht="13.2" spans="3:23">
+    <row r="941" ht="12.75" spans="3:23">
       <c r="C941" s="2"/>
       <c r="D941" s="2"/>
       <c r="E941" s="2"/>
@@ -23907,7 +23903,7 @@
       <c r="V941" s="2"/>
       <c r="W941" s="2"/>
     </row>
-    <row r="942" ht="13.2" spans="3:23">
+    <row r="942" ht="12.75" spans="3:23">
       <c r="C942" s="2"/>
       <c r="D942" s="2"/>
       <c r="E942" s="2"/>
@@ -23930,7 +23926,7 @@
       <c r="V942" s="2"/>
       <c r="W942" s="2"/>
     </row>
-    <row r="943" ht="13.2" spans="3:23">
+    <row r="943" ht="12.75" spans="3:23">
       <c r="C943" s="2"/>
       <c r="D943" s="2"/>
       <c r="E943" s="2"/>
@@ -23953,7 +23949,7 @@
       <c r="V943" s="2"/>
       <c r="W943" s="2"/>
     </row>
-    <row r="944" ht="13.2" spans="3:23">
+    <row r="944" ht="12.75" spans="3:23">
       <c r="C944" s="2"/>
       <c r="D944" s="2"/>
       <c r="E944" s="2"/>
@@ -23976,7 +23972,7 @@
       <c r="V944" s="2"/>
       <c r="W944" s="2"/>
     </row>
-    <row r="945" ht="13.2" spans="3:23">
+    <row r="945" ht="12.75" spans="3:23">
       <c r="C945" s="2"/>
       <c r="D945" s="2"/>
       <c r="E945" s="2"/>
@@ -23999,7 +23995,7 @@
       <c r="V945" s="2"/>
       <c r="W945" s="2"/>
     </row>
-    <row r="946" ht="13.2" spans="3:23">
+    <row r="946" ht="12.75" spans="3:23">
       <c r="C946" s="2"/>
       <c r="D946" s="2"/>
       <c r="E946" s="2"/>
@@ -24022,7 +24018,7 @@
       <c r="V946" s="2"/>
       <c r="W946" s="2"/>
     </row>
-    <row r="947" ht="13.2" spans="3:23">
+    <row r="947" ht="12.75" spans="3:23">
       <c r="C947" s="2"/>
       <c r="D947" s="2"/>
       <c r="E947" s="2"/>
@@ -24045,7 +24041,7 @@
       <c r="V947" s="2"/>
       <c r="W947" s="2"/>
     </row>
-    <row r="948" ht="13.2" spans="3:23">
+    <row r="948" ht="12.75" spans="3:23">
       <c r="C948" s="2"/>
       <c r="D948" s="2"/>
       <c r="E948" s="2"/>
@@ -24068,7 +24064,7 @@
       <c r="V948" s="2"/>
       <c r="W948" s="2"/>
     </row>
-    <row r="949" ht="13.2" spans="3:23">
+    <row r="949" ht="12.75" spans="3:23">
       <c r="C949" s="2"/>
       <c r="D949" s="2"/>
       <c r="E949" s="2"/>
@@ -24091,7 +24087,7 @@
       <c r="V949" s="2"/>
       <c r="W949" s="2"/>
     </row>
-    <row r="950" ht="13.2" spans="3:23">
+    <row r="950" ht="12.75" spans="3:23">
       <c r="C950" s="2"/>
       <c r="D950" s="2"/>
       <c r="E950" s="2"/>
@@ -24114,7 +24110,7 @@
       <c r="V950" s="2"/>
       <c r="W950" s="2"/>
     </row>
-    <row r="951" ht="13.2" spans="3:23">
+    <row r="951" ht="12.75" spans="3:23">
       <c r="C951" s="2"/>
       <c r="D951" s="2"/>
       <c r="E951" s="2"/>
@@ -24137,7 +24133,7 @@
       <c r="V951" s="2"/>
       <c r="W951" s="2"/>
     </row>
-    <row r="952" ht="13.2" spans="3:23">
+    <row r="952" ht="12.75" spans="3:23">
       <c r="C952" s="2"/>
       <c r="D952" s="2"/>
       <c r="E952" s="2"/>
@@ -24160,7 +24156,7 @@
       <c r="V952" s="2"/>
       <c r="W952" s="2"/>
     </row>
-    <row r="953" ht="13.2" spans="3:23">
+    <row r="953" ht="12.75" spans="3:23">
       <c r="C953" s="2"/>
       <c r="D953" s="2"/>
       <c r="E953" s="2"/>
@@ -24183,7 +24179,7 @@
       <c r="V953" s="2"/>
       <c r="W953" s="2"/>
     </row>
-    <row r="954" ht="13.2" spans="3:23">
+    <row r="954" ht="12.75" spans="3:23">
       <c r="C954" s="2"/>
       <c r="D954" s="2"/>
       <c r="E954" s="2"/>
@@ -24206,7 +24202,7 @@
       <c r="V954" s="2"/>
       <c r="W954" s="2"/>
     </row>
-    <row r="955" ht="13.2" spans="3:23">
+    <row r="955" ht="12.75" spans="3:23">
       <c r="C955" s="2"/>
       <c r="D955" s="2"/>
       <c r="E955" s="2"/>
@@ -24229,7 +24225,7 @@
       <c r="V955" s="2"/>
       <c r="W955" s="2"/>
     </row>
-    <row r="956" ht="13.2" spans="3:23">
+    <row r="956" ht="12.75" spans="3:23">
       <c r="C956" s="2"/>
       <c r="D956" s="2"/>
       <c r="E956" s="2"/>
@@ -24252,7 +24248,7 @@
       <c r="V956" s="2"/>
       <c r="W956" s="2"/>
     </row>
-    <row r="957" ht="13.2" spans="3:23">
+    <row r="957" ht="12.75" spans="3:23">
       <c r="C957" s="2"/>
       <c r="D957" s="2"/>
       <c r="E957" s="2"/>
@@ -24275,7 +24271,7 @@
       <c r="V957" s="2"/>
       <c r="W957" s="2"/>
     </row>
-    <row r="958" ht="13.2" spans="3:23">
+    <row r="958" ht="12.75" spans="3:23">
       <c r="C958" s="2"/>
       <c r="D958" s="2"/>
       <c r="E958" s="2"/>
@@ -24298,7 +24294,7 @@
       <c r="V958" s="2"/>
       <c r="W958" s="2"/>
     </row>
-    <row r="959" ht="13.2" spans="3:23">
+    <row r="959" ht="12.75" spans="3:23">
       <c r="C959" s="2"/>
       <c r="D959" s="2"/>
       <c r="E959" s="2"/>
@@ -24321,7 +24317,7 @@
       <c r="V959" s="2"/>
       <c r="W959" s="2"/>
     </row>
-    <row r="960" ht="13.2" spans="3:23">
+    <row r="960" ht="12.75" spans="3:23">
       <c r="C960" s="2"/>
       <c r="D960" s="2"/>
       <c r="E960" s="2"/>
@@ -24344,7 +24340,7 @@
       <c r="V960" s="2"/>
       <c r="W960" s="2"/>
     </row>
-    <row r="961" ht="13.2" spans="3:23">
+    <row r="961" ht="12.75" spans="3:23">
       <c r="C961" s="2"/>
       <c r="D961" s="2"/>
       <c r="E961" s="2"/>
@@ -24367,7 +24363,7 @@
       <c r="V961" s="2"/>
       <c r="W961" s="2"/>
     </row>
-    <row r="962" ht="13.2" spans="3:23">
+    <row r="962" ht="12.75" spans="3:23">
       <c r="C962" s="2"/>
       <c r="D962" s="2"/>
       <c r="E962" s="2"/>
@@ -24390,7 +24386,7 @@
       <c r="V962" s="2"/>
       <c r="W962" s="2"/>
     </row>
-    <row r="963" ht="13.2" spans="3:23">
+    <row r="963" ht="12.75" spans="3:23">
       <c r="C963" s="2"/>
       <c r="D963" s="2"/>
       <c r="E963" s="2"/>
@@ -24413,7 +24409,7 @@
       <c r="V963" s="2"/>
       <c r="W963" s="2"/>
     </row>
-    <row r="964" ht="13.2" spans="3:23">
+    <row r="964" ht="12.75" spans="3:23">
       <c r="C964" s="2"/>
       <c r="D964" s="2"/>
       <c r="E964" s="2"/>
@@ -24436,7 +24432,7 @@
       <c r="V964" s="2"/>
       <c r="W964" s="2"/>
     </row>
-    <row r="965" ht="13.2" spans="3:23">
+    <row r="965" ht="12.75" spans="3:23">
       <c r="C965" s="2"/>
       <c r="D965" s="2"/>
       <c r="E965" s="2"/>
@@ -24459,7 +24455,7 @@
       <c r="V965" s="2"/>
       <c r="W965" s="2"/>
     </row>
-    <row r="966" ht="13.2" spans="3:23">
+    <row r="966" ht="12.75" spans="3:23">
       <c r="C966" s="2"/>
       <c r="D966" s="2"/>
       <c r="E966" s="2"/>
@@ -24482,7 +24478,7 @@
       <c r="V966" s="2"/>
       <c r="W966" s="2"/>
     </row>
-    <row r="967" ht="13.2" spans="3:23">
+    <row r="967" ht="12.75" spans="3:23">
       <c r="C967" s="2"/>
       <c r="D967" s="2"/>
       <c r="E967" s="2"/>
@@ -24505,7 +24501,7 @@
       <c r="V967" s="2"/>
       <c r="W967" s="2"/>
     </row>
-    <row r="968" ht="13.2" spans="3:23">
+    <row r="968" ht="12.75" spans="3:23">
       <c r="C968" s="2"/>
       <c r="D968" s="2"/>
       <c r="E968" s="2"/>
@@ -24528,7 +24524,7 @@
       <c r="V968" s="2"/>
       <c r="W968" s="2"/>
     </row>
-    <row r="969" ht="13.2" spans="3:23">
+    <row r="969" ht="12.75" spans="3:23">
       <c r="C969" s="2"/>
       <c r="D969" s="2"/>
       <c r="E969" s="2"/>
@@ -24551,7 +24547,7 @@
       <c r="V969" s="2"/>
       <c r="W969" s="2"/>
     </row>
-    <row r="970" ht="13.2" spans="3:23">
+    <row r="970" ht="12.75" spans="3:23">
       <c r="C970" s="2"/>
       <c r="D970" s="2"/>
       <c r="E970" s="2"/>
@@ -24574,7 +24570,7 @@
       <c r="V970" s="2"/>
       <c r="W970" s="2"/>
     </row>
-    <row r="971" ht="13.2" spans="3:23">
+    <row r="971" ht="12.75" spans="3:23">
       <c r="C971" s="2"/>
       <c r="D971" s="2"/>
       <c r="E971" s="2"/>
@@ -24597,7 +24593,7 @@
       <c r="V971" s="2"/>
       <c r="W971" s="2"/>
     </row>
-    <row r="972" ht="13.2" spans="3:23">
+    <row r="972" ht="12.75" spans="3:23">
       <c r="C972" s="2"/>
       <c r="D972" s="2"/>
       <c r="E972" s="2"/>
@@ -24620,7 +24616,7 @@
       <c r="V972" s="2"/>
       <c r="W972" s="2"/>
     </row>
-    <row r="973" ht="13.2" spans="3:23">
+    <row r="973" ht="12.75" spans="3:23">
       <c r="C973" s="2"/>
       <c r="D973" s="2"/>
       <c r="E973" s="2"/>
@@ -24643,7 +24639,7 @@
       <c r="V973" s="2"/>
       <c r="W973" s="2"/>
     </row>
-    <row r="974" ht="13.2" spans="3:23">
+    <row r="974" ht="12.75" spans="3:23">
       <c r="C974" s="2"/>
       <c r="D974" s="2"/>
       <c r="E974" s="2"/>
@@ -24666,7 +24662,7 @@
       <c r="V974" s="2"/>
       <c r="W974" s="2"/>
     </row>
-    <row r="975" ht="13.2" spans="3:23">
+    <row r="975" ht="12.75" spans="3:23">
       <c r="C975" s="2"/>
       <c r="D975" s="2"/>
       <c r="E975" s="2"/>
@@ -24689,7 +24685,7 @@
       <c r="V975" s="2"/>
       <c r="W975" s="2"/>
     </row>
-    <row r="976" ht="13.2" spans="3:23">
+    <row r="976" ht="12.75" spans="3:23">
       <c r="C976" s="2"/>
       <c r="D976" s="2"/>
       <c r="E976" s="2"/>
@@ -24712,7 +24708,7 @@
       <c r="V976" s="2"/>
       <c r="W976" s="2"/>
     </row>
-    <row r="977" ht="13.2" spans="3:23">
+    <row r="977" ht="12.75" spans="3:23">
       <c r="C977" s="2"/>
       <c r="D977" s="2"/>
       <c r="E977" s="2"/>
@@ -24735,7 +24731,7 @@
       <c r="V977" s="2"/>
       <c r="W977" s="2"/>
     </row>
-    <row r="978" ht="13.2" spans="3:23">
+    <row r="978" ht="12.75" spans="3:23">
       <c r="C978" s="2"/>
       <c r="D978" s="2"/>
       <c r="E978" s="2"/>
@@ -24758,7 +24754,7 @@
       <c r="V978" s="2"/>
       <c r="W978" s="2"/>
     </row>
-    <row r="979" ht="13.2" spans="3:23">
+    <row r="979" ht="12.75" spans="3:23">
       <c r="C979" s="2"/>
       <c r="D979" s="2"/>
       <c r="E979" s="2"/>
@@ -24781,7 +24777,7 @@
       <c r="V979" s="2"/>
       <c r="W979" s="2"/>
     </row>
-    <row r="980" ht="13.2" spans="3:23">
+    <row r="980" ht="12.75" spans="3:23">
       <c r="C980" s="2"/>
       <c r="D980" s="2"/>
       <c r="E980" s="2"/>
@@ -24804,7 +24800,7 @@
       <c r="V980" s="2"/>
       <c r="W980" s="2"/>
     </row>
-    <row r="981" ht="13.2" spans="3:23">
+    <row r="981" ht="12.75" spans="3:23">
       <c r="C981" s="2"/>
       <c r="D981" s="2"/>
       <c r="E981" s="2"/>
@@ -24827,7 +24823,7 @@
       <c r="V981" s="2"/>
       <c r="W981" s="2"/>
     </row>
-    <row r="982" ht="13.2" spans="3:23">
+    <row r="982" ht="12.75" spans="3:23">
       <c r="C982" s="2"/>
       <c r="D982" s="2"/>
       <c r="E982" s="2"/>
@@ -24850,7 +24846,7 @@
       <c r="V982" s="2"/>
       <c r="W982" s="2"/>
     </row>
-    <row r="983" ht="13.2" spans="3:23">
+    <row r="983" ht="12.75" spans="3:23">
       <c r="C983" s="2"/>
       <c r="D983" s="2"/>
       <c r="E983" s="2"/>
@@ -24873,7 +24869,7 @@
       <c r="V983" s="2"/>
       <c r="W983" s="2"/>
     </row>
-    <row r="984" ht="13.2" spans="3:23">
+    <row r="984" ht="12.75" spans="3:23">
       <c r="C984" s="2"/>
       <c r="D984" s="2"/>
       <c r="E984" s="2"/>
@@ -24896,7 +24892,7 @@
       <c r="V984" s="2"/>
       <c r="W984" s="2"/>
     </row>
-    <row r="985" ht="13.2" spans="3:23">
+    <row r="985" ht="12.75" spans="3:23">
       <c r="C985" s="2"/>
       <c r="D985" s="2"/>
       <c r="E985" s="2"/>
@@ -24919,7 +24915,7 @@
       <c r="V985" s="2"/>
       <c r="W985" s="2"/>
     </row>
-    <row r="986" ht="13.2" spans="3:23">
+    <row r="986" ht="12.75" spans="3:23">
       <c r="C986" s="2"/>
       <c r="D986" s="2"/>
       <c r="E986" s="2"/>
@@ -24942,7 +24938,7 @@
       <c r="V986" s="2"/>
       <c r="W986" s="2"/>
     </row>
-    <row r="987" ht="13.2" spans="3:23">
+    <row r="987" ht="12.75" spans="3:23">
       <c r="C987" s="2"/>
       <c r="D987" s="2"/>
       <c r="E987" s="2"/>
@@ -24965,7 +24961,7 @@
       <c r="V987" s="2"/>
       <c r="W987" s="2"/>
     </row>
-    <row r="988" ht="13.2" spans="3:23">
+    <row r="988" ht="12.75" spans="3:23">
       <c r="C988" s="2"/>
       <c r="D988" s="2"/>
       <c r="E988" s="2"/>
@@ -24988,7 +24984,7 @@
       <c r="V988" s="2"/>
       <c r="W988" s="2"/>
     </row>
-    <row r="989" ht="13.2" spans="3:23">
+    <row r="989" ht="12.75" spans="3:23">
       <c r="C989" s="2"/>
       <c r="D989" s="2"/>
       <c r="E989" s="2"/>
@@ -25011,7 +25007,7 @@
       <c r="V989" s="2"/>
       <c r="W989" s="2"/>
     </row>
-    <row r="990" ht="13.2" spans="3:23">
+    <row r="990" ht="12.75" spans="3:23">
       <c r="C990" s="2"/>
       <c r="D990" s="2"/>
       <c r="E990" s="2"/>
@@ -25034,7 +25030,7 @@
       <c r="V990" s="2"/>
       <c r="W990" s="2"/>
     </row>
-    <row r="991" ht="13.2" spans="3:23">
+    <row r="991" ht="12.75" spans="3:23">
       <c r="C991" s="2"/>
       <c r="D991" s="2"/>
       <c r="E991" s="2"/>
@@ -25057,7 +25053,7 @@
       <c r="V991" s="2"/>
       <c r="W991" s="2"/>
     </row>
-    <row r="992" ht="13.2" spans="3:23">
+    <row r="992" ht="12.75" spans="3:23">
       <c r="C992" s="2"/>
       <c r="D992" s="2"/>
       <c r="E992" s="2"/>
@@ -25080,7 +25076,7 @@
       <c r="V992" s="2"/>
       <c r="W992" s="2"/>
     </row>
-    <row r="993" ht="13.2" spans="3:23">
+    <row r="993" ht="12.75" spans="3:23">
       <c r="C993" s="2"/>
       <c r="D993" s="2"/>
       <c r="E993" s="2"/>
@@ -25103,7 +25099,7 @@
       <c r="V993" s="2"/>
       <c r="W993" s="2"/>
     </row>
-    <row r="994" ht="13.2" spans="3:23">
+    <row r="994" ht="12.75" spans="3:23">
       <c r="C994" s="2"/>
       <c r="D994" s="2"/>
       <c r="E994" s="2"/>
@@ -25126,7 +25122,7 @@
       <c r="V994" s="2"/>
       <c r="W994" s="2"/>
     </row>
-    <row r="995" ht="13.2" spans="3:23">
+    <row r="995" ht="12.75" spans="3:23">
       <c r="C995" s="2"/>
       <c r="D995" s="2"/>
       <c r="E995" s="2"/>

--- a/オーギヤ半田島図.xlsx
+++ b/オーギヤ半田島図.xlsx
@@ -37,14 +37,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -54,6 +46,13 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -82,16 +81,47 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -113,22 +143,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -142,14 +157,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
@@ -159,22 +166,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -182,7 +182,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -197,13 +197,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -221,19 +233,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -251,19 +257,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -275,13 +275,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -293,7 +323,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -305,13 +347,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -323,61 +377,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -424,6 +424,15 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
@@ -432,8 +441,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -454,6 +465,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -468,171 +488,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1027,7 +1027,7 @@
       <c r="V3" s="2"/>
       <c r="W3" s="2"/>
     </row>
-    <row r="4" ht="12.75" spans="1:23">
+    <row r="4" spans="1:23">
       <c r="A4" s="2">
         <v>1114</v>
       </c>
@@ -1085,61 +1085,67 @@
       <c r="V4" s="2"/>
       <c r="W4" s="2"/>
     </row>
-    <row r="5" ht="12.75" spans="1:23">
+    <row r="5" spans="1:23">
       <c r="A5" s="2">
         <v>1115</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
+      <c r="E5" s="2">
+        <v>1170</v>
+      </c>
       <c r="F5" s="2">
+        <v>1169</v>
+      </c>
+      <c r="G5" s="2">
         <v>1168</v>
       </c>
-      <c r="G5" s="2">
+      <c r="H5" s="2">
         <v>1167</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="2">
         <v>1166</v>
       </c>
-      <c r="I5" s="2">
+      <c r="J5" s="2">
         <v>1165</v>
       </c>
-      <c r="J5" s="2">
+      <c r="K5" s="2">
         <v>1164</v>
       </c>
-      <c r="K5" s="2">
+      <c r="L5" s="2">
         <v>1163</v>
       </c>
-      <c r="L5" s="2">
+      <c r="M5" s="2">
         <v>1162</v>
       </c>
-      <c r="M5" s="2">
+      <c r="N5" s="2">
         <v>1161</v>
       </c>
-      <c r="N5" s="2">
+      <c r="O5" s="2">
         <v>1160</v>
       </c>
-      <c r="O5" s="2">
+      <c r="P5" s="2">
         <v>1159</v>
       </c>
-      <c r="P5" s="2">
+      <c r="Q5" s="2">
         <v>1158</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="R5" s="2">
         <v>1157</v>
       </c>
-      <c r="R5" s="2">
+      <c r="S5" s="2">
         <v>1156</v>
       </c>
-      <c r="S5" s="2">
+      <c r="T5" s="2">
         <v>1155</v>
       </c>
-      <c r="T5" s="2">
+      <c r="U5" s="2">
         <v>1154</v>
       </c>
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
     </row>
-    <row r="6" ht="12.75" spans="1:23">
+    <row r="6" spans="1:23">
       <c r="A6" s="2">
         <v>1116</v>
       </c>
@@ -1164,56 +1170,50 @@
       <c r="V6" s="2"/>
       <c r="W6" s="2"/>
     </row>
-    <row r="7" ht="12.75" spans="1:30">
+    <row r="7" spans="1:30">
       <c r="A7" s="2">
         <v>1117</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
-      <c r="F7" s="2">
-        <v>1169</v>
-      </c>
       <c r="G7" s="2">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H7" s="2">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="I7" s="2">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="J7" s="2">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="K7" s="2">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="L7" s="2">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="M7" s="2">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="N7" s="2">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="O7" s="2">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="P7" s="2">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="Q7" s="2">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="R7" s="2">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="S7" s="2">
-        <v>1182</v>
-      </c>
-      <c r="T7" s="2">
         <v>1183</v>
       </c>
       <c r="V7" s="2"/>
@@ -1225,7 +1225,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="8" ht="12.75" spans="1:30">
+    <row r="8" spans="1:30">
       <c r="A8" s="2">
         <v>1118</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="39" spans="1:33">
+    <row r="39" ht="12.75" spans="1:33">
       <c r="A39" s="2">
         <v>778</v>
       </c>

--- a/オーギヤ半田島図.xlsx
+++ b/オーギヤ半田島図.xlsx
@@ -16,10 +16,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -44,66 +44,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -121,14 +61,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -136,7 +83,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -144,6 +91,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -157,6 +111,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
@@ -165,10 +134,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="Arial"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -187,6 +156,37 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -197,7 +197,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -215,31 +353,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -251,61 +365,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -317,67 +377,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,46 +406,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -488,13 +453,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -503,136 +503,136 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1027,7 +1027,7 @@
       <c r="V3" s="2"/>
       <c r="W3" s="2"/>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" ht="12.75" spans="1:23">
       <c r="A4" s="2">
         <v>1114</v>
       </c>
@@ -1085,7 +1085,7 @@
       <c r="V4" s="2"/>
       <c r="W4" s="2"/>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" ht="12.75" spans="1:23">
       <c r="A5" s="2">
         <v>1115</v>
       </c>
@@ -1170,7 +1170,7 @@
       <c r="V6" s="2"/>
       <c r="W6" s="2"/>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:23">
       <c r="A7" s="2">
         <v>1117</v>
       </c>
@@ -1218,14 +1218,8 @@
       </c>
       <c r="V7" s="2"/>
       <c r="W7" s="2"/>
-      <c r="AB7" s="2">
-        <v>1059</v>
-      </c>
-      <c r="AD7" s="2">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30">
+    </row>
+    <row r="8" spans="1:23">
       <c r="A8" s="2">
         <v>1118</v>
       </c>
@@ -1273,14 +1267,8 @@
         <v>1218</v>
       </c>
       <c r="W8" s="2"/>
-      <c r="AB8" s="2">
-        <v>1060</v>
-      </c>
-      <c r="AD8" s="2">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="9" ht="12.75" spans="1:30">
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9" s="2">
         <v>1119</v>
       </c>
@@ -1303,14 +1291,8 @@
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
-      <c r="AB9" s="2">
-        <v>1061</v>
-      </c>
-      <c r="AD9" s="2">
-        <v>1056</v>
-      </c>
-    </row>
-    <row r="10" ht="12.75" spans="1:30">
+    </row>
+    <row r="10" spans="1:25">
       <c r="A10" s="2">
         <v>1120</v>
       </c>
@@ -1355,14 +1337,8 @@
       <c r="Y10" s="2">
         <v>1184</v>
       </c>
-      <c r="AB10" s="2">
-        <v>1062</v>
-      </c>
-      <c r="AD10" s="2">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="11" ht="12.75" spans="1:30">
+    </row>
+    <row r="11" spans="1:25">
       <c r="A11" s="2">
         <v>1121</v>
       </c>
@@ -1408,14 +1384,8 @@
       <c r="Y11" s="2">
         <v>1185</v>
       </c>
-      <c r="AB11" s="2">
-        <v>1063</v>
-      </c>
-      <c r="AD11" s="2">
-        <v>1054</v>
-      </c>
-    </row>
-    <row r="12" ht="12.75" spans="1:30">
+    </row>
+    <row r="12" spans="1:25">
       <c r="A12" s="2">
         <v>1122</v>
       </c>
@@ -1449,14 +1419,8 @@
       <c r="Y12" s="2">
         <v>1186</v>
       </c>
-      <c r="AB12" s="2">
-        <v>1064</v>
-      </c>
-      <c r="AD12" s="2">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="13" ht="12.75" spans="1:30">
+    </row>
+    <row r="13" spans="1:25">
       <c r="A13" s="2">
         <v>1123</v>
       </c>
@@ -1502,14 +1466,8 @@
       <c r="Y13" s="2">
         <v>1187</v>
       </c>
-      <c r="AB13" s="2">
-        <v>1065</v>
-      </c>
-      <c r="AD13" s="2">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="14" ht="12.75" spans="1:30">
+    </row>
+    <row r="14" spans="1:27">
       <c r="A14" s="2">
         <v>1124</v>
       </c>
@@ -1557,14 +1515,8 @@
       <c r="AA14" s="2">
         <v>1091</v>
       </c>
-      <c r="AB14" s="2">
-        <v>1066</v>
-      </c>
-      <c r="AD14" s="2">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="15" ht="12.75" spans="1:30">
+    </row>
+    <row r="15" spans="1:27">
       <c r="A15" s="2">
         <v>1125</v>
       </c>
@@ -1599,14 +1551,8 @@
       <c r="AA15" s="2">
         <v>1090</v>
       </c>
-      <c r="AB15" s="2">
-        <v>1067</v>
-      </c>
-      <c r="AD15" s="2">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="16" ht="12.75" spans="1:30">
+    </row>
+    <row r="16" spans="1:27">
       <c r="A16" s="2">
         <v>1126</v>
       </c>
@@ -1647,14 +1593,8 @@
       <c r="AA16" s="2">
         <v>1089</v>
       </c>
-      <c r="AB16" s="2">
-        <v>1068</v>
-      </c>
-      <c r="AD16" s="2">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="17" ht="12.75" spans="1:30">
+    </row>
+    <row r="17" spans="1:27">
       <c r="A17" s="2">
         <v>1127</v>
       </c>
@@ -1698,14 +1638,8 @@
       <c r="AA17" s="2">
         <v>1088</v>
       </c>
-      <c r="AB17" s="2">
-        <v>1069</v>
-      </c>
-      <c r="AD17" s="2">
-        <v>1048</v>
-      </c>
-    </row>
-    <row r="18" ht="12.75" spans="1:30">
+    </row>
+    <row r="18" spans="1:27">
       <c r="A18" s="2">
         <v>1128</v>
       </c>
@@ -1745,14 +1679,8 @@
       <c r="AA18" s="2">
         <v>1087</v>
       </c>
-      <c r="AB18" s="2">
-        <v>1070</v>
-      </c>
-      <c r="AD18" s="2">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="19" ht="12.75" spans="1:30">
+    </row>
+    <row r="19" spans="1:27">
       <c r="A19" s="2">
         <v>1129</v>
       </c>
@@ -1797,14 +1725,8 @@
       <c r="AA19" s="2">
         <v>1086</v>
       </c>
-      <c r="AB19" s="2">
-        <v>1071</v>
-      </c>
-      <c r="AD19" s="2">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="20" ht="12.75" spans="1:30">
+    </row>
+    <row r="20" spans="1:27">
       <c r="A20" s="2">
         <v>1130</v>
       </c>
@@ -1849,14 +1771,8 @@
       <c r="AA20" s="2">
         <v>1085</v>
       </c>
-      <c r="AB20" s="2">
-        <v>1072</v>
-      </c>
-      <c r="AD20" s="2">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="21" ht="12.75" spans="1:30">
+    </row>
+    <row r="21" spans="1:27">
       <c r="A21" s="2">
         <v>1131</v>
       </c>
@@ -1909,14 +1825,8 @@
       <c r="AA21" s="2">
         <v>1084</v>
       </c>
-      <c r="AB21" s="2">
-        <v>1073</v>
-      </c>
-      <c r="AD21" s="2">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="22" ht="12.75" spans="1:30">
+    </row>
+    <row r="22" spans="1:27">
       <c r="A22" s="2">
         <v>1132</v>
       </c>
@@ -1969,14 +1879,8 @@
       <c r="AA22" s="2">
         <v>1083</v>
       </c>
-      <c r="AB22" s="2">
-        <v>1074</v>
-      </c>
-      <c r="AD22" s="2">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="23" ht="12.75" spans="1:30">
+    </row>
+    <row r="23" spans="1:27">
       <c r="A23" s="2">
         <v>1133</v>
       </c>
@@ -2029,14 +1933,8 @@
       <c r="AA23" s="2">
         <v>1082</v>
       </c>
-      <c r="AB23" s="2">
-        <v>1075</v>
-      </c>
-      <c r="AD23" s="2">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="24" ht="12.75" spans="1:30">
+    </row>
+    <row r="24" spans="1:27">
       <c r="A24" s="2">
         <v>1134</v>
       </c>
@@ -2089,14 +1987,8 @@
       <c r="AA24" s="2">
         <v>1081</v>
       </c>
-      <c r="AB24" s="2">
-        <v>1076</v>
-      </c>
-      <c r="AD24" s="2">
-        <v>1041</v>
-      </c>
-    </row>
-    <row r="25" ht="12.75" spans="1:30">
+    </row>
+    <row r="25" spans="1:27">
       <c r="A25" s="2">
         <v>1135</v>
       </c>
@@ -2150,14 +2042,8 @@
       <c r="AA25" s="2">
         <v>1080</v>
       </c>
-      <c r="AB25" s="2">
-        <v>1077</v>
-      </c>
-      <c r="AD25" s="2">
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="26" ht="12.75" spans="1:30">
+    </row>
+    <row r="26" spans="1:27">
       <c r="A26" s="2">
         <v>1136</v>
       </c>
@@ -2211,14 +2097,8 @@
       <c r="AA26" s="2">
         <v>1079</v>
       </c>
-      <c r="AB26" s="2">
-        <v>1078</v>
-      </c>
-      <c r="AD26" s="2">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="27" ht="12.75" spans="3:26">
+    </row>
+    <row r="27" spans="3:26">
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="H27" s="2"/>
